--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-16.xlsx
@@ -860,16 +860,16 @@
         <v>2.14</v>
       </c>
       <c r="G2" t="n">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="H2" t="n">
         <v>3.05</v>
       </c>
       <c r="I2" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="J2" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="K2" t="n">
         <v>4.3</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-14 01:01:34</t>
+          <t>2026-06-14 03:16:20</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-14 01:01:34</t>
+          <t>2026-06-14 03:16:20</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-14 01:01:34</t>
+          <t>2026-06-14 03:16:20</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-14 01:01:34</t>
+          <t>2026-06-14 03:16:20</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-14 01:01:34</t>
+          <t>2026-06-14 03:16:20</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-14 01:01:34</t>
+          <t>2026-06-14 03:16:20</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB7"/>
+  <dimension ref="A1:CB6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -860,16 +860,16 @@
         <v>2.14</v>
       </c>
       <c r="G2" t="n">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="H2" t="n">
         <v>3.05</v>
       </c>
       <c r="I2" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="J2" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="K2" t="n">
         <v>4.3</v>
@@ -1080,14 +1080,14 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-14 03:16:20</t>
+          <t>2026-06-14 05:31:26</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,36 +1097,36 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Always Ready</t>
+          <t>Vikingur Reykjavik</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>KR Reykjavik</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-14 03:16:20</t>
+          <t>2026-06-14 05:31:26</t>
         </is>
       </c>
     </row>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Vikingur Reykjavik</t>
+          <t>IA Akranes</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>KR Reykjavik</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -1395,7 +1395,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
       <c r="Q4" t="n">
         <v>1.01</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-14 03:16:20</t>
+          <t>2026-06-14 05:31:26</t>
         </is>
       </c>
     </row>
@@ -1610,12 +1610,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>IA Akranes</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1649,7 +1649,7 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="Q5" t="n">
         <v>1.01</v>
@@ -1842,14 +1842,14 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-14 03:16:20</t>
+          <t>2026-06-14 05:31:26</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,17 +1859,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Fortaleza EC</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>America MG</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1903,7 +1903,7 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q6" t="n">
         <v>1.01</v>
@@ -2096,261 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-14 03:16:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Brazilian Serie B</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>20:00:00</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Fortaleza EC</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>America MG</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB7" t="inlineStr">
-        <is>
-          <t>2026-06-14 03:16:20</t>
+          <t>2026-06-14 05:31:26</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-16.xlsx
@@ -860,13 +860,13 @@
         <v>2.14</v>
       </c>
       <c r="G2" t="n">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="H2" t="n">
         <v>3.05</v>
       </c>
       <c r="I2" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="J2" t="n">
         <v>3.65</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-14 05:31:26</t>
+          <t>2026-06-14 07:45:58</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-14 05:31:26</t>
+          <t>2026-06-14 07:45:58</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-14 05:31:26</t>
+          <t>2026-06-14 07:45:58</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-14 05:31:26</t>
+          <t>2026-06-14 07:45:58</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-14 05:31:26</t>
+          <t>2026-06-14 07:45:58</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-16.xlsx
@@ -860,16 +860,16 @@
         <v>2.14</v>
       </c>
       <c r="G2" t="n">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="H2" t="n">
         <v>3.05</v>
       </c>
       <c r="I2" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="J2" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="K2" t="n">
         <v>4.3</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-14 07:45:58</t>
+          <t>2026-06-14 09:59:38</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-14 07:45:58</t>
+          <t>2026-06-14 09:59:38</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-14 07:45:58</t>
+          <t>2026-06-14 09:59:38</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-14 07:45:58</t>
+          <t>2026-06-14 09:59:38</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-14 07:45:58</t>
+          <t>2026-06-14 09:59:38</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-16.xlsx
@@ -860,7 +860,7 @@
         <v>2.14</v>
       </c>
       <c r="G2" t="n">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="H2" t="n">
         <v>3.05</v>
@@ -869,7 +869,7 @@
         <v>3.55</v>
       </c>
       <c r="J2" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="K2" t="n">
         <v>4.3</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-14 09:59:38</t>
+          <t>2026-06-14 12:11:34</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-14 09:59:38</t>
+          <t>2026-06-14 12:11:34</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-14 09:59:38</t>
+          <t>2026-06-14 12:11:34</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-14 09:59:38</t>
+          <t>2026-06-14 12:11:34</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-14 09:59:38</t>
+          <t>2026-06-14 12:11:34</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-16.xlsx
@@ -857,16 +857,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="G2" t="n">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="H2" t="n">
         <v>3.05</v>
       </c>
       <c r="I2" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="J2" t="n">
         <v>3.65</v>
@@ -875,212 +875,212 @@
         <v>4.3</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="P2" t="n">
         <v>2.24</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BH2" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BP2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-14 12:11:34</t>
+          <t>2026-06-14 14:21:20</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-14 12:11:34</t>
+          <t>2026-06-14 14:21:20</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-14 12:11:34</t>
+          <t>2026-06-14 14:21:20</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-14 12:11:34</t>
+          <t>2026-06-14 14:21:20</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-14 12:11:34</t>
+          <t>2026-06-14 14:21:20</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-16.xlsx
@@ -866,7 +866,7 @@
         <v>3.05</v>
       </c>
       <c r="I2" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="J2" t="n">
         <v>3.65</v>
@@ -875,7 +875,7 @@
         <v>4.3</v>
       </c>
       <c r="L2" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="M2" t="n">
         <v>1.04</v>
@@ -893,70 +893,70 @@
         <v>1.64</v>
       </c>
       <c r="R2" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="S2" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="T2" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="U2" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="V2" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W2" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="X2" t="n">
         <v>24</v>
       </c>
       <c r="Y2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="Z2" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AA2" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AB2" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AD2" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AF2" t="n">
         <v>17.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AI2" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AJ2" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AK2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AL2" t="n">
         <v>32</v>
       </c>
       <c r="AM2" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AN2" t="n">
         <v>15</v>
@@ -965,52 +965,52 @@
         <v>29</v>
       </c>
       <c r="AP2" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AQ2" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AR2" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB2" t="n">
         <v>21</v>
       </c>
-      <c r="AS2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BC2" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>6.6</v>
+        <v>4.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.4</v>
+        <v>5</v>
       </c>
       <c r="BF2" t="n">
         <v>10</v>
@@ -1022,65 +1022,65 @@
         <v>4.2</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="BJ2" t="n">
         <v>9</v>
       </c>
       <c r="BK2" t="n">
-        <v>7.4</v>
+        <v>4.9</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>22</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN2" t="n">
         <v>5.6</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="BP2" t="n">
         <v>16</v>
       </c>
       <c r="BQ2" t="n">
-        <v>13</v>
+        <v>6.4</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>20</v>
+        <v>7.6</v>
       </c>
       <c r="BT2" t="n">
         <v>7</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>19.5</v>
+        <v>7.6</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>25</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ2" t="n">
         <v>19</v>
       </c>
       <c r="CA2" t="n">
-        <v>15.5</v>
+        <v>7</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-14 14:21:20</t>
+          <t>2026-06-14 16:30:24</t>
         </is>
       </c>
     </row>
@@ -1129,212 +1129,212 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="P3" t="n">
         <v>1.24</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-14 14:21:20</t>
+          <t>2026-06-14 16:30:24</t>
         </is>
       </c>
     </row>
@@ -1383,212 +1383,212 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="P4" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-14 14:21:20</t>
+          <t>2026-06-14 16:30:24</t>
         </is>
       </c>
     </row>
@@ -1637,212 +1637,212 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="P5" t="n">
         <v>1.24</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-14 14:21:20</t>
+          <t>2026-06-14 16:30:24</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-14 14:21:20</t>
+          <t>2026-06-14 16:30:24</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-16.xlsx
@@ -860,19 +860,19 @@
         <v>2.2</v>
       </c>
       <c r="G2" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="H2" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I2" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="J2" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K2" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L2" t="n">
         <v>1.31</v>
@@ -881,13 +881,13 @@
         <v>1.04</v>
       </c>
       <c r="N2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O2" t="n">
         <v>1.22</v>
       </c>
       <c r="P2" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q2" t="n">
         <v>1.64</v>
@@ -899,25 +899,25 @@
         <v>2.6</v>
       </c>
       <c r="T2" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="U2" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V2" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W2" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X2" t="n">
         <v>24</v>
       </c>
       <c r="Y2" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AA2" t="n">
         <v>65</v>
@@ -926,13 +926,13 @@
         <v>15</v>
       </c>
       <c r="AC2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AE2" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AF2" t="n">
         <v>17.5</v>
@@ -944,49 +944,49 @@
         <v>18</v>
       </c>
       <c r="AI2" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AJ2" t="n">
         <v>34</v>
       </c>
       <c r="AK2" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AL2" t="n">
         <v>32</v>
       </c>
       <c r="AM2" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN2" t="n">
         <v>15</v>
       </c>
       <c r="AO2" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AP2" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AQ2" t="n">
         <v>12.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AS2" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="AT2" t="n">
         <v>10</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AV2" t="n">
         <v>11</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="AX2" t="n">
         <v>12.5</v>
@@ -998,19 +998,19 @@
         <v>12</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>21</v>
+        <v>5.4</v>
       </c>
       <c r="BC2" t="n">
         <v>16.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BE2" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BF2" t="n">
         <v>10</v>
@@ -1040,7 +1040,7 @@
         <v>5.6</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BP2" t="n">
         <v>16</v>
@@ -1052,7 +1052,7 @@
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>7.6</v>
+        <v>18.5</v>
       </c>
       <c r="BT2" t="n">
         <v>7</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-14 16:30:24</t>
+          <t>2026-06-14 18:38:51</t>
         </is>
       </c>
     </row>
@@ -1135,19 +1135,19 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="O3" t="n">
         <v>1.04</v>
       </c>
       <c r="P3" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q3" t="n">
         <v>1.04</v>
       </c>
       <c r="R3" t="n">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="S3" t="n">
         <v>1.04</v>
@@ -1219,52 +1219,52 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF3" t="n">
         <v>1.01</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-14 16:30:24</t>
+          <t>2026-06-14 18:38:51</t>
         </is>
       </c>
     </row>
@@ -1386,10 +1386,10 @@
         <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N4" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="O4" t="n">
         <v>1.09</v>
@@ -1473,52 +1473,52 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF4" t="n">
         <v>1.01</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-14 16:30:24</t>
+          <t>2026-06-14 18:38:51</t>
         </is>
       </c>
     </row>
@@ -1643,19 +1643,19 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="O5" t="n">
         <v>1.05</v>
       </c>
       <c r="P5" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q5" t="n">
         <v>1.05</v>
       </c>
       <c r="R5" t="n">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="S5" t="n">
         <v>1.05</v>
@@ -1727,52 +1727,52 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF5" t="n">
         <v>1.01</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-14 16:30:24</t>
+          <t>2026-06-14 18:38:51</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-14 16:30:24</t>
+          <t>2026-06-14 18:38:51</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-16.xlsx
@@ -863,10 +863,10 @@
         <v>2.36</v>
       </c>
       <c r="H2" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I2" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J2" t="n">
         <v>3.75</v>
@@ -923,10 +923,10 @@
         <v>65</v>
       </c>
       <c r="AB2" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD2" t="n">
         <v>15</v>
@@ -938,10 +938,10 @@
         <v>17.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH2" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI2" t="n">
         <v>40</v>
@@ -959,7 +959,7 @@
         <v>70</v>
       </c>
       <c r="AN2" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO2" t="n">
         <v>26</v>
@@ -974,7 +974,7 @@
         <v>21</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AT2" t="n">
         <v>10</v>
@@ -986,7 +986,7 @@
         <v>11</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="AX2" t="n">
         <v>12.5</v>
@@ -998,19 +998,19 @@
         <v>12</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BC2" t="n">
         <v>16.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BF2" t="n">
         <v>10</v>
@@ -1040,7 +1040,7 @@
         <v>5.6</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="BP2" t="n">
         <v>16</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-14 18:38:51</t>
+          <t>2026-06-14 20:46:35</t>
         </is>
       </c>
     </row>
@@ -1150,13 +1150,13 @@
         <v>1.24</v>
       </c>
       <c r="S3" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U3" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V3" t="n">
         <v>1.01</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-14 18:38:51</t>
+          <t>2026-06-14 20:46:35</t>
         </is>
       </c>
     </row>
@@ -1389,28 +1389,28 @@
         <v>1.02</v>
       </c>
       <c r="N4" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="O4" t="n">
         <v>1.09</v>
       </c>
       <c r="P4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q4" t="n">
         <v>1.08</v>
       </c>
-      <c r="Q4" t="n">
-        <v>1.09</v>
-      </c>
       <c r="R4" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="S4" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V4" t="n">
         <v>1.01</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-14 18:38:51</t>
+          <t>2026-06-14 20:46:35</t>
         </is>
       </c>
     </row>
@@ -1643,28 +1643,28 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.26</v>
+        <v>1.79</v>
       </c>
       <c r="O5" t="n">
         <v>1.05</v>
       </c>
       <c r="P5" t="n">
-        <v>1.26</v>
+        <v>1.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="R5" t="n">
-        <v>1.26</v>
+        <v>1.79</v>
       </c>
       <c r="S5" t="n">
         <v>1.05</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V5" t="n">
         <v>1.01</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-14 18:38:51</t>
+          <t>2026-06-14 20:46:35</t>
         </is>
       </c>
     </row>
@@ -1873,230 +1873,230 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P6" t="n">
-        <v>1.25</v>
+        <v>1.58</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-14 18:38:51</t>
+          <t>2026-06-14 20:46:35</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-16.xlsx
@@ -866,7 +866,7 @@
         <v>3.05</v>
       </c>
       <c r="I2" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="J2" t="n">
         <v>3.75</v>
@@ -890,7 +890,7 @@
         <v>2.26</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="R2" t="n">
         <v>1.5</v>
@@ -1028,7 +1028,7 @@
         <v>9</v>
       </c>
       <c r="BK2" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-14 20:46:35</t>
+          <t>2026-06-14 22:53:46</t>
         </is>
       </c>
     </row>
@@ -1135,7 +1135,7 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="O3" t="n">
         <v>1.04</v>
@@ -1147,10 +1147,10 @@
         <v>1.04</v>
       </c>
       <c r="R3" t="n">
-        <v>1.24</v>
+        <v>1.97</v>
       </c>
       <c r="S3" t="n">
-        <v>1.05</v>
+        <v>1.31</v>
       </c>
       <c r="T3" t="n">
         <v>1.11</v>
@@ -1219,52 +1219,52 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF3" t="n">
         <v>1.01</v>
@@ -1276,65 +1276,65 @@
         <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN3" t="n">
         <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-14 20:46:35</t>
+          <t>2026-06-14 22:53:46</t>
         </is>
       </c>
     </row>
@@ -1398,13 +1398,13 @@
         <v>1.07</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="R4" t="n">
-        <v>1.22</v>
+        <v>1.56</v>
       </c>
       <c r="S4" t="n">
-        <v>1.05</v>
+        <v>1.56</v>
       </c>
       <c r="T4" t="n">
         <v>1.11</v>
@@ -1473,52 +1473,52 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
         <v>1.01</v>
@@ -1530,65 +1530,65 @@
         <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN4" t="n">
         <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT4" t="n">
         <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-14 20:46:35</t>
+          <t>2026-06-14 22:53:46</t>
         </is>
       </c>
     </row>
@@ -1643,22 +1643,22 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.79</v>
+        <v>1.1</v>
       </c>
       <c r="O5" t="n">
         <v>1.05</v>
       </c>
       <c r="P5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="R5" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.79</v>
-      </c>
       <c r="S5" t="n">
-        <v>1.05</v>
+        <v>1.43</v>
       </c>
       <c r="T5" t="n">
         <v>1.11</v>
@@ -1727,52 +1727,52 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
         <v>1.01</v>
@@ -1784,65 +1784,65 @@
         <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN5" t="n">
         <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT5" t="n">
         <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-14 20:46:35</t>
+          <t>2026-06-14 22:53:46</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="G6" t="n">
         <v>1.72</v>
@@ -1882,13 +1882,13 @@
         <v>6.2</v>
       </c>
       <c r="I6" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="J6" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="K6" t="n">
-        <v>950</v>
+        <v>6.8</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1897,16 +1897,16 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>2.7</v>
+        <v>2.98</v>
       </c>
       <c r="O6" t="n">
         <v>1.36</v>
       </c>
       <c r="P6" t="n">
-        <v>1.58</v>
+        <v>1.79</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="R6" t="n">
         <v>1.22</v>
@@ -1945,7 +1945,7 @@
         <v>11</v>
       </c>
       <c r="AD6" t="n">
-        <v>42</v>
+        <v>950</v>
       </c>
       <c r="AE6" t="n">
         <v>1000</v>
@@ -1957,7 +1957,7 @@
         <v>12.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>32</v>
+        <v>950</v>
       </c>
       <c r="AI6" t="n">
         <v>1000</v>
@@ -1975,128 +1975,128 @@
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.66</v>
+        <v>3.2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>2.82</v>
+        <v>3.5</v>
       </c>
       <c r="AR6" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AY6" t="n">
         <v>3.1</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>2.56</v>
       </c>
       <c r="AZ6" t="n">
         <v>19</v>
       </c>
       <c r="BA6" t="n">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="BB6" t="n">
-        <v>2.74</v>
+        <v>3.35</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.82</v>
+        <v>3.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.15</v>
+        <v>4</v>
       </c>
       <c r="BE6" t="n">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.2</v>
+        <v>7.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="BH6" t="n">
         <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN6" t="n">
         <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT6" t="n">
         <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-14 20:46:35</t>
+          <t>2026-06-14 22:53:46</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-16.xlsx
@@ -890,7 +890,7 @@
         <v>2.26</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="R2" t="n">
         <v>1.5</v>
@@ -1028,7 +1028,7 @@
         <v>9</v>
       </c>
       <c r="BK2" t="n">
-        <v>7</v>
+        <v>4.9</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
@@ -1052,7 +1052,7 @@
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>18.5</v>
+        <v>7.6</v>
       </c>
       <c r="BT2" t="n">
         <v>7</v>
@@ -1076,11 +1076,11 @@
         <v>19</v>
       </c>
       <c r="CA2" t="n">
-        <v>7</v>
+        <v>13.5</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-14 22:53:46</t>
+          <t>2026-06-15 01:00:47</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-14 22:53:46</t>
+          <t>2026-06-15 01:00:47</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-14 22:53:46</t>
+          <t>2026-06-15 01:00:47</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-14 22:53:46</t>
+          <t>2026-06-15 01:00:47</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="G6" t="n">
         <v>1.72</v>
@@ -1888,7 +1888,7 @@
         <v>3.75</v>
       </c>
       <c r="K6" t="n">
-        <v>6.8</v>
+        <v>950</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1993,7 +1993,7 @@
         <v>4.1</v>
       </c>
       <c r="AT6" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="AU6" t="n">
         <v>3</v>
@@ -2023,7 +2023,7 @@
         <v>3.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BE6" t="n">
         <v>4.1</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-14 22:53:46</t>
+          <t>2026-06-15 01:00:47</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-16.xlsx
@@ -863,7 +863,7 @@
         <v>2.36</v>
       </c>
       <c r="H2" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="I2" t="n">
         <v>3.5</v>
@@ -878,7 +878,7 @@
         <v>1.31</v>
       </c>
       <c r="M2" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N2" t="n">
         <v>4.7</v>
@@ -890,13 +890,13 @@
         <v>2.26</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="R2" t="n">
         <v>1.5</v>
       </c>
       <c r="S2" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T2" t="n">
         <v>1.59</v>
@@ -908,7 +908,7 @@
         <v>1.4</v>
       </c>
       <c r="W2" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X2" t="n">
         <v>24</v>
@@ -920,13 +920,13 @@
         <v>27</v>
       </c>
       <c r="AA2" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AB2" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD2" t="n">
         <v>15</v>
@@ -938,7 +938,7 @@
         <v>17.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH2" t="n">
         <v>17.5</v>
@@ -947,7 +947,7 @@
         <v>40</v>
       </c>
       <c r="AJ2" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AK2" t="n">
         <v>23</v>
@@ -956,10 +956,10 @@
         <v>32</v>
       </c>
       <c r="AM2" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN2" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AO2" t="n">
         <v>26</v>
@@ -974,7 +974,7 @@
         <v>21</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AT2" t="n">
         <v>10</v>
@@ -986,7 +986,7 @@
         <v>11</v>
       </c>
       <c r="AW2" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AX2" t="n">
         <v>12.5</v>
@@ -998,19 +998,19 @@
         <v>12</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB2" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BC2" t="n">
         <v>16.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BE2" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF2" t="n">
         <v>10</v>
@@ -1028,31 +1028,31 @@
         <v>9</v>
       </c>
       <c r="BK2" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BO2" t="n">
         <v>4.3</v>
       </c>
       <c r="BP2" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BT2" t="n">
         <v>7</v>
@@ -1064,23 +1064,23 @@
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BZ2" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>13.5</v>
+        <v>7.2</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-15 01:00:47</t>
+          <t>2026-06-15 03:07:48</t>
         </is>
       </c>
     </row>
@@ -1219,58 +1219,58 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BH3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-15 01:00:47</t>
+          <t>2026-06-15 03:07:48</t>
         </is>
       </c>
     </row>
@@ -1473,58 +1473,58 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BH4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-15 01:00:47</t>
+          <t>2026-06-15 03:07:48</t>
         </is>
       </c>
     </row>
@@ -1727,58 +1727,58 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BH5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-15 01:00:47</t>
+          <t>2026-06-15 03:07:48</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
         <v>1.46</v>
       </c>
       <c r="G6" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="H6" t="n">
         <v>6.2</v>
@@ -1888,25 +1888,25 @@
         <v>3.75</v>
       </c>
       <c r="K6" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M6" t="n">
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>2.98</v>
+        <v>1.1</v>
       </c>
       <c r="O6" t="n">
         <v>1.36</v>
       </c>
       <c r="P6" t="n">
-        <v>1.79</v>
+        <v>1.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.1</v>
+        <v>1.77</v>
       </c>
       <c r="R6" t="n">
         <v>1.22</v>
@@ -1924,7 +1924,7 @@
         <v>1.11</v>
       </c>
       <c r="W6" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="X6" t="n">
         <v>15</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-15 01:00:47</t>
+          <t>2026-06-15 03:07:48</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB6"/>
+  <dimension ref="A1:CB9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,251 +843,251 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Varnamo</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Helsingborgs</t>
+          <t>SK Super Nova</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.2</v>
+        <v>1.02</v>
       </c>
       <c r="G2" t="n">
-        <v>2.36</v>
+        <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>3.15</v>
+        <v>1.02</v>
       </c>
       <c r="I2" t="n">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>3.75</v>
+        <v>1.02</v>
       </c>
       <c r="K2" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="L2" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>4.7</v>
+        <v>1.26</v>
       </c>
       <c r="O2" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="P2" t="n">
-        <v>2.26</v>
+        <v>1.26</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.65</v>
+        <v>1.3</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="T2" t="n">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR2" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AU2" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AV2" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AW2" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AX2" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY2" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AZ2" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="BC2" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD2" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="BF2" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="BJ2" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BP2" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BT2" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-15 03:07:48</t>
+          <t>2026-06-15 05:15:13</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,251 +1097,251 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Vikingur Reykjavik</t>
+          <t>FK Suduva</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>KR Reykjavik</t>
+          <t>FK Siauliai</t>
         </is>
       </c>
       <c r="F3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ3" t="n">
         <v>0</v>
       </c>
-      <c r="G3" t="n">
+      <c r="CA3" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>1.04</v>
-      </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-15 03:07:48</t>
+          <t>2026-06-15 05:15:13</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,251 +1351,251 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>IA Akranes</t>
+          <t>VMFD Zalgiris</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Panevezys</t>
         </is>
       </c>
       <c r="F4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ4" t="n">
         <v>0</v>
       </c>
-      <c r="G4" t="n">
+      <c r="CA4" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>1.04</v>
-      </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-15 03:07:48</t>
+          <t>2026-06-15 05:15:13</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,251 +1605,251 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Varnamo</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Helsingborgs</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N5" t="n">
-        <v>1.1</v>
+        <v>4.7</v>
       </c>
       <c r="O5" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="P5" t="n">
-        <v>1.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.05</v>
+        <v>1.64</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="S5" t="n">
-        <v>1.43</v>
+        <v>2.62</v>
       </c>
       <c r="T5" t="n">
-        <v>1.11</v>
+        <v>1.59</v>
       </c>
       <c r="U5" t="n">
-        <v>1.11</v>
+        <v>2.4</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.1</v>
+        <v>17.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.1</v>
+        <v>12.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.1</v>
+        <v>21</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.1</v>
+        <v>7.6</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.1</v>
+        <v>10</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.1</v>
+        <v>8</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.1</v>
+        <v>11</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.1</v>
+        <v>7.4</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.1</v>
+        <v>12.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.1</v>
+        <v>12</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.1</v>
+        <v>7.4</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.1</v>
+        <v>7.2</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.1</v>
+        <v>16.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.1</v>
+        <v>7.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.1</v>
+        <v>7.8</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.1</v>
+        <v>10</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.1</v>
+        <v>18.5</v>
       </c>
       <c r="BH5" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BN5" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BP5" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.04</v>
+        <v>18.5</v>
       </c>
       <c r="BT5" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-15 03:07:48</t>
+          <t>2026-06-15 05:15:13</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,39 +1859,39 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Fortaleza EC</t>
+          <t>Vikingur Reykjavik</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>America MG</t>
+          <t>KR Reykjavik</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
         <v>1.01</v>
@@ -1900,203 +1900,965 @@
         <v>1.1</v>
       </c>
       <c r="O6" t="n">
-        <v>1.36</v>
+        <v>1.04</v>
       </c>
       <c r="P6" t="n">
         <v>1.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.77</v>
+        <v>1.04</v>
       </c>
       <c r="R6" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>2026-06-15 05:15:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Icelandic Urvalsdeild</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>IA Akranes</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Valur</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>2026-06-15 05:15:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Icelandic Urvalsdeild</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Stjarnan</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Breidablik</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>2026-06-15 05:15:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Fortaleza EC</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>America MG</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="H9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R9" t="n">
         <v>1.22</v>
       </c>
-      <c r="S6" t="n">
+      <c r="S9" t="n">
         <v>3.4</v>
       </c>
-      <c r="T6" t="n">
+      <c r="T9" t="n">
         <v>1.94</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U9" t="n">
         <v>1.6</v>
       </c>
-      <c r="V6" t="n">
+      <c r="V9" t="n">
         <v>1.11</v>
       </c>
-      <c r="W6" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="X6" t="n">
+      <c r="W9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="X9" t="n">
         <v>15</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="Y9" t="n">
         <v>24</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="Z9" t="n">
         <v>75</v>
       </c>
-      <c r="AA6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB6" t="n">
+      <c r="AA9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB9" t="n">
         <v>8</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AC9" t="n">
         <v>11</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="AD9" t="n">
         <v>950</v>
       </c>
-      <c r="AE6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF6" t="n">
+      <c r="AE9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF9" t="n">
         <v>10</v>
       </c>
-      <c r="AG6" t="n">
+      <c r="AG9" t="n">
         <v>12.5</v>
       </c>
-      <c r="AH6" t="n">
+      <c r="AH9" t="n">
         <v>950</v>
       </c>
-      <c r="AI6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ6" t="n">
+      <c r="AI9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ9" t="n">
         <v>18.5</v>
       </c>
-      <c r="AK6" t="n">
+      <c r="AK9" t="n">
         <v>24</v>
       </c>
-      <c r="AL6" t="n">
+      <c r="AL9" t="n">
         <v>55</v>
       </c>
-      <c r="AM6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN6" t="n">
+      <c r="AM9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN9" t="n">
         <v>14.5</v>
       </c>
-      <c r="AO6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP6" t="n">
+      <c r="AO9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP9" t="n">
         <v>3.2</v>
       </c>
-      <c r="AQ6" t="n">
+      <c r="AQ9" t="n">
         <v>3.5</v>
       </c>
-      <c r="AR6" t="n">
+      <c r="AR9" t="n">
         <v>3.95</v>
       </c>
-      <c r="AS6" t="n">
+      <c r="AS9" t="n">
         <v>4.1</v>
       </c>
-      <c r="AT6" t="n">
+      <c r="AT9" t="n">
         <v>2.72</v>
       </c>
-      <c r="AU6" t="n">
+      <c r="AU9" t="n">
         <v>3</v>
       </c>
-      <c r="AV6" t="n">
+      <c r="AV9" t="n">
         <v>3.75</v>
       </c>
-      <c r="AW6" t="n">
+      <c r="AW9" t="n">
         <v>4.1</v>
       </c>
-      <c r="AX6" t="n">
+      <c r="AX9" t="n">
         <v>2.92</v>
       </c>
-      <c r="AY6" t="n">
+      <c r="AY9" t="n">
         <v>3.1</v>
       </c>
-      <c r="AZ6" t="n">
+      <c r="AZ9" t="n">
         <v>19</v>
       </c>
-      <c r="BA6" t="n">
+      <c r="BA9" t="n">
         <v>4.1</v>
       </c>
-      <c r="BB6" t="n">
+      <c r="BB9" t="n">
         <v>3.35</v>
       </c>
-      <c r="BC6" t="n">
+      <c r="BC9" t="n">
         <v>3.5</v>
       </c>
-      <c r="BD6" t="n">
+      <c r="BD9" t="n">
         <v>4.1</v>
       </c>
-      <c r="BE6" t="n">
+      <c r="BE9" t="n">
         <v>4.1</v>
       </c>
-      <c r="BF6" t="n">
+      <c r="BF9" t="n">
         <v>7.6</v>
       </c>
-      <c r="BG6" t="n">
+      <c r="BG9" t="n">
         <v>4.1</v>
       </c>
-      <c r="BH6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>2026-06-15 03:07:48</t>
+      <c r="BH9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>2026-06-15 05:15:13</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB9"/>
+  <dimension ref="A1:CB13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -881,22 +881,22 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="O2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="P2" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="R2" t="n">
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>2.42</v>
+        <v>2.84</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-15 05:15:13</t>
+          <t>2026-06-15 07:22:59</t>
         </is>
       </c>
     </row>
@@ -1135,22 +1135,22 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="O3" t="n">
         <v>1.27</v>
       </c>
       <c r="P3" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Q3" t="n">
         <v>1.27</v>
       </c>
       <c r="R3" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="S3" t="n">
-        <v>1.27</v>
+        <v>2.74</v>
       </c>
       <c r="T3" t="n">
         <v>1.01</v>
@@ -1334,14 +1334,14 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-15 05:15:13</t>
+          <t>2026-06-15 07:22:59</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lithuanian A Lyga</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,27 +1351,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VMFD Zalgiris</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Panevezys</t>
+          <t>Trans Narva</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="G4" t="n">
         <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="I4" t="n">
         <v>1000</v>
@@ -1380,31 +1380,31 @@
         <v>1.02</v>
       </c>
       <c r="K4" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N4" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="O4" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="P4" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="R4" t="n">
         <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>2.5</v>
+        <v>1.22</v>
       </c>
       <c r="T4" t="n">
         <v>1.01</v>
@@ -1588,14 +1588,14 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-15 05:15:13</t>
+          <t>2026-06-15 07:22:59</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,251 +1605,251 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Varnamo</t>
+          <t>Parnu JK Vaprus</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Helsingborgs</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="G5" t="n">
-        <v>2.32</v>
+        <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="I5" t="n">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="K5" t="n">
-        <v>4.1</v>
+        <v>950</v>
       </c>
       <c r="L5" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="N5" t="n">
-        <v>4.7</v>
+        <v>1.25</v>
       </c>
       <c r="O5" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="P5" t="n">
-        <v>2.26</v>
+        <v>1.24</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.64</v>
+        <v>1.13</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>2.62</v>
+        <v>1.13</v>
       </c>
       <c r="T5" t="n">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="BA5" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="BF5" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="BJ5" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN5" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BP5" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT5" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-15 05:15:13</t>
+          <t>2026-06-15 07:22:59</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,66 +1859,66 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Vikingur Reykjavik</t>
+          <t>SC Grobina</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>KR Reykjavik</t>
+          <t>Liepajas Metalurgs</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="O6" t="n">
-        <v>1.04</v>
+        <v>1.24</v>
       </c>
       <c r="P6" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.04</v>
+        <v>1.24</v>
       </c>
       <c r="R6" t="n">
-        <v>1.97</v>
+        <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>1.31</v>
+        <v>2.56</v>
       </c>
       <c r="T6" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
         <v>1.01</v>
@@ -1981,129 +1981,129 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="n">
         <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN6" t="n">
         <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT6" t="n">
         <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-15 05:15:13</t>
+          <t>2026-06-15 07:22:59</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,251 +2113,251 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>IA Akranes</t>
+          <t>VMFD Zalgiris</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Panevezys</t>
         </is>
       </c>
       <c r="F7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ7" t="n">
         <v>0</v>
       </c>
-      <c r="G7" t="n">
+      <c r="CA7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>1.04</v>
-      </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-15 05:15:13</t>
+          <t>2026-06-15 07:22:59</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,498 +2367,1514 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Varnamo</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Helsingborgs</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>1.1</v>
+        <v>4.7</v>
       </c>
       <c r="O8" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="P8" t="n">
-        <v>1.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.05</v>
+        <v>1.64</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="S8" t="n">
-        <v>1.43</v>
+        <v>2.62</v>
       </c>
       <c r="T8" t="n">
-        <v>1.11</v>
+        <v>1.59</v>
       </c>
       <c r="U8" t="n">
-        <v>1.11</v>
+        <v>2.4</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.1</v>
+        <v>17.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.1</v>
+        <v>12.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.1</v>
+        <v>21</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.1</v>
+        <v>40</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.1</v>
+        <v>10</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.1</v>
+        <v>8</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.1</v>
+        <v>11</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.1</v>
+        <v>7.4</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.1</v>
+        <v>12.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.1</v>
+        <v>12</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.1</v>
+        <v>28</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.1</v>
+        <v>7.2</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.1</v>
+        <v>16.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.1</v>
+        <v>7.4</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.1</v>
+        <v>7.8</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.1</v>
+        <v>10</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.1</v>
+        <v>18.5</v>
       </c>
       <c r="BH8" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BN8" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BP8" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BT8" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-15 05:15:13</t>
+          <t>2026-06-15 07:22:59</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Swedish Superettan</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Landskrona</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>United IK Nordic</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X9" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>29</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>2026-06-15 07:22:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Icelandic Urvalsdeild</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Vikingur Reykjavik</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>KR Reykjavik</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>2026-06-15 07:22:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Icelandic Urvalsdeild</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>IA Akranes</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Valur</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>2026-06-15 07:22:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Icelandic Urvalsdeild</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Stjarnan</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Breidablik</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>2026-06-15 07:22:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>Brazilian Serie B</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>2026-06-16</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Fortaleza EC</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>America MG</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="G9" t="n">
+      <c r="F13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="H13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S13" t="n">
+        <v>4</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U13" t="n">
         <v>1.73</v>
       </c>
-      <c r="H9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="I9" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="X9" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>24</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>75</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB9" t="n">
+      <c r="V13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X13" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>330</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>170</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>240</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>280</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR13" t="n">
         <v>8</v>
       </c>
-      <c r="AC9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG9" t="n">
+      <c r="AS13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB13" t="n">
         <v>12.5</v>
       </c>
-      <c r="AH9" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BF9" t="n">
+      <c r="BC13" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD13" t="n">
         <v>7.6</v>
       </c>
-      <c r="BG9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BZ9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>2026-06-15 05:15:13</t>
+      <c r="BE13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>2026-06-15 07:22:59</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-16.xlsx
@@ -857,178 +857,178 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.02</v>
+        <v>1.9</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>2.14</v>
       </c>
       <c r="H2" t="n">
-        <v>1.02</v>
+        <v>3.65</v>
       </c>
       <c r="I2" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="J2" t="n">
-        <v>1.02</v>
+        <v>3.45</v>
       </c>
       <c r="K2" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>1.28</v>
+        <v>3.5</v>
       </c>
       <c r="O2" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="P2" t="n">
-        <v>1.28</v>
+        <v>1.88</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.28</v>
+        <v>1.9</v>
       </c>
       <c r="R2" t="n">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="S2" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA2" t="n">
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI2" t="n">
         <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM2" t="n">
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.03</v>
+        <v>1.94</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.03</v>
+        <v>1.94</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>1.84</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>1.9</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.03</v>
+        <v>2.2</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.03</v>
+        <v>2.2</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.03</v>
+        <v>1.94</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.03</v>
+        <v>1.88</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.03</v>
+        <v>1.71</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.03</v>
+        <v>1.67</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.03</v>
+        <v>1.78</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.03</v>
+        <v>1.88</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.03</v>
+        <v>1.81</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.03</v>
+        <v>1.8</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.03</v>
+        <v>1.85</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.03</v>
+        <v>1.9</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="BH2" t="n">
         <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.01</v>
+        <v>2.82</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
@@ -1040,31 +1040,31 @@
         <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-15 07:22:59</t>
+          <t>2026-06-15 09:31:21</t>
         </is>
       </c>
     </row>
@@ -1111,58 +1111,58 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.02</v>
+        <v>1.49</v>
       </c>
       <c r="G3" t="n">
-        <v>1000</v>
+        <v>1.83</v>
       </c>
       <c r="H3" t="n">
-        <v>1.02</v>
+        <v>4.1</v>
       </c>
       <c r="I3" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="J3" t="n">
-        <v>1.02</v>
+        <v>3.65</v>
       </c>
       <c r="K3" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>1.09</v>
+        <v>3.6</v>
       </c>
       <c r="O3" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="P3" t="n">
-        <v>1.09</v>
+        <v>1.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.27</v>
+        <v>1.84</v>
       </c>
       <c r="R3" t="n">
-        <v>1.09</v>
+        <v>1.35</v>
       </c>
       <c r="S3" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="T3" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="U3" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1276,13 +1276,13 @@
         <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.01</v>
+        <v>2.8</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1294,25 +1294,25 @@
         <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-15 07:22:59</t>
+          <t>2026-06-15 09:31:21</t>
         </is>
       </c>
     </row>
@@ -1365,175 +1365,175 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.01</v>
+        <v>2.54</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="H4" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.02</v>
+        <v>3.15</v>
       </c>
       <c r="K4" t="n">
-        <v>950</v>
+        <v>4.4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M4" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O4" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P4" t="n">
-        <v>1.27</v>
+        <v>1.98</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.21</v>
+        <v>1.6</v>
       </c>
       <c r="R4" t="n">
-        <v>1.18</v>
+        <v>1.43</v>
       </c>
       <c r="S4" t="n">
-        <v>1.22</v>
+        <v>2.26</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.03</v>
+        <v>3</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BH4" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BI4" t="n">
         <v>1.01</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK4" t="n">
         <v>1.01</v>
@@ -1542,40 +1542,40 @@
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN4" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BO4" t="n">
         <v>1.01</v>
       </c>
       <c r="BP4" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BQ4" t="n">
         <v>1.01</v>
       </c>
       <c r="BR4" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS4" t="n">
         <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU4" t="n">
         <v>1.01</v>
       </c>
       <c r="BV4" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BW4" t="n">
         <v>1.01</v>
       </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY4" t="n">
         <v>1.01</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-15 07:22:59</t>
+          <t>2026-06-15 09:31:21</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G5" t="n">
         <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K5" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1643,19 +1643,19 @@
         <v>1.02</v>
       </c>
       <c r="N5" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O5" t="n">
         <v>1.13</v>
       </c>
       <c r="P5" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Q5" t="n">
         <v>1.13</v>
       </c>
       <c r="R5" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S5" t="n">
         <v>1.13</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-15 07:22:59</t>
+          <t>2026-06-15 09:31:21</t>
         </is>
       </c>
     </row>
@@ -1873,25 +1873,25 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.02</v>
+        <v>3.4</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="H6" t="n">
-        <v>1.02</v>
+        <v>1.83</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>2.12</v>
       </c>
       <c r="J6" t="n">
-        <v>1.02</v>
+        <v>3.4</v>
       </c>
       <c r="K6" t="n">
-        <v>950</v>
+        <v>4.4</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M6" t="n">
         <v>1.05</v>
@@ -1903,200 +1903,200 @@
         <v>1.24</v>
       </c>
       <c r="P6" t="n">
-        <v>1.26</v>
+        <v>2.08</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.24</v>
+        <v>1.7</v>
       </c>
       <c r="R6" t="n">
-        <v>1.18</v>
+        <v>1.43</v>
       </c>
       <c r="S6" t="n">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.03</v>
+        <v>3.05</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BH6" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN6" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BP6" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR6" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT6" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BV6" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BX6" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-15 07:22:59</t>
+          <t>2026-06-15 09:31:21</t>
         </is>
       </c>
     </row>
@@ -2127,220 +2127,220 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.02</v>
+        <v>1.53</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>1.65</v>
       </c>
       <c r="H7" t="n">
-        <v>1.02</v>
+        <v>5.3</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="J7" t="n">
-        <v>1.02</v>
+        <v>3.7</v>
       </c>
       <c r="K7" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M7" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>1.29</v>
+        <v>3.75</v>
       </c>
       <c r="O7" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="P7" t="n">
-        <v>1.29</v>
+        <v>2.12</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.23</v>
+        <v>1.64</v>
       </c>
       <c r="R7" t="n">
-        <v>1.19</v>
+        <v>1.44</v>
       </c>
       <c r="S7" t="n">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BH7" t="n">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN7" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BP7" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BR7" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BT7" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-15 07:22:59</t>
+          <t>2026-06-15 09:31:21</t>
         </is>
       </c>
     </row>
@@ -2402,7 +2402,7 @@
         <v>1.31</v>
       </c>
       <c r="M8" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N8" t="n">
         <v>4.7</v>
@@ -2414,16 +2414,16 @@
         <v>2.26</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="R8" t="n">
         <v>1.5</v>
       </c>
       <c r="S8" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="T8" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U8" t="n">
         <v>2.4</v>
@@ -2438,7 +2438,7 @@
         <v>24</v>
       </c>
       <c r="Y8" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="Z8" t="n">
         <v>27</v>
@@ -2459,22 +2459,22 @@
         <v>36</v>
       </c>
       <c r="AF8" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG8" t="n">
         <v>12</v>
       </c>
       <c r="AH8" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI8" t="n">
         <v>40</v>
       </c>
       <c r="AJ8" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL8" t="n">
         <v>32</v>
@@ -2483,7 +2483,7 @@
         <v>65</v>
       </c>
       <c r="AN8" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AO8" t="n">
         <v>26</v>
@@ -2510,7 +2510,7 @@
         <v>11</v>
       </c>
       <c r="AW8" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AX8" t="n">
         <v>12.5</v>
@@ -2525,25 +2525,25 @@
         <v>28</v>
       </c>
       <c r="BB8" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BC8" t="n">
         <v>16.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BE8" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BG8" t="n">
         <v>18.5</v>
       </c>
       <c r="BH8" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BI8" t="n">
         <v>3.3</v>
@@ -2552,31 +2552,31 @@
         <v>9</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN8" t="n">
         <v>5.5</v>
       </c>
       <c r="BO8" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BP8" t="n">
         <v>15.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BT8" t="n">
         <v>7</v>
@@ -2588,23 +2588,23 @@
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="CA8" t="n">
-        <v>7.2</v>
+        <v>14</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-15 07:22:59</t>
+          <t>2026-06-15 09:31:21</t>
         </is>
       </c>
     </row>
@@ -2635,166 +2635,166 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.58</v>
+        <v>2.44</v>
       </c>
       <c r="G9" t="n">
-        <v>2.88</v>
+        <v>2.64</v>
       </c>
       <c r="H9" t="n">
-        <v>2.54</v>
+        <v>2.74</v>
       </c>
       <c r="I9" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J9" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="K9" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L9" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
         <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="O9" t="n">
         <v>1.23</v>
       </c>
       <c r="P9" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R9" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S9" t="n">
-        <v>2.58</v>
+        <v>2.72</v>
       </c>
       <c r="T9" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U9" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V9" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W9" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="X9" t="n">
         <v>26</v>
       </c>
       <c r="Y9" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="Z9" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AB9" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AC9" t="n">
         <v>12.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AE9" t="n">
         <v>38</v>
       </c>
       <c r="AF9" t="n">
-        <v>29</v>
+        <v>970</v>
       </c>
       <c r="AG9" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AH9" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AI9" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK9" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="AL9" t="n">
         <v>36</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN9" t="n">
-        <v>25</v>
+        <v>970</v>
       </c>
       <c r="AO9" t="n">
         <v>25</v>
       </c>
       <c r="AP9" t="n">
-        <v>3.35</v>
+        <v>2.32</v>
       </c>
       <c r="AQ9" t="n">
-        <v>3.75</v>
+        <v>2.54</v>
       </c>
       <c r="AR9" t="n">
-        <v>3.35</v>
+        <v>2.92</v>
       </c>
       <c r="AS9" t="n">
-        <v>2.94</v>
+        <v>2.66</v>
       </c>
       <c r="AT9" t="n">
-        <v>3.5</v>
+        <v>2.36</v>
       </c>
       <c r="AU9" t="n">
-        <v>3.7</v>
+        <v>3.05</v>
       </c>
       <c r="AV9" t="n">
-        <v>4.2</v>
+        <v>2.38</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.8</v>
+        <v>2.64</v>
       </c>
       <c r="AX9" t="n">
         <v>3.35</v>
       </c>
       <c r="AY9" t="n">
-        <v>3.6</v>
+        <v>5.7</v>
       </c>
       <c r="AZ9" t="n">
-        <v>3.55</v>
+        <v>2.48</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="BB9" t="n">
-        <v>2.94</v>
+        <v>2.72</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.1</v>
+        <v>2.98</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.3</v>
+        <v>2.68</v>
       </c>
       <c r="BE9" t="n">
-        <v>3.25</v>
+        <v>2.72</v>
       </c>
       <c r="BF9" t="n">
-        <v>3.55</v>
+        <v>2.44</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.55</v>
+        <v>6.8</v>
       </c>
       <c r="BH9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-15 07:22:59</t>
+          <t>2026-06-15 09:31:21</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-15 07:22:59</t>
+          <t>2026-06-15 09:31:21</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-15 07:22:59</t>
+          <t>2026-06-15 09:31:21</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-15 07:22:59</t>
+          <t>2026-06-15 09:31:21</t>
         </is>
       </c>
     </row>
@@ -3660,10 +3660,10 @@
         <v>6.8</v>
       </c>
       <c r="I13" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J13" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K13" t="n">
         <v>4.4</v>
@@ -3675,28 +3675,28 @@
         <v>1.08</v>
       </c>
       <c r="N13" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O13" t="n">
         <v>1.38</v>
       </c>
       <c r="P13" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="R13" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
       </c>
       <c r="T13" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U13" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="V13" t="n">
         <v>1.15</v>
@@ -3711,7 +3711,7 @@
         <v>21</v>
       </c>
       <c r="Z13" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AA13" t="n">
         <v>330</v>
@@ -3720,10 +3720,10 @@
         <v>7</v>
       </c>
       <c r="AC13" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>32</v>
+        <v>950</v>
       </c>
       <c r="AE13" t="n">
         <v>170</v>
@@ -3732,7 +3732,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AG13" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH13" t="n">
         <v>950</v>
@@ -3744,13 +3744,13 @@
         <v>15.5</v>
       </c>
       <c r="AK13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL13" t="n">
         <v>50</v>
       </c>
       <c r="AM13" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AN13" t="n">
         <v>12.5</v>
@@ -3765,10 +3765,10 @@
         <v>17</v>
       </c>
       <c r="AR13" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT13" t="n">
         <v>5.9</v>
@@ -3777,10 +3777,10 @@
         <v>8</v>
       </c>
       <c r="AV13" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AW13" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AX13" t="n">
         <v>7.2</v>
@@ -3789,10 +3789,10 @@
         <v>8.6</v>
       </c>
       <c r="AZ13" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BA13" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BB13" t="n">
         <v>12.5</v>
@@ -3801,16 +3801,16 @@
         <v>16</v>
       </c>
       <c r="BD13" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF13" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BG13" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-15 07:22:59</t>
+          <t>2026-06-15 09:31:21</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB13"/>
+  <dimension ref="A1:CB14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -863,7 +863,7 @@
         <v>2.14</v>
       </c>
       <c r="H2" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="I2" t="n">
         <v>5.2</v>
@@ -875,13 +875,13 @@
         <v>4.7</v>
       </c>
       <c r="L2" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O2" t="n">
         <v>1.31</v>
@@ -911,10 +911,10 @@
         <v>1.87</v>
       </c>
       <c r="X2" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="Y2" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="Z2" t="n">
         <v>38</v>
@@ -923,22 +923,22 @@
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.6</v>
+        <v>970</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.6</v>
+        <v>970</v>
       </c>
       <c r="AD2" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AE2" t="n">
         <v>65</v>
       </c>
       <c r="AF2" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AG2" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AH2" t="n">
         <v>22</v>
@@ -959,64 +959,64 @@
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AO2" t="n">
         <v>70</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.94</v>
+        <v>2.9</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.94</v>
+        <v>3.55</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.84</v>
+        <v>3.25</v>
       </c>
       <c r="AS2" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW2" t="n">
         <v>1.9</v>
       </c>
-      <c r="AT2" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>1.88</v>
-      </c>
       <c r="AX2" t="n">
-        <v>1.71</v>
+        <v>2.88</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.67</v>
+        <v>2.78</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.78</v>
+        <v>3.05</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.81</v>
+        <v>2.38</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.8</v>
+        <v>2.36</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.85</v>
+        <v>3.3</v>
       </c>
       <c r="BE2" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BG2" t="n">
         <v>1.9</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>1.88</v>
       </c>
       <c r="BH2" t="n">
         <v>1000</v>
@@ -1028,7 +1028,7 @@
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
@@ -1040,31 +1040,31 @@
         <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-15 09:31:21</t>
+          <t>2026-06-15 11:39:29</t>
         </is>
       </c>
     </row>
@@ -1144,19 +1144,19 @@
         <v>1.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.84</v>
+        <v>1.74</v>
       </c>
       <c r="R3" t="n">
         <v>1.35</v>
       </c>
       <c r="S3" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="T3" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="U3" t="n">
         <v>1.87</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.86</v>
       </c>
       <c r="V3" t="n">
         <v>1.13</v>
@@ -1282,7 +1282,7 @@
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1294,25 +1294,25 @@
         <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-15 09:31:21</t>
+          <t>2026-06-15 11:39:29</t>
         </is>
       </c>
     </row>
@@ -1365,220 +1365,220 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="G4" t="n">
-        <v>3.35</v>
+        <v>2.76</v>
       </c>
       <c r="H4" t="n">
-        <v>2.24</v>
+        <v>2.7</v>
       </c>
       <c r="I4" t="n">
         <v>3.05</v>
       </c>
       <c r="J4" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K4" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="L4" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="M4" t="n">
         <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>1.3</v>
+        <v>4.1</v>
       </c>
       <c r="O4" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="P4" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="R4" t="n">
         <v>1.43</v>
       </c>
       <c r="S4" t="n">
-        <v>2.26</v>
+        <v>2.86</v>
       </c>
       <c r="T4" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="U4" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V4" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="W4" t="n">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="X4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z4" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AA4" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AB4" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AC4" t="n">
         <v>10.5</v>
       </c>
       <c r="AD4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR4" t="n">
         <v>15</v>
       </c>
-      <c r="AE4" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>26</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH4" t="n">
+      <c r="AS4" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BP4" t="n">
         <v>19</v>
       </c>
-      <c r="AI4" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>26</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>22</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>4</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>22</v>
-      </c>
       <c r="BQ4" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BR4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BT4" t="n">
         <v>6.4</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BV4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BX4" t="n">
         <v>32</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-15 09:31:21</t>
+          <t>2026-06-15 11:39:29</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.02</v>
+        <v>6.4</v>
       </c>
       <c r="G5" t="n">
         <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>1.02</v>
+        <v>1.33</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>1.5</v>
       </c>
       <c r="J5" t="n">
-        <v>1.02</v>
+        <v>3.2</v>
       </c>
       <c r="K5" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1643,34 +1643,34 @@
         <v>1.02</v>
       </c>
       <c r="N5" t="n">
-        <v>1.28</v>
+        <v>4.8</v>
       </c>
       <c r="O5" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="P5" t="n">
-        <v>1.28</v>
+        <v>2.22</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.13</v>
+        <v>1.34</v>
       </c>
       <c r="R5" t="n">
-        <v>1.22</v>
+        <v>1.54</v>
       </c>
       <c r="S5" t="n">
-        <v>1.13</v>
+        <v>2.14</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1842,14 +1842,14 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-15 09:31:21</t>
+          <t>2026-06-15 11:39:29</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Georgian Umaglesi Liga</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1864,246 +1864,246 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SC Grobina</t>
+          <t>Dila Gori</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Liepajas Metalurgs</t>
+          <t>FC Spaeri</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.4</v>
+        <v>1.05</v>
       </c>
       <c r="G6" t="n">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>1.83</v>
+        <v>1.06</v>
       </c>
       <c r="I6" t="n">
-        <v>2.12</v>
+        <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>3.4</v>
+        <v>1.06</v>
       </c>
       <c r="K6" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="L6" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P6" t="n">
         <v>1.24</v>
       </c>
-      <c r="P6" t="n">
-        <v>2.08</v>
-      </c>
       <c r="Q6" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="R6" t="n">
-        <v>1.43</v>
+        <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>2.74</v>
+        <v>1.3</v>
       </c>
       <c r="T6" t="n">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.9</v>
+        <v>1.02</v>
       </c>
       <c r="W6" t="n">
-        <v>1.23</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.55</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.15</v>
+        <v>1.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>3.3</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>3.65</v>
+        <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.5</v>
+        <v>1.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.05</v>
+        <v>1.03</v>
       </c>
       <c r="AV6" t="n">
-        <v>3.15</v>
+        <v>1.03</v>
       </c>
       <c r="AW6" t="n">
-        <v>3.55</v>
+        <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>3.8</v>
+        <v>1.03</v>
       </c>
       <c r="AY6" t="n">
-        <v>3.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6" t="n">
-        <v>3.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA6" t="n">
-        <v>3.75</v>
+        <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BP6" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BR6" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BT6" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="BV6" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BX6" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-15 09:31:21</t>
+          <t>2026-06-15 11:39:29</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Lithuanian A Lyga</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,251 +2113,251 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VMFD Zalgiris</t>
+          <t>SC Grobina</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Panevezys</t>
+          <t>Liepajas Metalurgs</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.53</v>
+        <v>3.35</v>
       </c>
       <c r="G7" t="n">
-        <v>1.65</v>
+        <v>5.2</v>
       </c>
       <c r="H7" t="n">
-        <v>5.3</v>
+        <v>1.84</v>
       </c>
       <c r="I7" t="n">
-        <v>8</v>
+        <v>2.1</v>
       </c>
       <c r="J7" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="K7" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="L7" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="M7" t="n">
         <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>3.75</v>
+        <v>1.1</v>
       </c>
       <c r="O7" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P7" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="R7" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S7" t="n">
-        <v>2.66</v>
+        <v>2.3</v>
       </c>
       <c r="T7" t="n">
-        <v>1.82</v>
+        <v>1.65</v>
       </c>
       <c r="U7" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="V7" t="n">
-        <v>1.14</v>
+        <v>1.9</v>
       </c>
       <c r="W7" t="n">
-        <v>2.52</v>
+        <v>1.23</v>
       </c>
       <c r="X7" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>27</v>
+      </c>
+      <c r="AB7" t="n">
         <v>22</v>
       </c>
-      <c r="Y7" t="n">
-        <v>27</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>65</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>210</v>
-      </c>
-      <c r="AB7" t="n">
+      <c r="AC7" t="n">
         <v>11</v>
       </c>
-      <c r="AC7" t="n">
-        <v>12</v>
-      </c>
       <c r="AD7" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="AE7" t="n">
-        <v>110</v>
+        <v>24</v>
       </c>
       <c r="AF7" t="n">
-        <v>11.5</v>
+        <v>40</v>
       </c>
       <c r="AG7" t="n">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="AH7" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AI7" t="n">
-        <v>95</v>
+        <v>38</v>
       </c>
       <c r="AJ7" t="n">
-        <v>17.5</v>
+        <v>100</v>
       </c>
       <c r="AK7" t="n">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="AL7" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="AM7" t="n">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="AN7" t="n">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="AO7" t="n">
-        <v>120</v>
+        <v>14</v>
       </c>
       <c r="AP7" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.8</v>
+        <v>3.35</v>
       </c>
       <c r="AS7" t="n">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="AT7" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AU7" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AW7" t="n">
         <v>3.6</v>
       </c>
-      <c r="AV7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>4.9</v>
-      </c>
       <c r="AX7" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="AY7" t="n">
         <v>3.55</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.9</v>
+        <v>3.8</v>
       </c>
       <c r="BB7" t="n">
         <v>4</v>
       </c>
       <c r="BC7" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BE7" t="n">
         <v>4</v>
       </c>
-      <c r="BD7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>5</v>
-      </c>
       <c r="BF7" t="n">
-        <v>3.3</v>
+        <v>3.95</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.9</v>
+        <v>3.25</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="BJ7" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK7" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BN7" t="n">
-        <v>4.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="BP7" t="n">
-        <v>10.5</v>
+        <v>34</v>
       </c>
       <c r="BQ7" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BR7" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="BS7" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BT7" t="n">
-        <v>10.5</v>
+        <v>5.1</v>
       </c>
       <c r="BU7" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BV7" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BW7" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BX7" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BY7" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-15 09:31:21</t>
+          <t>2026-06-15 11:39:29</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,244 +2367,244 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Varnamo</t>
+          <t>VMFD Zalgiris</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Helsingborgs</t>
+          <t>Panevezys</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="G8" t="n">
-        <v>2.32</v>
+        <v>1.66</v>
       </c>
       <c r="H8" t="n">
-        <v>3.15</v>
+        <v>5.3</v>
       </c>
       <c r="I8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="X8" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>27</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>210</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>19</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX8" t="n">
         <v>3.55</v>
       </c>
-      <c r="J8" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="K8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="X8" t="n">
-        <v>24</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>27</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>36</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>29</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>65</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>13</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>26</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>40</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV8" t="n">
+      <c r="AY8" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ8" t="n">
         <v>11</v>
       </c>
-      <c r="AW8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>28</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>8</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>11</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>9</v>
-      </c>
       <c r="BK8" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BN8" t="n">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="BO8" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BP8" t="n">
-        <v>15.5</v>
+        <v>10.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BR8" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BS8" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BT8" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="CA8" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-15 09:31:21</t>
+          <t>2026-06-15 11:39:29</t>
         </is>
       </c>
     </row>
@@ -2626,246 +2626,246 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Varnamo</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>United IK Nordic</t>
+          <t>Helsingborgs</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.44</v>
+        <v>2.16</v>
       </c>
       <c r="G9" t="n">
-        <v>2.64</v>
+        <v>2.34</v>
       </c>
       <c r="H9" t="n">
-        <v>2.74</v>
+        <v>3.15</v>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="J9" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K9" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M9" t="n">
         <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O9" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P9" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="R9" t="n">
         <v>1.5</v>
       </c>
       <c r="S9" t="n">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="T9" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="U9" t="n">
         <v>2.42</v>
       </c>
       <c r="V9" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W9" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="X9" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Y9" t="n">
         <v>970</v>
       </c>
       <c r="Z9" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>26</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA9" t="n">
         <v>28</v>
       </c>
-      <c r="AA9" t="n">
-        <v>48</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>38</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>970</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>25</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>3.65</v>
-      </c>
       <c r="BB9" t="n">
-        <v>2.72</v>
+        <v>7.6</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.98</v>
+        <v>16.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>2.68</v>
+        <v>23</v>
       </c>
       <c r="BE9" t="n">
-        <v>2.72</v>
+        <v>8.4</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.44</v>
+        <v>11</v>
       </c>
       <c r="BG9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>9</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>11</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BQ9" t="n">
         <v>6.8</v>
       </c>
-      <c r="BH9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BT9" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-15 09:31:21</t>
+          <t>2026-06-15 11:39:29</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,244 +2875,244 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Vikingur Reykjavik</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>KR Reykjavik</t>
+          <t>United IK Nordic</t>
         </is>
       </c>
       <c r="F10" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="X10" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>11</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ10" t="n">
         <v>0</v>
       </c>
-      <c r="G10" t="n">
+      <c r="CA10" t="n">
         <v>0</v>
       </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BX10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BZ10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA10" t="n">
-        <v>1.04</v>
-      </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-15 09:31:21</t>
+          <t>2026-06-15 11:39:29</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>IA Akranes</t>
+          <t>Vikingur Reykjavik</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KR Reykjavik</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -3164,25 +3164,25 @@
         <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N11" t="n">
         <v>1.1</v>
       </c>
       <c r="O11" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="P11" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="R11" t="n">
-        <v>1.56</v>
+        <v>1.97</v>
       </c>
       <c r="S11" t="n">
-        <v>1.56</v>
+        <v>1.31</v>
       </c>
       <c r="T11" t="n">
         <v>1.11</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-15 09:31:21</t>
+          <t>2026-06-15 11:39:29</t>
         </is>
       </c>
     </row>
@@ -3388,12 +3388,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>IA Akranes</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -3418,25 +3418,25 @@
         <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N12" t="n">
         <v>1.1</v>
       </c>
       <c r="O12" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="P12" t="n">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="R12" t="n">
-        <v>1.8</v>
+        <v>1.56</v>
       </c>
       <c r="S12" t="n">
-        <v>1.43</v>
+        <v>1.56</v>
       </c>
       <c r="T12" t="n">
         <v>1.11</v>
@@ -3620,14 +3620,14 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-15 09:31:21</t>
+          <t>2026-06-15 11:39:29</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3637,180 +3637,180 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Fortaleza EC</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>America MG</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="O13" t="n">
-        <v>1.38</v>
+        <v>1.05</v>
       </c>
       <c r="P13" t="n">
-        <v>1.75</v>
+        <v>1.24</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.08</v>
+        <v>1.05</v>
       </c>
       <c r="R13" t="n">
-        <v>1.28</v>
+        <v>1.8</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>1.43</v>
       </c>
       <c r="T13" t="n">
-        <v>2.12</v>
+        <v>1.11</v>
       </c>
       <c r="U13" t="n">
-        <v>1.75</v>
+        <v>1.11</v>
       </c>
       <c r="V13" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>330</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AD13" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AE13" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH13" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI13" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>10.5</v>
+        <v>1.1</v>
       </c>
       <c r="AQ13" t="n">
-        <v>17</v>
+        <v>1.1</v>
       </c>
       <c r="AR13" t="n">
-        <v>8.800000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="AS13" t="n">
-        <v>9.800000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="AT13" t="n">
-        <v>5.9</v>
+        <v>1.1</v>
       </c>
       <c r="AU13" t="n">
-        <v>8</v>
+        <v>1.1</v>
       </c>
       <c r="AV13" t="n">
-        <v>7.6</v>
+        <v>1.1</v>
       </c>
       <c r="AW13" t="n">
-        <v>9.6</v>
+        <v>1.1</v>
       </c>
       <c r="AX13" t="n">
-        <v>7.2</v>
+        <v>1.1</v>
       </c>
       <c r="AY13" t="n">
-        <v>8.6</v>
+        <v>1.1</v>
       </c>
       <c r="AZ13" t="n">
-        <v>7.4</v>
+        <v>1.1</v>
       </c>
       <c r="BA13" t="n">
-        <v>9.6</v>
+        <v>1.1</v>
       </c>
       <c r="BB13" t="n">
-        <v>12.5</v>
+        <v>1.1</v>
       </c>
       <c r="BC13" t="n">
-        <v>16</v>
+        <v>1.1</v>
       </c>
       <c r="BD13" t="n">
-        <v>8.4</v>
+        <v>1.1</v>
       </c>
       <c r="BE13" t="n">
-        <v>9.800000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="BF13" t="n">
-        <v>9.800000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="BG13" t="n">
-        <v>9.800000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="BH13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,261 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-15 09:31:21</t>
+          <t>2026-06-15 11:39:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Fortaleza EC</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>America MG</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="H14" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X14" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>320</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>170</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>230</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>270</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>2026-06-15 11:39:29</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-16.xlsx
@@ -860,55 +860,55 @@
         <v>1.9</v>
       </c>
       <c r="G2" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H2" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="I2" t="n">
         <v>5.2</v>
       </c>
       <c r="J2" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K2" t="n">
-        <v>4.7</v>
+        <v>950</v>
       </c>
       <c r="L2" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M2" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="N2" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="O2" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="P2" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="R2" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="T2" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="U2" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V2" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W2" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="X2" t="n">
         <v>970</v>
@@ -965,64 +965,64 @@
         <v>70</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.55</v>
+        <v>4.4</v>
       </c>
       <c r="AR2" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.92</v>
+        <v>2.76</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.9</v>
+        <v>3.35</v>
       </c>
       <c r="AX2" t="n">
-        <v>2.88</v>
+        <v>4.2</v>
       </c>
       <c r="AY2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE2" t="n">
         <v>2.78</v>
       </c>
-      <c r="AZ2" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1.92</v>
-      </c>
       <c r="BF2" t="n">
-        <v>2.92</v>
+        <v>4.3</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.9</v>
+        <v>3.35</v>
       </c>
       <c r="BH2" t="n">
         <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.82</v>
+        <v>1.01</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-15 11:39:29</t>
+          <t>2026-06-15 13:49:21</t>
         </is>
       </c>
     </row>
@@ -1111,220 +1111,220 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="G3" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="H3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="I3" t="n">
+        <v>10</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="X3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>280</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>140</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>190</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN3" t="n">
         <v>4.1</v>
       </c>
-      <c r="I3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="K3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>1000</v>
-      </c>
       <c r="BO3" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BP3" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BT3" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-15 11:39:29</t>
+          <t>2026-06-15 13:49:21</t>
         </is>
       </c>
     </row>
@@ -1365,25 +1365,25 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="G4" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="H4" t="n">
         <v>2.7</v>
       </c>
       <c r="I4" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="J4" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="K4" t="n">
         <v>4.1</v>
       </c>
       <c r="L4" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="M4" t="n">
         <v>1.05</v>
@@ -1407,16 +1407,16 @@
         <v>2.86</v>
       </c>
       <c r="T4" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="U4" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V4" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="W4" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="X4" t="n">
         <v>22</v>
@@ -1461,7 +1461,7 @@
         <v>32</v>
       </c>
       <c r="AL4" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AM4" t="n">
         <v>90</v>
@@ -1476,7 +1476,7 @@
         <v>13</v>
       </c>
       <c r="AQ4" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AR4" t="n">
         <v>15</v>
@@ -1488,7 +1488,7 @@
         <v>9.4</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AV4" t="n">
         <v>9.6</v>
@@ -1500,16 +1500,16 @@
         <v>13</v>
       </c>
       <c r="AY4" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ4" t="n">
         <v>11.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BB4" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BC4" t="n">
         <v>18.5</v>
@@ -1518,7 +1518,7 @@
         <v>3.85</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BF4" t="n">
         <v>13.5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-15 11:39:29</t>
+          <t>2026-06-15 13:49:21</t>
         </is>
       </c>
     </row>
@@ -1619,175 +1619,175 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="H5" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="I5" t="n">
         <v>1.5</v>
       </c>
       <c r="J5" t="n">
-        <v>3.2</v>
+        <v>4.7</v>
       </c>
       <c r="K5" t="n">
-        <v>10.5</v>
+        <v>5.5</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M5" t="n">
         <v>1.02</v>
       </c>
       <c r="N5" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O5" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="P5" t="n">
-        <v>2.22</v>
+        <v>2.34</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.34</v>
+        <v>1.61</v>
       </c>
       <c r="R5" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="S5" t="n">
-        <v>2.14</v>
+        <v>2.5</v>
       </c>
       <c r="T5" t="n">
-        <v>1.11</v>
+        <v>1.79</v>
       </c>
       <c r="U5" t="n">
-        <v>1.11</v>
+        <v>2.02</v>
       </c>
       <c r="V5" t="n">
         <v>3</v>
       </c>
       <c r="W5" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BH5" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK5" t="n">
         <v>1.01</v>
@@ -1799,7 +1799,7 @@
         <v>1.01</v>
       </c>
       <c r="BN5" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BO5" t="n">
         <v>1.01</v>
@@ -1817,19 +1817,19 @@
         <v>1.01</v>
       </c>
       <c r="BT5" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BV5" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BW5" t="n">
         <v>1.01</v>
       </c>
       <c r="BX5" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BY5" t="n">
         <v>1.01</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-15 11:39:29</t>
+          <t>2026-06-15 13:49:21</t>
         </is>
       </c>
     </row>
@@ -1873,19 +1873,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="G6" t="n">
         <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="I6" t="n">
         <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="K6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-15 11:39:29</t>
+          <t>2026-06-15 13:49:21</t>
         </is>
       </c>
     </row>
@@ -2127,230 +2127,230 @@
         </is>
       </c>
       <c r="F7" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S7" t="n">
         <v>3.35</v>
       </c>
-      <c r="G7" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="I7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.3</v>
-      </c>
       <c r="T7" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="U7" t="n">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="V7" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="W7" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="X7" t="n">
-        <v>23</v>
+        <v>17.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA7" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AB7" t="n">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AD7" t="n">
         <v>13</v>
       </c>
       <c r="AE7" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AF7" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AG7" t="n">
         <v>21</v>
       </c>
       <c r="AH7" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>110</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>70</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX7" t="n">
         <v>21</v>
       </c>
-      <c r="AI7" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>100</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>60</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO7" t="n">
+      <c r="AY7" t="n">
         <v>14</v>
       </c>
-      <c r="AP7" t="n">
+      <c r="AZ7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BH7" t="n">
         <v>3.6</v>
       </c>
-      <c r="AQ7" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>4</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BI7" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="BJ7" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BN7" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BP7" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BR7" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BT7" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BV7" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BX7" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BZ7" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-15 11:39:29</t>
+          <t>2026-06-15 13:49:21</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
         <v>1.53</v>
       </c>
       <c r="G8" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="H8" t="n">
         <v>5.3</v>
@@ -2393,46 +2393,46 @@
         <v>7.4</v>
       </c>
       <c r="J8" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="K8" t="n">
         <v>4.9</v>
       </c>
       <c r="L8" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M8" t="n">
         <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>1.1</v>
+        <v>4.4</v>
       </c>
       <c r="O8" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P8" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="R8" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="S8" t="n">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="T8" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U8" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V8" t="n">
         <v>1.15</v>
       </c>
       <c r="W8" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="X8" t="n">
         <v>22</v>
@@ -2546,55 +2546,55 @@
         <v>3.95</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BJ8" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BN8" t="n">
         <v>4.3</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BP8" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BR8" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BT8" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-15 11:39:29</t>
+          <t>2026-06-15 13:49:21</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G9" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="H9" t="n">
         <v>3.15</v>
       </c>
       <c r="I9" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J9" t="n">
         <v>3.75</v>
       </c>
       <c r="K9" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L9" t="n">
         <v>1.31</v>
@@ -2692,109 +2692,109 @@
         <v>24</v>
       </c>
       <c r="Y9" t="n">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AA9" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AB9" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AC9" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AD9" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AE9" t="n">
         <v>36</v>
       </c>
       <c r="AF9" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH9" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AI9" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AJ9" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO9" t="n">
         <v>29</v>
       </c>
-      <c r="AK9" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>65</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>26</v>
-      </c>
       <c r="AP9" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AQ9" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS9" t="n">
-        <v>40</v>
+        <v>4.8</v>
       </c>
       <c r="AT9" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU9" t="n">
         <v>8</v>
       </c>
       <c r="AV9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW9" t="n">
         <v>26</v>
       </c>
       <c r="AX9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ9" t="n">
         <v>13</v>
       </c>
-      <c r="AY9" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>12</v>
-      </c>
       <c r="BA9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BB9" t="n">
-        <v>7.6</v>
+        <v>21</v>
       </c>
       <c r="BC9" t="n">
-        <v>16.5</v>
+        <v>5.3</v>
       </c>
       <c r="BD9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BE9" t="n">
-        <v>8.4</v>
+        <v>4.8</v>
       </c>
       <c r="BF9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BG9" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BH9" t="n">
         <v>4.1</v>
@@ -2836,7 +2836,7 @@
         <v>7</v>
       </c>
       <c r="BU9" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-15 11:39:29</t>
+          <t>2026-06-15 13:49:21</t>
         </is>
       </c>
     </row>
@@ -2892,22 +2892,22 @@
         <v>2.26</v>
       </c>
       <c r="G10" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="H10" t="n">
         <v>2.98</v>
       </c>
       <c r="I10" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J10" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K10" t="n">
         <v>4.1</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M10" t="n">
         <v>1.05</v>
@@ -2922,7 +2922,7 @@
         <v>2.22</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="R10" t="n">
         <v>1.49</v>
@@ -2931,16 +2931,16 @@
         <v>2.72</v>
       </c>
       <c r="T10" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="U10" t="n">
         <v>2.4</v>
       </c>
       <c r="V10" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W10" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="X10" t="n">
         <v>26</v>
@@ -2949,10 +2949,10 @@
         <v>970</v>
       </c>
       <c r="Z10" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AA10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AB10" t="n">
         <v>17</v>
@@ -2976,19 +2976,19 @@
         <v>970</v>
       </c>
       <c r="AI10" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AJ10" t="n">
         <v>36</v>
       </c>
       <c r="AK10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL10" t="n">
         <v>40</v>
       </c>
       <c r="AM10" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AN10" t="n">
         <v>17</v>
@@ -2997,112 +2997,112 @@
         <v>27</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.62</v>
+        <v>5.2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>2.82</v>
+        <v>4.9</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="AS10" t="n">
-        <v>3.1</v>
+        <v>4.9</v>
       </c>
       <c r="AT10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AZ10" t="n">
         <v>4.9</v>
       </c>
-      <c r="AU10" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>2.56</v>
-      </c>
       <c r="BA10" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="BC10" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>2.66</v>
+        <v>5.3</v>
       </c>
       <c r="BE10" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="BF10" t="n">
         <v>11</v>
       </c>
       <c r="BG10" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="BH10" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BJ10" t="n">
         <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="BN10" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="BT10" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-15 11:39:29</t>
+          <t>2026-06-15 13:49:21</t>
         </is>
       </c>
     </row>
@@ -3251,58 +3251,58 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="BH11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-15 11:39:29</t>
+          <t>2026-06-15 13:49:21</t>
         </is>
       </c>
     </row>
@@ -3505,58 +3505,58 @@
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="BH12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-15 11:39:29</t>
+          <t>2026-06-15 13:49:21</t>
         </is>
       </c>
     </row>
@@ -3759,58 +3759,58 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="BH13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-15 11:39:29</t>
+          <t>2026-06-15 13:49:21</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="G14" t="n">
         <v>1.66</v>
@@ -3917,7 +3917,7 @@
         <v>7.8</v>
       </c>
       <c r="J14" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K14" t="n">
         <v>4.3</v>
@@ -3929,31 +3929,31 @@
         <v>1.08</v>
       </c>
       <c r="N14" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O14" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="P14" t="n">
         <v>1.74</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="R14" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
       </c>
       <c r="T14" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="U14" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="V14" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W14" t="n">
         <v>2.5</v>
@@ -3962,13 +3962,13 @@
         <v>13</v>
       </c>
       <c r="Y14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z14" t="n">
         <v>65</v>
       </c>
       <c r="AA14" t="n">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="AB14" t="n">
         <v>7</v>
@@ -4019,10 +4019,10 @@
         <v>17</v>
       </c>
       <c r="AR14" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AS14" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT14" t="n">
         <v>5.9</v>
@@ -4031,22 +4031,22 @@
         <v>8</v>
       </c>
       <c r="AV14" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AW14" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AX14" t="n">
         <v>7.2</v>
       </c>
       <c r="AY14" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ14" t="n">
         <v>7.6</v>
       </c>
       <c r="BA14" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BB14" t="n">
         <v>12.5</v>
@@ -4055,16 +4055,16 @@
         <v>16</v>
       </c>
       <c r="BD14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BE14" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BF14" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BG14" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BH14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-15 11:39:29</t>
+          <t>2026-06-15 13:49:21</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-16.xlsx
@@ -857,40 +857,40 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="G2" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="H2" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="I2" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="J2" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K2" t="n">
-        <v>950</v>
+        <v>4.7</v>
       </c>
       <c r="L2" t="n">
         <v>1.4</v>
       </c>
       <c r="M2" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="O2" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="P2" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R2" t="n">
         <v>1.28</v>
@@ -899,16 +899,16 @@
         <v>2.86</v>
       </c>
       <c r="T2" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U2" t="n">
         <v>2.04</v>
       </c>
       <c r="V2" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W2" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="X2" t="n">
         <v>970</v>
@@ -965,58 +965,58 @@
         <v>70</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AR2" t="n">
-        <v>3.2</v>
+        <v>2.72</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AW2" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="AX2" t="n">
         <v>4.2</v>
       </c>
       <c r="AY2" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BA2" t="n">
-        <v>3.35</v>
+        <v>2.84</v>
       </c>
       <c r="BB2" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.9</v>
+        <v>3.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="BF2" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.35</v>
+        <v>2.84</v>
       </c>
       <c r="BH2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-15 13:49:21</t>
+          <t>2026-06-15 15:58:37</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="G3" t="n">
         <v>1.74</v>
@@ -1120,10 +1120,10 @@
         <v>5.7</v>
       </c>
       <c r="I3" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="J3" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K3" t="n">
         <v>6.4</v>
@@ -1135,25 +1135,25 @@
         <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O3" t="n">
         <v>1.3</v>
       </c>
       <c r="P3" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="R3" t="n">
         <v>1.36</v>
       </c>
       <c r="S3" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="T3" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U3" t="n">
         <v>1.86</v>
@@ -1162,25 +1162,25 @@
         <v>1.11</v>
       </c>
       <c r="W3" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="X3" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Z3" t="n">
         <v>75</v>
       </c>
       <c r="AA3" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD3" t="n">
         <v>34</v>
@@ -1225,34 +1225,34 @@
         <v>16.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AT3" t="n">
         <v>6</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.25</v>
+        <v>7.2</v>
       </c>
       <c r="AV3" t="n">
         <v>20</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AX3" t="n">
         <v>7.8</v>
       </c>
       <c r="AY3" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BB3" t="n">
         <v>10.5</v>
@@ -1261,22 +1261,22 @@
         <v>12.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BJ3" t="n">
         <v>11.5</v>
@@ -1300,7 +1300,7 @@
         <v>10.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-15 13:49:21</t>
+          <t>2026-06-15 15:58:37</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G4" t="n">
         <v>2.74</v>
@@ -1374,10 +1374,10 @@
         <v>2.7</v>
       </c>
       <c r="I4" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K4" t="n">
         <v>4.1</v>
@@ -1413,7 +1413,7 @@
         <v>2.3</v>
       </c>
       <c r="V4" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W4" t="n">
         <v>1.57</v>
@@ -1422,7 +1422,7 @@
         <v>22</v>
       </c>
       <c r="Y4" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z4" t="n">
         <v>26</v>
@@ -1443,13 +1443,13 @@
         <v>38</v>
       </c>
       <c r="AF4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG4" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AH4" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI4" t="n">
         <v>46</v>
@@ -1461,7 +1461,7 @@
         <v>32</v>
       </c>
       <c r="AL4" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AM4" t="n">
         <v>90</v>
@@ -1482,10 +1482,10 @@
         <v>15</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AT4" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AU4" t="n">
         <v>7.4</v>
@@ -1500,7 +1500,7 @@
         <v>13</v>
       </c>
       <c r="AY4" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ4" t="n">
         <v>11.5</v>
@@ -1512,16 +1512,16 @@
         <v>3.85</v>
       </c>
       <c r="BC4" t="n">
-        <v>18.5</v>
+        <v>3.7</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BE4" t="n">
         <v>4</v>
       </c>
       <c r="BF4" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BG4" t="n">
         <v>16.5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-15 13:49:21</t>
+          <t>2026-06-15 15:58:37</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
         <v>7</v>
       </c>
       <c r="G5" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="H5" t="n">
         <v>1.45</v>
@@ -1631,7 +1631,7 @@
         <v>1.5</v>
       </c>
       <c r="J5" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K5" t="n">
         <v>5.5</v>
@@ -1670,7 +1670,7 @@
         <v>3</v>
       </c>
       <c r="W5" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X5" t="n">
         <v>28</v>
@@ -1790,31 +1790,31 @@
         <v>11</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BN5" t="n">
         <v>11.5</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BT5" t="n">
         <v>4.3</v>
@@ -1826,13 +1826,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BX5" t="n">
         <v>23</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-15 13:49:21</t>
+          <t>2026-06-15 15:58:37</t>
         </is>
       </c>
     </row>
@@ -1885,7 +1885,7 @@
         <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="K6" t="n">
         <v>1000</v>
@@ -1915,10 +1915,10 @@
         <v>1.3</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V6" t="n">
         <v>1.02</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-15 13:49:21</t>
+          <t>2026-06-15 15:58:37</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2133,7 @@
         <v>4.3</v>
       </c>
       <c r="H7" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="I7" t="n">
         <v>2.12</v>
@@ -2157,10 +2157,10 @@
         <v>1.31</v>
       </c>
       <c r="P7" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="R7" t="n">
         <v>1.34</v>
@@ -2169,16 +2169,16 @@
         <v>3.35</v>
       </c>
       <c r="T7" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="U7" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V7" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="W7" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="X7" t="n">
         <v>17.5</v>
@@ -2292,7 +2292,7 @@
         <v>3.6</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="BJ7" t="n">
         <v>10</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-15 13:49:21</t>
+          <t>2026-06-15 15:58:37</t>
         </is>
       </c>
     </row>
@@ -2381,25 +2381,25 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="G8" t="n">
         <v>1.65</v>
       </c>
       <c r="H8" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="I8" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J8" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="K8" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L8" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="M8" t="n">
         <v>1.05</v>
@@ -2429,22 +2429,22 @@
         <v>2.04</v>
       </c>
       <c r="V8" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W8" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="X8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
         <v>65</v>
       </c>
       <c r="AA8" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AB8" t="n">
         <v>11</v>
@@ -2453,94 +2453,94 @@
         <v>12</v>
       </c>
       <c r="AD8" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AE8" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AF8" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG8" t="n">
         <v>11.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI8" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AJ8" t="n">
         <v>17.5</v>
       </c>
       <c r="AK8" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL8" t="n">
         <v>38</v>
       </c>
       <c r="AM8" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN8" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO8" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP8" t="n">
-        <v>4.2</v>
+        <v>15</v>
       </c>
       <c r="AQ8" t="n">
-        <v>4.3</v>
+        <v>18</v>
       </c>
       <c r="AR8" t="n">
         <v>4.8</v>
       </c>
       <c r="AS8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AW8" t="n">
         <v>5</v>
       </c>
-      <c r="AT8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>4.9</v>
-      </c>
       <c r="AX8" t="n">
-        <v>3.55</v>
+        <v>8</v>
       </c>
       <c r="AY8" t="n">
-        <v>3.55</v>
+        <v>7.8</v>
       </c>
       <c r="AZ8" t="n">
-        <v>4.3</v>
+        <v>16</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BB8" t="n">
-        <v>4</v>
+        <v>11.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BE8" t="n">
         <v>5</v>
       </c>
       <c r="BF8" t="n">
-        <v>3.3</v>
+        <v>6</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BH8" t="n">
         <v>3.95</v>
@@ -2558,7 +2558,7 @@
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="BN8" t="n">
         <v>4.3</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-15 13:49:21</t>
+          <t>2026-06-15 15:58:37</t>
         </is>
       </c>
     </row>
@@ -2641,7 +2641,7 @@
         <v>2.32</v>
       </c>
       <c r="H9" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I9" t="n">
         <v>3.5</v>
@@ -2650,16 +2650,16 @@
         <v>3.75</v>
       </c>
       <c r="K9" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="M9" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N9" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O9" t="n">
         <v>1.22</v>
@@ -2668,10 +2668,10 @@
         <v>2.32</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="S9" t="n">
         <v>2.62</v>
@@ -2680,7 +2680,7 @@
         <v>1.59</v>
       </c>
       <c r="U9" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="V9" t="n">
         <v>1.4</v>
@@ -2695,22 +2695,22 @@
         <v>19.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AA9" t="n">
         <v>65</v>
       </c>
       <c r="AB9" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD9" t="n">
         <v>16.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AF9" t="n">
         <v>19.5</v>
@@ -2719,10 +2719,10 @@
         <v>13</v>
       </c>
       <c r="AH9" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AJ9" t="n">
         <v>34</v>
@@ -2731,7 +2731,7 @@
         <v>25</v>
       </c>
       <c r="AL9" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AM9" t="n">
         <v>75</v>
@@ -2740,34 +2740,34 @@
         <v>15</v>
       </c>
       <c r="AO9" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AP9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ9" t="n">
         <v>14.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AT9" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV9" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AX9" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AY9" t="n">
         <v>9.800000000000001</v>
@@ -2776,37 +2776,37 @@
         <v>13</v>
       </c>
       <c r="BA9" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BB9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>11</v>
+      </c>
+      <c r="BG9" t="n">
         <v>21</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>22</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>10</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>19.5</v>
       </c>
       <c r="BH9" t="n">
         <v>4.1</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="BJ9" t="n">
         <v>9</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
@@ -2824,7 +2824,7 @@
         <v>15.5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
@@ -2842,23 +2842,23 @@
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ9" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="CA9" t="n">
         <v>7.6</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-15 13:49:21</t>
+          <t>2026-06-15 15:58:37</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="G10" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="H10" t="n">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="I10" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J10" t="n">
         <v>3.7</v>
       </c>
       <c r="K10" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L10" t="n">
         <v>1.29</v>
@@ -2922,7 +2922,7 @@
         <v>2.22</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R10" t="n">
         <v>1.49</v>
@@ -2934,7 +2934,7 @@
         <v>1.6</v>
       </c>
       <c r="U10" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V10" t="n">
         <v>1.44</v>
@@ -2949,10 +2949,10 @@
         <v>970</v>
       </c>
       <c r="Z10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB10" t="n">
         <v>17</v>
@@ -2988,22 +2988,22 @@
         <v>40</v>
       </c>
       <c r="AM10" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN10" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AO10" t="n">
         <v>27</v>
       </c>
       <c r="AP10" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AR10" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AS10" t="n">
         <v>4.9</v>
@@ -3018,28 +3018,28 @@
         <v>10.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AX10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AZ10" t="n">
         <v>5.1</v>
       </c>
-      <c r="AY10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BA10" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB10" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BC10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BD10" t="n">
         <v>5.5</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>5.3</v>
       </c>
       <c r="BE10" t="n">
         <v>4</v>
@@ -3048,7 +3048,7 @@
         <v>11</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BH10" t="n">
         <v>4</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-15 13:49:21</t>
+          <t>2026-06-15 15:58:37</t>
         </is>
       </c>
     </row>
@@ -3167,13 +3167,13 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="O11" t="n">
         <v>1.04</v>
       </c>
       <c r="P11" t="n">
-        <v>1.25</v>
+        <v>1.98</v>
       </c>
       <c r="Q11" t="n">
         <v>1.04</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-15 13:49:21</t>
+          <t>2026-06-15 15:58:37</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-15 13:49:21</t>
+          <t>2026-06-15 15:58:37</t>
         </is>
       </c>
     </row>
@@ -3681,13 +3681,13 @@
         <v>1.05</v>
       </c>
       <c r="P13" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q13" t="n">
         <v>1.05</v>
       </c>
       <c r="R13" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="S13" t="n">
         <v>1.43</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-15 13:49:21</t>
+          <t>2026-06-15 15:58:37</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="G14" t="n">
         <v>1.66</v>
@@ -3914,13 +3914,13 @@
         <v>6.8</v>
       </c>
       <c r="I14" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J14" t="n">
         <v>3.85</v>
       </c>
       <c r="K14" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
@@ -3929,7 +3929,7 @@
         <v>1.08</v>
       </c>
       <c r="N14" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O14" t="n">
         <v>1.4</v>
@@ -3941,19 +3941,19 @@
         <v>2.16</v>
       </c>
       <c r="R14" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
       </c>
       <c r="T14" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="U14" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="V14" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W14" t="n">
         <v>2.5</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-15 13:49:21</t>
+          <t>2026-06-15 15:58:37</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-16.xlsx
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="G2" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="H2" t="n">
         <v>3.8</v>
@@ -899,16 +899,16 @@
         <v>2.86</v>
       </c>
       <c r="T2" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U2" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="V2" t="n">
         <v>1.27</v>
       </c>
       <c r="W2" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="X2" t="n">
         <v>970</v>
@@ -983,10 +983,10 @@
         <v>3.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="AW2" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="AX2" t="n">
         <v>4.2</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-15 15:58:37</t>
+          <t>2026-06-15 18:07:21</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="G3" t="n">
         <v>1.74</v>
@@ -1126,7 +1126,7 @@
         <v>3.15</v>
       </c>
       <c r="K3" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -1138,7 +1138,7 @@
         <v>3.5</v>
       </c>
       <c r="O3" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P3" t="n">
         <v>1.9</v>
@@ -1270,13 +1270,13 @@
         <v>7</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BH3" t="n">
         <v>3.6</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="BJ3" t="n">
         <v>11.5</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-15 15:58:37</t>
+          <t>2026-06-15 18:07:21</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
         <v>2.74</v>
       </c>
       <c r="H4" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="I4" t="n">
         <v>3.1</v>
@@ -1398,7 +1398,7 @@
         <v>2.08</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R4" t="n">
         <v>1.43</v>
@@ -1407,7 +1407,7 @@
         <v>2.86</v>
       </c>
       <c r="T4" t="n">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="U4" t="n">
         <v>2.3</v>
@@ -1440,13 +1440,13 @@
         <v>16</v>
       </c>
       <c r="AE4" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AF4" t="n">
         <v>23</v>
       </c>
       <c r="AG4" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH4" t="n">
         <v>19</v>
@@ -1461,7 +1461,7 @@
         <v>32</v>
       </c>
       <c r="AL4" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AM4" t="n">
         <v>90</v>
@@ -1482,7 +1482,7 @@
         <v>15</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.9</v>
+        <v>32</v>
       </c>
       <c r="AT4" t="n">
         <v>10.5</v>
@@ -1500,28 +1500,28 @@
         <v>13</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AZ4" t="n">
         <v>11.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BB4" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.7</v>
+        <v>19</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BE4" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BF4" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG4" t="n">
         <v>16.5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-15 15:58:37</t>
+          <t>2026-06-15 18:07:21</t>
         </is>
       </c>
     </row>
@@ -1622,16 +1622,16 @@
         <v>7</v>
       </c>
       <c r="G5" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="H5" t="n">
         <v>1.45</v>
       </c>
       <c r="I5" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="J5" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="K5" t="n">
         <v>5.5</v>
@@ -1643,13 +1643,13 @@
         <v>1.02</v>
       </c>
       <c r="N5" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O5" t="n">
         <v>1.2</v>
       </c>
       <c r="P5" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="Q5" t="n">
         <v>1.61</v>
@@ -1658,19 +1658,19 @@
         <v>1.53</v>
       </c>
       <c r="S5" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="T5" t="n">
         <v>1.79</v>
       </c>
       <c r="U5" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V5" t="n">
         <v>3</v>
       </c>
       <c r="W5" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X5" t="n">
         <v>28</v>
@@ -1730,7 +1730,7 @@
         <v>17</v>
       </c>
       <c r="AQ5" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR5" t="n">
         <v>7.4</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-15 15:58:37</t>
+          <t>2026-06-15 18:07:21</t>
         </is>
       </c>
     </row>
@@ -1885,7 +1885,7 @@
         <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="K6" t="n">
         <v>1000</v>
@@ -2029,10 +2029,10 @@
         <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BH6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-15 15:58:37</t>
+          <t>2026-06-15 18:07:21</t>
         </is>
       </c>
     </row>
@@ -2175,7 +2175,7 @@
         <v>2.06</v>
       </c>
       <c r="V7" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="W7" t="n">
         <v>1.31</v>
@@ -2310,7 +2310,7 @@
         <v>7.8</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="BP7" t="n">
         <v>36</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-15 15:58:37</t>
+          <t>2026-06-15 18:07:21</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
         <v>1.55</v>
       </c>
       <c r="G8" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="H8" t="n">
         <v>6</v>
@@ -2396,7 +2396,7 @@
         <v>4.3</v>
       </c>
       <c r="K8" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L8" t="n">
         <v>1.29</v>
@@ -2405,34 +2405,34 @@
         <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="O8" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P8" t="n">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="R8" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="S8" t="n">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="T8" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="U8" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="V8" t="n">
         <v>1.16</v>
       </c>
       <c r="W8" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="X8" t="n">
         <v>23</v>
@@ -2441,22 +2441,22 @@
         <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA8" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AB8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC8" t="n">
         <v>11</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>12</v>
       </c>
       <c r="AD8" t="n">
         <v>28</v>
       </c>
       <c r="AE8" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AF8" t="n">
         <v>12</v>
@@ -2465,28 +2465,28 @@
         <v>11.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI8" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ8" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK8" t="n">
         <v>17.5</v>
       </c>
-      <c r="AK8" t="n">
-        <v>18.5</v>
-      </c>
       <c r="AL8" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM8" t="n">
         <v>120</v>
       </c>
       <c r="AN8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO8" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AP8" t="n">
         <v>15</v>
@@ -2495,25 +2495,25 @@
         <v>18</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="AT8" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU8" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AV8" t="n">
         <v>18.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AX8" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AY8" t="n">
         <v>7.8</v>
@@ -2522,7 +2522,7 @@
         <v>16</v>
       </c>
       <c r="BA8" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BB8" t="n">
         <v>11.5</v>
@@ -2531,19 +2531,19 @@
         <v>12</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BE8" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BF8" t="n">
         <v>6</v>
       </c>
       <c r="BG8" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BI8" t="n">
         <v>3.2</v>
@@ -2570,7 +2570,7 @@
         <v>10</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
@@ -2582,19 +2582,19 @@
         <v>10</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-15 15:58:37</t>
+          <t>2026-06-15 18:07:21</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
         <v>2.18</v>
       </c>
       <c r="G9" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="H9" t="n">
         <v>3.2</v>
@@ -2707,7 +2707,7 @@
         <v>10.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AE9" t="n">
         <v>40</v>
@@ -2731,10 +2731,10 @@
         <v>25</v>
       </c>
       <c r="AL9" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM9" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AN9" t="n">
         <v>15</v>
@@ -2752,7 +2752,7 @@
         <v>18.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AT9" t="n">
         <v>11.5</v>
@@ -2776,19 +2776,19 @@
         <v>13</v>
       </c>
       <c r="BA9" t="n">
-        <v>32</v>
+        <v>5.3</v>
       </c>
       <c r="BB9" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BC9" t="n">
         <v>15.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BE9" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BF9" t="n">
         <v>11</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-15 15:58:37</t>
+          <t>2026-06-15 18:07:21</t>
         </is>
       </c>
     </row>
@@ -2889,28 +2889,28 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G10" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="H10" t="n">
         <v>2.92</v>
       </c>
       <c r="I10" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="J10" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K10" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L10" t="n">
         <v>1.29</v>
       </c>
       <c r="M10" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N10" t="n">
         <v>4.6</v>
@@ -2919,31 +2919,31 @@
         <v>1.23</v>
       </c>
       <c r="P10" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="R10" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S10" t="n">
         <v>2.72</v>
       </c>
       <c r="T10" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="U10" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="V10" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W10" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="X10" t="n">
-        <v>26</v>
+        <v>90</v>
       </c>
       <c r="Y10" t="n">
         <v>970</v>
@@ -2964,10 +2964,10 @@
         <v>970</v>
       </c>
       <c r="AE10" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="AF10" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="AG10" t="n">
         <v>970</v>
@@ -2976,7 +2976,7 @@
         <v>970</v>
       </c>
       <c r="AI10" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AJ10" t="n">
         <v>36</v>
@@ -2985,7 +2985,7 @@
         <v>27</v>
       </c>
       <c r="AL10" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AM10" t="n">
         <v>75</v>
@@ -2994,19 +2994,19 @@
         <v>970</v>
       </c>
       <c r="AO10" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AP10" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AQ10" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AR10" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="AT10" t="n">
         <v>9.800000000000001</v>
@@ -3018,37 +3018,37 @@
         <v>10.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AX10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AZ10" t="n">
         <v>5.4</v>
       </c>
-      <c r="AY10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BA10" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.6</v>
+        <v>4.7</v>
       </c>
       <c r="BC10" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BD10" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="BE10" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BF10" t="n">
         <v>11</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BH10" t="n">
         <v>4</v>
@@ -3066,10 +3066,10 @@
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.8</v>
+        <v>1.17</v>
       </c>
       <c r="BN10" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BO10" t="n">
         <v>4.8</v>
@@ -3078,13 +3078,13 @@
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.81</v>
+        <v>1.56</v>
       </c>
       <c r="BT10" t="n">
         <v>11.5</v>
@@ -3096,13 +3096,13 @@
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.84</v>
+        <v>1.17</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-15 15:58:37</t>
+          <t>2026-06-15 18:07:21</t>
         </is>
       </c>
     </row>
@@ -3143,43 +3143,43 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="M11" t="n">
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="O11" t="n">
         <v>1.04</v>
       </c>
       <c r="P11" t="n">
-        <v>1.98</v>
+        <v>2.5</v>
       </c>
       <c r="Q11" t="n">
         <v>1.04</v>
       </c>
       <c r="R11" t="n">
-        <v>1.97</v>
+        <v>2.5</v>
       </c>
       <c r="S11" t="n">
         <v>1.31</v>
@@ -3191,10 +3191,10 @@
         <v>1.11</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -3305,68 +3305,68 @@
         <v>1.01</v>
       </c>
       <c r="BH11" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN11" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BP11" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BR11" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BT11" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-15 15:58:37</t>
+          <t>2026-06-15 18:07:21</t>
         </is>
       </c>
     </row>
@@ -3397,22 +3397,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -3421,22 +3421,22 @@
         <v>1.02</v>
       </c>
       <c r="N12" t="n">
-        <v>1.1</v>
+        <v>3.05</v>
       </c>
       <c r="O12" t="n">
         <v>1.09</v>
       </c>
       <c r="P12" t="n">
-        <v>1.07</v>
+        <v>3.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.09</v>
+        <v>1.35</v>
       </c>
       <c r="R12" t="n">
-        <v>1.56</v>
+        <v>1.9</v>
       </c>
       <c r="S12" t="n">
-        <v>1.56</v>
+        <v>1.87</v>
       </c>
       <c r="T12" t="n">
         <v>1.11</v>
@@ -3445,10 +3445,10 @@
         <v>1.11</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-15 15:58:37</t>
+          <t>2026-06-15 18:07:21</t>
         </is>
       </c>
     </row>
@@ -3651,230 +3651,230 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="M13" t="n">
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="P13" t="n">
-        <v>1.25</v>
+        <v>3.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
       <c r="R13" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="S13" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="W13" t="n">
         <v>1.43</v>
       </c>
-      <c r="T13" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.01</v>
-      </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BH13" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BJ13" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK13" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN13" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BP13" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BQ13" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BR13" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BS13" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BT13" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU13" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BV13" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX13" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="CA13" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-15 15:58:37</t>
+          <t>2026-06-15 18:07:21</t>
         </is>
       </c>
     </row>
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="G14" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="H14" t="n">
         <v>6.8</v>
@@ -3917,19 +3917,19 @@
         <v>7.6</v>
       </c>
       <c r="J14" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K14" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N14" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O14" t="n">
         <v>1.4</v>
@@ -3941,7 +3941,7 @@
         <v>2.16</v>
       </c>
       <c r="R14" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -3956,10 +3956,10 @@
         <v>1.15</v>
       </c>
       <c r="W14" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="X14" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y14" t="n">
         <v>20</v>
@@ -3974,7 +3974,7 @@
         <v>7</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD14" t="n">
         <v>950</v>
@@ -4016,25 +4016,25 @@
         <v>10.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR14" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AS14" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT14" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AU14" t="n">
         <v>8</v>
       </c>
       <c r="AV14" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AW14" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AX14" t="n">
         <v>7.2</v>
@@ -4043,10 +4043,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ14" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BA14" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BB14" t="n">
         <v>12.5</v>
@@ -4055,16 +4055,16 @@
         <v>16</v>
       </c>
       <c r="BD14" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE14" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BF14" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BG14" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BH14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-15 15:58:37</t>
+          <t>2026-06-15 18:07:21</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-16.xlsx
@@ -857,40 +857,40 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="G2" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="H2" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="I2" t="n">
         <v>4.7</v>
       </c>
       <c r="J2" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="K2" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="L2" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M2" t="n">
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O2" t="n">
         <v>1.3</v>
       </c>
       <c r="P2" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="R2" t="n">
         <v>1.28</v>
@@ -908,115 +908,115 @@
         <v>1.27</v>
       </c>
       <c r="W2" t="n">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="X2" t="n">
-        <v>970</v>
+        <v>27</v>
       </c>
       <c r="Y2" t="n">
         <v>970</v>
       </c>
       <c r="Z2" t="n">
-        <v>38</v>
+        <v>500</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB2" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AC2" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AD2" t="n">
         <v>970</v>
       </c>
       <c r="AE2" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>500</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>500</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>500</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK2" t="n">
         <v>65</v>
       </c>
-      <c r="AF2" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>28</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>25</v>
-      </c>
       <c r="AL2" t="n">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN2" t="n">
-        <v>970</v>
+        <v>55</v>
       </c>
       <c r="AO2" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.6</v>
+        <v>5.9</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.72</v>
+        <v>3.15</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AT2" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="AU2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BF2" t="n">
         <v>3.8</v>
       </c>
-      <c r="AV2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BG2" t="n">
-        <v>2.84</v>
+        <v>4.8</v>
       </c>
       <c r="BH2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-15 18:07:21</t>
+          <t>2026-06-15 20:15:46</t>
         </is>
       </c>
     </row>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="G3" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="H3" t="n">
         <v>5.7</v>
@@ -1123,10 +1123,10 @@
         <v>9.6</v>
       </c>
       <c r="J3" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="K3" t="n">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -1156,7 +1156,7 @@
         <v>1.96</v>
       </c>
       <c r="U3" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="V3" t="n">
         <v>1.11</v>
@@ -1171,7 +1171,7 @@
         <v>27</v>
       </c>
       <c r="Z3" t="n">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AA3" t="n">
         <v>270</v>
@@ -1183,7 +1183,7 @@
         <v>11.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AE3" t="n">
         <v>140</v>
@@ -1195,7 +1195,7 @@
         <v>12</v>
       </c>
       <c r="AH3" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="AI3" t="n">
         <v>130</v>
@@ -1207,7 +1207,7 @@
         <v>21</v>
       </c>
       <c r="AL3" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AM3" t="n">
         <v>170</v>
@@ -1261,10 +1261,10 @@
         <v>12.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BF3" t="n">
         <v>7</v>
@@ -1276,7 +1276,7 @@
         <v>3.6</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="BJ3" t="n">
         <v>11.5</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-15 18:07:21</t>
+          <t>2026-06-15 20:15:46</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
         <v>2.42</v>
       </c>
       <c r="G4" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="H4" t="n">
         <v>2.72</v>
@@ -1377,10 +1377,10 @@
         <v>3.1</v>
       </c>
       <c r="J4" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="K4" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L4" t="n">
         <v>1.29</v>
@@ -1416,7 +1416,7 @@
         <v>1.47</v>
       </c>
       <c r="W4" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="X4" t="n">
         <v>22</v>
@@ -1443,31 +1443,31 @@
         <v>34</v>
       </c>
       <c r="AF4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG4" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AH4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AI4" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AJ4" t="n">
         <v>44</v>
       </c>
       <c r="AK4" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AL4" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM4" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AN4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO4" t="n">
         <v>28</v>
@@ -1482,7 +1482,7 @@
         <v>15</v>
       </c>
       <c r="AS4" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AT4" t="n">
         <v>10.5</v>
@@ -1506,19 +1506,19 @@
         <v>11.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="BB4" t="n">
-        <v>3.95</v>
+        <v>14.5</v>
       </c>
       <c r="BC4" t="n">
         <v>19</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.9</v>
+        <v>16</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BF4" t="n">
         <v>13.5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-15 18:07:21</t>
+          <t>2026-06-15 20:15:46</t>
         </is>
       </c>
     </row>
@@ -1619,13 +1619,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="G5" t="n">
         <v>8.4</v>
       </c>
       <c r="H5" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="I5" t="n">
         <v>1.49</v>
@@ -1634,7 +1634,7 @@
         <v>4.7</v>
       </c>
       <c r="K5" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="L5" t="n">
         <v>1.25</v>
@@ -1643,28 +1643,28 @@
         <v>1.02</v>
       </c>
       <c r="N5" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="O5" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P5" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="R5" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="S5" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="T5" t="n">
         <v>1.79</v>
       </c>
       <c r="U5" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V5" t="n">
         <v>3</v>
@@ -1685,10 +1685,10 @@
         <v>15.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AC5" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AD5" t="n">
         <v>11</v>
@@ -1697,31 +1697,31 @@
         <v>18</v>
       </c>
       <c r="AF5" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AG5" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AH5" t="n">
         <v>27</v>
       </c>
       <c r="AI5" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AJ5" t="n">
         <v>250</v>
       </c>
       <c r="AK5" t="n">
+        <v>260</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>230</v>
+      </c>
+      <c r="AM5" t="n">
         <v>120</v>
       </c>
-      <c r="AL5" t="n">
-        <v>100</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>130</v>
-      </c>
       <c r="AN5" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AO5" t="n">
         <v>6.8</v>
@@ -1733,7 +1733,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AR5" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AS5" t="n">
         <v>9.800000000000001</v>
@@ -1751,7 +1751,7 @@
         <v>10.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="AY5" t="n">
         <v>20</v>
@@ -1760,79 +1760,79 @@
         <v>16.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BH5" t="n">
         <v>4.4</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BJ5" t="n">
         <v>11</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BN5" t="n">
         <v>11.5</v>
       </c>
       <c r="BO5" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT5" t="n">
         <v>4.3</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BV5" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BW5" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BX5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BY5" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-15 18:07:21</t>
+          <t>2026-06-15 20:15:46</t>
         </is>
       </c>
     </row>
@@ -1873,37 +1873,37 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.09</v>
+        <v>1.6</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>2.72</v>
       </c>
       <c r="H6" t="n">
-        <v>1.09</v>
+        <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="J6" t="n">
-        <v>1.19</v>
+        <v>3.1</v>
       </c>
       <c r="K6" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="O6" t="n">
         <v>1.3</v>
       </c>
       <c r="P6" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Q6" t="n">
         <v>1.3</v>
@@ -1912,7 +1912,7 @@
         <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T6" t="n">
         <v>1.11</v>
@@ -1921,118 +1921,118 @@
         <v>1.11</v>
       </c>
       <c r="V6" t="n">
-        <v>1.02</v>
+        <v>1.18</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1.7</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.07</v>
+        <v>1.55</v>
       </c>
       <c r="BH6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-15 18:07:21</t>
+          <t>2026-06-15 20:15:46</t>
         </is>
       </c>
     </row>
@@ -2127,16 +2127,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="G7" t="n">
         <v>4.3</v>
       </c>
       <c r="H7" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="I7" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="J7" t="n">
         <v>3.75</v>
@@ -2169,16 +2169,16 @@
         <v>3.35</v>
       </c>
       <c r="T7" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="U7" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V7" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="W7" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="X7" t="n">
         <v>17.5</v>
@@ -2190,7 +2190,7 @@
         <v>15</v>
       </c>
       <c r="AA7" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AB7" t="n">
         <v>17.5</v>
@@ -2202,7 +2202,7 @@
         <v>13</v>
       </c>
       <c r="AE7" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AF7" t="n">
         <v>36</v>
@@ -2223,13 +2223,13 @@
         <v>65</v>
       </c>
       <c r="AL7" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AM7" t="n">
-        <v>130</v>
+        <v>580</v>
       </c>
       <c r="AN7" t="n">
-        <v>70</v>
+        <v>240</v>
       </c>
       <c r="AO7" t="n">
         <v>18</v>
@@ -2268,22 +2268,22 @@
         <v>16.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BG7" t="n">
         <v>11.5</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-15 18:07:21</t>
+          <t>2026-06-15 20:15:46</t>
         </is>
       </c>
     </row>
@@ -2384,13 +2384,13 @@
         <v>1.55</v>
       </c>
       <c r="G8" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="H8" t="n">
         <v>6</v>
       </c>
       <c r="I8" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J8" t="n">
         <v>4.3</v>
@@ -2414,7 +2414,7 @@
         <v>2.32</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="R8" t="n">
         <v>1.51</v>
@@ -2441,10 +2441,10 @@
         <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>60</v>
+        <v>220</v>
       </c>
       <c r="AA8" t="n">
-        <v>190</v>
+        <v>700</v>
       </c>
       <c r="AB8" t="n">
         <v>12</v>
@@ -2453,22 +2453,22 @@
         <v>11</v>
       </c>
       <c r="AD8" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="AE8" t="n">
-        <v>95</v>
+        <v>400</v>
       </c>
       <c r="AF8" t="n">
         <v>12</v>
       </c>
       <c r="AG8" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>85</v>
+        <v>700</v>
       </c>
       <c r="AJ8" t="n">
         <v>17</v>
@@ -2477,16 +2477,16 @@
         <v>17.5</v>
       </c>
       <c r="AL8" t="n">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="AM8" t="n">
-        <v>120</v>
+        <v>700</v>
       </c>
       <c r="AN8" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AO8" t="n">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="AP8" t="n">
         <v>15</v>
@@ -2495,10 +2495,10 @@
         <v>18</v>
       </c>
       <c r="AR8" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="AT8" t="n">
         <v>8.800000000000001</v>
@@ -2510,7 +2510,7 @@
         <v>18.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="AX8" t="n">
         <v>8.4</v>
@@ -2522,7 +2522,7 @@
         <v>16</v>
       </c>
       <c r="BA8" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BB8" t="n">
         <v>11.5</v>
@@ -2531,16 +2531,16 @@
         <v>12</v>
       </c>
       <c r="BD8" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BF8" t="n">
         <v>6</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BH8" t="n">
         <v>4</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-15 18:07:21</t>
+          <t>2026-06-15 20:15:46</t>
         </is>
       </c>
     </row>
@@ -2644,13 +2644,13 @@
         <v>3.2</v>
       </c>
       <c r="I9" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="J9" t="n">
         <v>3.75</v>
       </c>
       <c r="K9" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L9" t="n">
         <v>1.28</v>
@@ -2668,34 +2668,34 @@
         <v>2.32</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="R9" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S9" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="T9" t="n">
         <v>1.59</v>
       </c>
       <c r="U9" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="V9" t="n">
         <v>1.4</v>
       </c>
       <c r="W9" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="X9" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="Y9" t="n">
         <v>19.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="AA9" t="n">
         <v>65</v>
@@ -2707,7 +2707,7 @@
         <v>10.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AE9" t="n">
         <v>40</v>
@@ -2719,10 +2719,10 @@
         <v>13</v>
       </c>
       <c r="AH9" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AI9" t="n">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="AJ9" t="n">
         <v>34</v>
@@ -2731,16 +2731,16 @@
         <v>25</v>
       </c>
       <c r="AL9" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="AM9" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AN9" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AO9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP9" t="n">
         <v>15</v>
@@ -2752,7 +2752,7 @@
         <v>18.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AT9" t="n">
         <v>11.5</v>
@@ -2776,19 +2776,19 @@
         <v>13</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BB9" t="n">
-        <v>5.2</v>
+        <v>14.5</v>
       </c>
       <c r="BC9" t="n">
         <v>15.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>6</v>
+        <v>14.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>6.2</v>
+        <v>23</v>
       </c>
       <c r="BF9" t="n">
         <v>11</v>
@@ -2830,7 +2830,7 @@
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BT9" t="n">
         <v>7</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-15 18:07:21</t>
+          <t>2026-06-15 20:15:46</t>
         </is>
       </c>
     </row>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="G10" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="H10" t="n">
         <v>2.92</v>
@@ -2901,34 +2901,34 @@
         <v>3.1</v>
       </c>
       <c r="J10" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N10" t="n">
         <v>4.1</v>
       </c>
-      <c r="L10" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N10" t="n">
-        <v>4.6</v>
-      </c>
       <c r="O10" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="P10" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S10" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="T10" t="n">
         <v>1.63</v>
@@ -2940,115 +2940,115 @@
         <v>1.47</v>
       </c>
       <c r="W10" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="X10" t="n">
         <v>90</v>
       </c>
       <c r="Y10" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="Z10" t="n">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="AA10" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AB10" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AC10" t="n">
         <v>12.5</v>
       </c>
       <c r="AD10" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF10" t="n">
         <v>970</v>
       </c>
-      <c r="AE10" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>22</v>
-      </c>
       <c r="AG10" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AH10" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="AI10" t="n">
-        <v>38</v>
+        <v>500</v>
       </c>
       <c r="AJ10" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AK10" t="n">
-        <v>27</v>
+        <v>500</v>
       </c>
       <c r="AL10" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AM10" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AN10" t="n">
-        <v>970</v>
+        <v>55</v>
       </c>
       <c r="AO10" t="n">
-        <v>25</v>
+        <v>500</v>
       </c>
       <c r="AP10" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ10" t="n">
-        <v>5.4</v>
+        <v>8.4</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.5</v>
+        <v>8.6</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.4</v>
+        <v>10.5</v>
       </c>
       <c r="AT10" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AU10" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AV10" t="n">
         <v>10.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>6.6</v>
+        <v>14.5</v>
       </c>
       <c r="AX10" t="n">
-        <v>5</v>
+        <v>8.4</v>
       </c>
       <c r="AY10" t="n">
-        <v>4.9</v>
+        <v>10</v>
       </c>
       <c r="AZ10" t="n">
-        <v>5.4</v>
+        <v>8.4</v>
       </c>
       <c r="BA10" t="n">
-        <v>6.8</v>
+        <v>24</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.7</v>
+        <v>14.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>5.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.6</v>
+        <v>9.6</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BF10" t="n">
         <v>11</v>
       </c>
       <c r="BG10" t="n">
-        <v>6.2</v>
+        <v>17.5</v>
       </c>
       <c r="BH10" t="n">
         <v>4</v>
@@ -3066,7 +3066,7 @@
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="BN10" t="n">
         <v>7.8</v>
@@ -3078,13 +3078,13 @@
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="BT10" t="n">
         <v>11.5</v>
@@ -3102,7 +3102,7 @@
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-15 18:07:21</t>
+          <t>2026-06-15 20:15:46</t>
         </is>
       </c>
     </row>
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="G11" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="H11" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="J11" t="n">
         <v>4.4</v>
       </c>
       <c r="K11" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L11" t="n">
         <v>1.15</v>
@@ -3167,16 +3167,16 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="O11" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="P11" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="R11" t="n">
         <v>2.5</v>
@@ -3191,7 +3191,7 @@
         <v>1.11</v>
       </c>
       <c r="V11" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="W11" t="n">
         <v>2.66</v>
@@ -3209,10 +3209,10 @@
         <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD11" t="n">
         <v>1000</v>
@@ -3221,10 +3221,10 @@
         <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH11" t="n">
         <v>1000</v>
@@ -3233,88 +3233,88 @@
         <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM11" t="n">
         <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO11" t="n">
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH11" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BI11" t="n">
         <v>5.5</v>
       </c>
       <c r="BJ11" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BK11" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
@@ -3341,16 +3341,16 @@
         <v>6.4</v>
       </c>
       <c r="BT11" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BU11" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
@@ -3362,11 +3362,11 @@
         <v>6.8</v>
       </c>
       <c r="CA11" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-15 18:07:21</t>
+          <t>2026-06-15 20:15:46</t>
         </is>
       </c>
     </row>
@@ -3409,13 +3409,13 @@
         <v>3.35</v>
       </c>
       <c r="J12" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K12" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="M12" t="n">
         <v>1.02</v>
@@ -3451,112 +3451,112 @@
         <v>1.74</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD12" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BH12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-15 18:07:21</t>
+          <t>2026-06-15 20:15:46</t>
         </is>
       </c>
     </row>
@@ -3657,7 +3657,7 @@
         <v>3.3</v>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="I13" t="n">
         <v>2.24</v>
@@ -3705,7 +3705,7 @@
         <v>1.43</v>
       </c>
       <c r="X13" t="n">
-        <v>950</v>
+        <v>240</v>
       </c>
       <c r="Y13" t="n">
         <v>26</v>
@@ -3741,10 +3741,10 @@
         <v>23</v>
       </c>
       <c r="AJ13" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="AK13" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AL13" t="n">
         <v>30</v>
@@ -3795,7 +3795,7 @@
         <v>18</v>
       </c>
       <c r="BB13" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BC13" t="n">
         <v>18</v>
@@ -3822,7 +3822,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK13" t="n">
-        <v>5.8</v>
+        <v>4.7</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
@@ -3834,7 +3834,7 @@
         <v>8</v>
       </c>
       <c r="BO13" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BP13" t="n">
         <v>20</v>
@@ -3852,13 +3852,13 @@
         <v>6.6</v>
       </c>
       <c r="BU13" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="BV13" t="n">
         <v>13.5</v>
       </c>
       <c r="BW13" t="n">
-        <v>8.800000000000001</v>
+        <v>5.7</v>
       </c>
       <c r="BX13" t="n">
         <v>17.5</v>
@@ -3870,11 +3870,11 @@
         <v>9.4</v>
       </c>
       <c r="CA13" t="n">
-        <v>6.2</v>
+        <v>4.8</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-15 18:07:21</t>
+          <t>2026-06-15 20:15:46</t>
         </is>
       </c>
     </row>
@@ -3911,13 +3911,13 @@
         <v>1.68</v>
       </c>
       <c r="H14" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="I14" t="n">
         <v>7.6</v>
       </c>
       <c r="J14" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K14" t="n">
         <v>4.1</v>
@@ -3935,19 +3935,19 @@
         <v>1.4</v>
       </c>
       <c r="P14" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R14" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
       </c>
       <c r="T14" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="U14" t="n">
         <v>1.75</v>
@@ -3962,13 +3962,13 @@
         <v>12.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA14" t="n">
-        <v>310</v>
+        <v>290</v>
       </c>
       <c r="AB14" t="n">
         <v>7</v>
@@ -3980,7 +3980,7 @@
         <v>950</v>
       </c>
       <c r="AE14" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AF14" t="n">
         <v>8.800000000000001</v>
@@ -3992,13 +3992,13 @@
         <v>950</v>
       </c>
       <c r="AI14" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AJ14" t="n">
         <v>16.5</v>
       </c>
       <c r="AK14" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AL14" t="n">
         <v>50</v>
@@ -4010,7 +4010,7 @@
         <v>12.5</v>
       </c>
       <c r="AO14" t="n">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="AP14" t="n">
         <v>10.5</v>
@@ -4019,10 +4019,10 @@
         <v>16</v>
       </c>
       <c r="AR14" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AS14" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT14" t="n">
         <v>6</v>
@@ -4031,7 +4031,7 @@
         <v>8</v>
       </c>
       <c r="AV14" t="n">
-        <v>7.8</v>
+        <v>21</v>
       </c>
       <c r="AW14" t="n">
         <v>10</v>
@@ -4043,19 +4043,19 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ14" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BA14" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BB14" t="n">
         <v>12.5</v>
       </c>
       <c r="BC14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD14" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE14" t="n">
         <v>10</v>
@@ -4070,7 +4070,7 @@
         <v>1000</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="BJ14" t="n">
         <v>1000</v>
@@ -4082,53 +4082,53 @@
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="BN14" t="n">
         <v>1000</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="BT14" t="n">
         <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-15 18:07:21</t>
+          <t>2026-06-15 20:15:46</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-16.xlsx
@@ -881,16 +881,16 @@
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O2" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="P2" t="n">
         <v>1.82</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R2" t="n">
         <v>1.28</v>
@@ -908,7 +908,7 @@
         <v>1.27</v>
       </c>
       <c r="W2" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="X2" t="n">
         <v>27</v>
@@ -941,7 +941,7 @@
         <v>500</v>
       </c>
       <c r="AH2" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AI2" t="n">
         <v>500</v>
@@ -968,13 +968,13 @@
         <v>5.7</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AR2" t="n">
-        <v>3.15</v>
+        <v>4.7</v>
       </c>
       <c r="AS2" t="n">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="AT2" t="n">
         <v>5.1</v>
@@ -986,7 +986,7 @@
         <v>6.2</v>
       </c>
       <c r="AW2" t="n">
-        <v>3.3</v>
+        <v>2.86</v>
       </c>
       <c r="AX2" t="n">
         <v>6.2</v>
@@ -998,79 +998,79 @@
         <v>6.4</v>
       </c>
       <c r="BA2" t="n">
-        <v>3.35</v>
+        <v>2.62</v>
       </c>
       <c r="BB2" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="BC2" t="n">
         <v>6.6</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BE2" t="n">
-        <v>3.05</v>
+        <v>2.84</v>
       </c>
       <c r="BF2" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BH2" t="n">
         <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN2" t="n">
         <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-15 20:15:46</t>
+          <t>2026-06-15 22:23:54</t>
         </is>
       </c>
     </row>
@@ -1114,31 +1114,31 @@
         <v>1.54</v>
       </c>
       <c r="G3" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="H3" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="I3" t="n">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="K3" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="O3" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P3" t="n">
         <v>1.9</v>
@@ -1153,25 +1153,25 @@
         <v>3.3</v>
       </c>
       <c r="T3" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="U3" t="n">
         <v>1.84</v>
       </c>
       <c r="V3" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="W3" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="X3" t="n">
         <v>18.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>27</v>
+        <v>950</v>
       </c>
       <c r="Z3" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AA3" t="n">
         <v>270</v>
@@ -1219,10 +1219,10 @@
         <v>190</v>
       </c>
       <c r="AP3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AQ3" t="n">
-        <v>16.5</v>
+        <v>4.2</v>
       </c>
       <c r="AR3" t="n">
         <v>4.4</v>
@@ -1231,16 +1231,16 @@
         <v>4.6</v>
       </c>
       <c r="AT3" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AU3" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AV3" t="n">
-        <v>20</v>
+        <v>4.2</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AX3" t="n">
         <v>7.8</v>
@@ -1252,16 +1252,16 @@
         <v>4</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BB3" t="n">
         <v>10.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>12.5</v>
+        <v>3.9</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BE3" t="n">
         <v>4.6</v>
@@ -1276,7 +1276,7 @@
         <v>3.6</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="BJ3" t="n">
         <v>11.5</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-15 20:15:46</t>
+          <t>2026-06-15 22:23:54</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
         <v>2.42</v>
       </c>
       <c r="G4" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="H4" t="n">
         <v>2.72</v>
@@ -1380,7 +1380,7 @@
         <v>3.5</v>
       </c>
       <c r="K4" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="L4" t="n">
         <v>1.29</v>
@@ -1416,7 +1416,7 @@
         <v>1.47</v>
       </c>
       <c r="W4" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="X4" t="n">
         <v>22</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-15 20:15:46</t>
+          <t>2026-06-15 22:23:54</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
         <v>1.44</v>
       </c>
       <c r="I5" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="J5" t="n">
         <v>4.7</v>
@@ -1652,7 +1652,7 @@
         <v>2.42</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="R5" t="n">
         <v>1.56</v>
@@ -1661,13 +1661,13 @@
         <v>2.42</v>
       </c>
       <c r="T5" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="U5" t="n">
         <v>2.06</v>
       </c>
       <c r="V5" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="W5" t="n">
         <v>1.13</v>
@@ -1724,13 +1724,13 @@
         <v>120</v>
       </c>
       <c r="AO5" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AP5" t="n">
         <v>17</v>
       </c>
       <c r="AQ5" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AR5" t="n">
         <v>8.6</v>
@@ -1751,7 +1751,7 @@
         <v>10.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AY5" t="n">
         <v>20</v>
@@ -1760,22 +1760,22 @@
         <v>16.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BC5" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BD5" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BG5" t="n">
         <v>5</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-15 20:15:46</t>
+          <t>2026-06-15 22:23:54</t>
         </is>
       </c>
     </row>
@@ -1897,13 +1897,13 @@
         <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="O6" t="n">
         <v>1.3</v>
       </c>
       <c r="P6" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q6" t="n">
         <v>1.3</v>
@@ -1927,10 +1927,10 @@
         <v>1.7</v>
       </c>
       <c r="X6" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Y6" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Z6" t="n">
         <v>500</v>
@@ -1939,13 +1939,13 @@
         <v>500</v>
       </c>
       <c r="AB6" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AC6" t="n">
         <v>500</v>
       </c>
       <c r="AD6" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AE6" t="n">
         <v>500</v>
@@ -1954,10 +1954,10 @@
         <v>500</v>
       </c>
       <c r="AG6" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AH6" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AI6" t="n">
         <v>500</v>
@@ -1981,55 +1981,55 @@
         <v>500</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AU6" t="n">
         <v>1.04</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="BG6" t="n">
         <v>1.55</v>
@@ -2038,65 +2038,65 @@
         <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN6" t="n">
         <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT6" t="n">
         <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-15 20:15:46</t>
+          <t>2026-06-15 22:23:54</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
         <v>1.97</v>
       </c>
       <c r="I7" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="J7" t="n">
         <v>3.75</v>
@@ -2148,10 +2148,10 @@
         <v>1.38</v>
       </c>
       <c r="M7" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O7" t="n">
         <v>1.31</v>
@@ -2169,16 +2169,16 @@
         <v>3.35</v>
       </c>
       <c r="T7" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U7" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V7" t="n">
         <v>1.92</v>
       </c>
       <c r="W7" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="X7" t="n">
         <v>17.5</v>
@@ -2190,7 +2190,7 @@
         <v>15</v>
       </c>
       <c r="AA7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AB7" t="n">
         <v>17.5</v>
@@ -2238,7 +2238,7 @@
         <v>10.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AR7" t="n">
         <v>10.5</v>
@@ -2268,22 +2268,22 @@
         <v>16.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BB7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC7" t="n">
         <v>4.6</v>
       </c>
-      <c r="BC7" t="n">
+      <c r="BD7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF7" t="n">
         <v>4.5</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>4.4</v>
       </c>
       <c r="BG7" t="n">
         <v>11.5</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-15 20:15:46</t>
+          <t>2026-06-15 22:23:54</t>
         </is>
       </c>
     </row>
@@ -2423,7 +2423,7 @@
         <v>2.66</v>
       </c>
       <c r="T8" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="U8" t="n">
         <v>2.12</v>
@@ -2447,7 +2447,7 @@
         <v>700</v>
       </c>
       <c r="AB8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC8" t="n">
         <v>11</v>
@@ -2495,10 +2495,10 @@
         <v>18</v>
       </c>
       <c r="AR8" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AS8" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AT8" t="n">
         <v>8.800000000000001</v>
@@ -2510,7 +2510,7 @@
         <v>18.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX8" t="n">
         <v>8.4</v>
@@ -2522,7 +2522,7 @@
         <v>16</v>
       </c>
       <c r="BA8" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BB8" t="n">
         <v>11.5</v>
@@ -2534,13 +2534,13 @@
         <v>18</v>
       </c>
       <c r="BE8" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF8" t="n">
         <v>6</v>
       </c>
       <c r="BG8" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BH8" t="n">
         <v>4</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-15 20:15:46</t>
+          <t>2026-06-15 22:23:54</t>
         </is>
       </c>
     </row>
@@ -2635,16 +2635,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G9" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="H9" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I9" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J9" t="n">
         <v>3.75</v>
@@ -2680,13 +2680,13 @@
         <v>1.59</v>
       </c>
       <c r="U9" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="V9" t="n">
         <v>1.4</v>
       </c>
       <c r="W9" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="X9" t="n">
         <v>40</v>
@@ -2734,7 +2734,7 @@
         <v>65</v>
       </c>
       <c r="AM9" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="AN9" t="n">
         <v>13</v>
@@ -2752,7 +2752,7 @@
         <v>18.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT9" t="n">
         <v>11.5</v>
@@ -2776,13 +2776,13 @@
         <v>13</v>
       </c>
       <c r="BA9" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB9" t="n">
         <v>14.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>15.5</v>
+        <v>10.5</v>
       </c>
       <c r="BD9" t="n">
         <v>14.5</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-15 20:15:46</t>
+          <t>2026-06-15 22:23:54</t>
         </is>
       </c>
     </row>
@@ -2895,7 +2895,7 @@
         <v>2.5</v>
       </c>
       <c r="H10" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="I10" t="n">
         <v>3.1</v>
@@ -2910,16 +2910,16 @@
         <v>1.28</v>
       </c>
       <c r="M10" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N10" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="O10" t="n">
         <v>1.21</v>
       </c>
       <c r="P10" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q10" t="n">
         <v>1.68</v>
@@ -2934,7 +2934,7 @@
         <v>1.63</v>
       </c>
       <c r="U10" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="V10" t="n">
         <v>1.47</v>
@@ -2943,7 +2943,7 @@
         <v>1.66</v>
       </c>
       <c r="X10" t="n">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="Y10" t="n">
         <v>500</v>
@@ -2973,7 +2973,7 @@
         <v>500</v>
       </c>
       <c r="AH10" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AI10" t="n">
         <v>500</v>
@@ -2997,7 +2997,7 @@
         <v>500</v>
       </c>
       <c r="AP10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AQ10" t="n">
         <v>8.4</v>
@@ -3006,10 +3006,10 @@
         <v>8.6</v>
       </c>
       <c r="AS10" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AT10" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU10" t="n">
         <v>7.6</v>
@@ -3027,7 +3027,7 @@
         <v>10</v>
       </c>
       <c r="AZ10" t="n">
-        <v>8.4</v>
+        <v>12.5</v>
       </c>
       <c r="BA10" t="n">
         <v>24</v>
@@ -3036,13 +3036,13 @@
         <v>14.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BD10" t="n">
-        <v>9.6</v>
+        <v>23</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="BF10" t="n">
         <v>11</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-15 20:15:46</t>
+          <t>2026-06-15 22:23:54</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3146,7 @@
         <v>1.47</v>
       </c>
       <c r="G11" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="H11" t="n">
         <v>4.5</v>
@@ -3188,10 +3188,10 @@
         <v>1.11</v>
       </c>
       <c r="U11" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="V11" t="n">
         <v>1.11</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.1</v>
       </c>
       <c r="W11" t="n">
         <v>2.66</v>
@@ -3305,7 +3305,7 @@
         <v>1.55</v>
       </c>
       <c r="BH11" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BI11" t="n">
         <v>5.5</v>
@@ -3314,7 +3314,7 @@
         <v>9</v>
       </c>
       <c r="BK11" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
@@ -3326,7 +3326,7 @@
         <v>5.7</v>
       </c>
       <c r="BO11" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BP11" t="n">
         <v>9.199999999999999</v>
@@ -3356,17 +3356,17 @@
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BZ11" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="CA11" t="n">
         <v>4.9</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-15 20:15:46</t>
+          <t>2026-06-15 22:23:54</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
         <v>1.35</v>
       </c>
       <c r="R12" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="S12" t="n">
         <v>1.87</v>
@@ -3442,7 +3442,7 @@
         <v>1.11</v>
       </c>
       <c r="U12" t="n">
-        <v>1.11</v>
+        <v>2.66</v>
       </c>
       <c r="V12" t="n">
         <v>1.43</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-15 20:15:46</t>
+          <t>2026-06-15 22:23:54</t>
         </is>
       </c>
     </row>
@@ -3669,7 +3669,7 @@
         <v>5.2</v>
       </c>
       <c r="L13" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="M13" t="n">
         <v>1.01</v>
@@ -3681,16 +3681,16 @@
         <v>1.09</v>
       </c>
       <c r="P13" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="Q13" t="n">
         <v>1.3</v>
       </c>
       <c r="R13" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="S13" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="T13" t="n">
         <v>1.35</v>
@@ -3738,7 +3738,7 @@
         <v>15</v>
       </c>
       <c r="AI13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AJ13" t="n">
         <v>120</v>
@@ -3756,10 +3756,10 @@
         <v>12</v>
       </c>
       <c r="AO13" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AP13" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AQ13" t="n">
         <v>20</v>
@@ -3795,7 +3795,7 @@
         <v>18</v>
       </c>
       <c r="BB13" t="n">
-        <v>7.8</v>
+        <v>23</v>
       </c>
       <c r="BC13" t="n">
         <v>18</v>
@@ -3813,7 +3813,7 @@
         <v>5.6</v>
       </c>
       <c r="BH13" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BI13" t="n">
         <v>4.9</v>
@@ -3822,13 +3822,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK13" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BN13" t="n">
         <v>8</v>
@@ -3843,10 +3843,10 @@
         <v>6.6</v>
       </c>
       <c r="BR13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BS13" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BT13" t="n">
         <v>6.6</v>
@@ -3858,13 +3858,13 @@
         <v>13.5</v>
       </c>
       <c r="BW13" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BX13" t="n">
         <v>17.5</v>
       </c>
       <c r="BY13" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BZ13" t="n">
         <v>9.4</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-15 20:15:46</t>
+          <t>2026-06-15 22:23:54</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
         <v>6.6</v>
       </c>
       <c r="I14" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J14" t="n">
         <v>3.75</v>
@@ -3926,16 +3926,16 @@
         <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N14" t="n">
         <v>3.2</v>
       </c>
       <c r="O14" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P14" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="Q14" t="n">
         <v>2.18</v>
@@ -3947,13 +3947,13 @@
         <v>4</v>
       </c>
       <c r="T14" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="U14" t="n">
         <v>1.75</v>
       </c>
       <c r="V14" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W14" t="n">
         <v>2.46</v>
@@ -4019,7 +4019,7 @@
         <v>16</v>
       </c>
       <c r="AR14" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS14" t="n">
         <v>10.5</v>
@@ -4046,7 +4046,7 @@
         <v>8.4</v>
       </c>
       <c r="BA14" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BB14" t="n">
         <v>12.5</v>
@@ -4055,7 +4055,7 @@
         <v>17</v>
       </c>
       <c r="BD14" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE14" t="n">
         <v>10</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-15 20:15:46</t>
+          <t>2026-06-15 22:23:54</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-16.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="G2" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I2" t="n">
         <v>4.7</v>
       </c>
       <c r="J2" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K2" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L2" t="n">
         <v>1.41</v>
@@ -881,34 +881,34 @@
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="O2" t="n">
         <v>1.33</v>
       </c>
       <c r="P2" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="R2" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V2" t="n">
         <v>1.28</v>
       </c>
-      <c r="S2" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.27</v>
-      </c>
       <c r="W2" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="X2" t="n">
         <v>27</v>
@@ -935,10 +935,10 @@
         <v>500</v>
       </c>
       <c r="AF2" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AG2" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AH2" t="n">
         <v>950</v>
@@ -962,16 +962,16 @@
         <v>55</v>
       </c>
       <c r="AO2" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.7</v>
+        <v>7.6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.7</v>
+        <v>3.65</v>
       </c>
       <c r="AS2" t="n">
         <v>2.62</v>
@@ -983,10 +983,10 @@
         <v>4.9</v>
       </c>
       <c r="AV2" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AW2" t="n">
-        <v>2.86</v>
+        <v>2.76</v>
       </c>
       <c r="AX2" t="n">
         <v>6.2</v>
@@ -995,82 +995,82 @@
         <v>6.2</v>
       </c>
       <c r="AZ2" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BA2" t="n">
         <v>2.62</v>
       </c>
       <c r="BB2" t="n">
-        <v>6</v>
+        <v>3.85</v>
       </c>
       <c r="BC2" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.84</v>
+        <v>2.66</v>
       </c>
       <c r="BF2" t="n">
         <v>3.55</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.6</v>
+        <v>4.1</v>
       </c>
       <c r="BH2" t="n">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.04</v>
+        <v>2.78</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.04</v>
+        <v>1.43</v>
       </c>
       <c r="BN2" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.04</v>
+        <v>1.67</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.04</v>
+        <v>1.45</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.04</v>
+        <v>1.41</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-15 22:23:54</t>
+          <t>2026-06-16 00:31:41</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
         <v>4.6</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
@@ -1156,7 +1156,7 @@
         <v>1.94</v>
       </c>
       <c r="U3" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="V3" t="n">
         <v>1.14</v>
@@ -1219,7 +1219,7 @@
         <v>190</v>
       </c>
       <c r="AP3" t="n">
-        <v>11</v>
+        <v>3.8</v>
       </c>
       <c r="AQ3" t="n">
         <v>4.2</v>
@@ -1255,19 +1255,19 @@
         <v>4.6</v>
       </c>
       <c r="BB3" t="n">
-        <v>10.5</v>
+        <v>4.1</v>
       </c>
       <c r="BC3" t="n">
         <v>3.9</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BE3" t="n">
         <v>4.6</v>
       </c>
       <c r="BF3" t="n">
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="BG3" t="n">
         <v>4.6</v>
@@ -1276,7 +1276,7 @@
         <v>3.6</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="BJ3" t="n">
         <v>11.5</v>
@@ -1294,13 +1294,13 @@
         <v>4.1</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BP3" t="n">
         <v>10.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.4</v>
+        <v>7.6</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-15 22:23:54</t>
+          <t>2026-06-16 00:31:41</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="G4" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="H4" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="I4" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K4" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L4" t="n">
         <v>1.29</v>
@@ -1392,7 +1392,7 @@
         <v>4.1</v>
       </c>
       <c r="O4" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="P4" t="n">
         <v>2.08</v>
@@ -1404,19 +1404,19 @@
         <v>1.43</v>
       </c>
       <c r="S4" t="n">
-        <v>2.86</v>
+        <v>2.58</v>
       </c>
       <c r="T4" t="n">
         <v>1.69</v>
       </c>
       <c r="U4" t="n">
-        <v>2.3</v>
+        <v>1.11</v>
       </c>
       <c r="V4" t="n">
         <v>1.47</v>
       </c>
       <c r="W4" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X4" t="n">
         <v>22</v>
@@ -1431,16 +1431,16 @@
         <v>55</v>
       </c>
       <c r="AB4" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>10.5</v>
+        <v>42</v>
       </c>
       <c r="AD4" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AE4" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AF4" t="n">
         <v>22</v>
@@ -1452,133 +1452,133 @@
         <v>17</v>
       </c>
       <c r="AI4" t="n">
-        <v>38</v>
+        <v>500</v>
       </c>
       <c r="AJ4" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AK4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL4" t="n">
         <v>36</v>
       </c>
       <c r="AM4" t="n">
-        <v>75</v>
+        <v>200</v>
       </c>
       <c r="AN4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AO4" t="n">
         <v>28</v>
       </c>
       <c r="AP4" t="n">
-        <v>13</v>
+        <v>3.35</v>
       </c>
       <c r="AQ4" t="n">
-        <v>10</v>
+        <v>3.8</v>
       </c>
       <c r="AR4" t="n">
-        <v>15</v>
+        <v>3.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>36</v>
+        <v>3.55</v>
       </c>
       <c r="AT4" t="n">
-        <v>10.5</v>
+        <v>4.1</v>
       </c>
       <c r="AU4" t="n">
-        <v>7.4</v>
+        <v>4.9</v>
       </c>
       <c r="AV4" t="n">
-        <v>9.6</v>
+        <v>3.8</v>
       </c>
       <c r="AW4" t="n">
-        <v>21</v>
+        <v>3.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>13</v>
+        <v>3.35</v>
       </c>
       <c r="AY4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>11.5</v>
+        <v>3.25</v>
       </c>
       <c r="BA4" t="n">
-        <v>20</v>
+        <v>3.65</v>
       </c>
       <c r="BB4" t="n">
-        <v>14.5</v>
+        <v>3.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>19</v>
+        <v>3.4</v>
       </c>
       <c r="BD4" t="n">
-        <v>16</v>
+        <v>3.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.7</v>
+        <v>3.65</v>
       </c>
       <c r="BF4" t="n">
-        <v>13.5</v>
+        <v>3.55</v>
       </c>
       <c r="BG4" t="n">
-        <v>16.5</v>
+        <v>4</v>
       </c>
       <c r="BH4" t="n">
         <v>3.9</v>
       </c>
       <c r="BI4" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="BJ4" t="n">
         <v>9.4</v>
       </c>
       <c r="BK4" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="BN4" t="n">
         <v>5.9</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BP4" t="n">
         <v>19</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BR4" t="n">
         <v>30</v>
       </c>
       <c r="BS4" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BT4" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BV4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BW4" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BX4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BY4" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-15 22:23:54</t>
+          <t>2026-06-16 00:31:41</t>
         </is>
       </c>
     </row>
@@ -1619,16 +1619,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="G5" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="H5" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="I5" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="J5" t="n">
         <v>4.7</v>
@@ -1637,64 +1637,64 @@
         <v>5.6</v>
       </c>
       <c r="L5" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="M5" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="N5" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="O5" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="P5" t="n">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="R5" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="S5" t="n">
-        <v>2.42</v>
+        <v>2.6</v>
       </c>
       <c r="T5" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="U5" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V5" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="W5" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X5" t="n">
         <v>28</v>
       </c>
       <c r="Y5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AB5" t="n">
         <v>75</v>
       </c>
       <c r="AC5" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AF5" t="n">
         <v>160</v>
@@ -1703,13 +1703,13 @@
         <v>75</v>
       </c>
       <c r="AH5" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AI5" t="n">
         <v>75</v>
       </c>
       <c r="AJ5" t="n">
-        <v>250</v>
+        <v>310</v>
       </c>
       <c r="AK5" t="n">
         <v>260</v>
@@ -1718,76 +1718,76 @@
         <v>230</v>
       </c>
       <c r="AM5" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="AN5" t="n">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="AO5" t="n">
         <v>6.2</v>
       </c>
       <c r="AP5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AQ5" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AR5" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AS5" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AU5" t="n">
         <v>10</v>
       </c>
       <c r="AV5" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW5" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="AY5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>20</v>
       </c>
-      <c r="AZ5" t="n">
-        <v>16.5</v>
-      </c>
       <c r="BA5" t="n">
-        <v>6.2</v>
+        <v>13</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC5" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE5" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>7.4</v>
+        <v>15</v>
       </c>
       <c r="BG5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BH5" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="BJ5" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK5" t="n">
         <v>5.5</v>
@@ -1796,10 +1796,10 @@
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN5" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BO5" t="n">
         <v>5.6</v>
@@ -1817,19 +1817,19 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BT5" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="BV5" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BW5" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BX5" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BY5" t="n">
         <v>7.2</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-15 22:23:54</t>
+          <t>2026-06-16 00:31:41</t>
         </is>
       </c>
     </row>
@@ -1876,10 +1876,10 @@
         <v>1.6</v>
       </c>
       <c r="G6" t="n">
-        <v>2.72</v>
+        <v>6</v>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="I6" t="n">
         <v>44</v>
@@ -1912,7 +1912,7 @@
         <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T6" t="n">
         <v>1.11</v>
@@ -1924,7 +1924,7 @@
         <v>1.18</v>
       </c>
       <c r="W6" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="X6" t="n">
         <v>950</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-15 22:23:54</t>
+          <t>2026-06-16 00:31:41</t>
         </is>
       </c>
     </row>
@@ -2133,10 +2133,10 @@
         <v>4.3</v>
       </c>
       <c r="H7" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="I7" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="J7" t="n">
         <v>3.75</v>
@@ -2151,7 +2151,7 @@
         <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="O7" t="n">
         <v>1.31</v>
@@ -2160,25 +2160,25 @@
         <v>1.96</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="R7" t="n">
         <v>1.34</v>
       </c>
       <c r="S7" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T7" t="n">
         <v>1.79</v>
       </c>
       <c r="U7" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V7" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="W7" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="X7" t="n">
         <v>17.5</v>
@@ -2199,7 +2199,7 @@
         <v>10</v>
       </c>
       <c r="AD7" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE7" t="n">
         <v>23</v>
@@ -2214,16 +2214,16 @@
         <v>23</v>
       </c>
       <c r="AI7" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AJ7" t="n">
         <v>110</v>
       </c>
       <c r="AK7" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AL7" t="n">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="AM7" t="n">
         <v>580</v>
@@ -2256,7 +2256,7 @@
         <v>7.8</v>
       </c>
       <c r="AW7" t="n">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="AX7" t="n">
         <v>21</v>
@@ -2265,92 +2265,92 @@
         <v>14</v>
       </c>
       <c r="AZ7" t="n">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BB7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC7" t="n">
         <v>4.7</v>
       </c>
-      <c r="BC7" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BD7" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BE7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF7" t="n">
         <v>4.7</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>4.5</v>
       </c>
       <c r="BG7" t="n">
         <v>11.5</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="BJ7" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BN7" t="n">
         <v>7.8</v>
       </c>
       <c r="BO7" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BP7" t="n">
         <v>36</v>
       </c>
       <c r="BQ7" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BT7" t="n">
         <v>4.9</v>
       </c>
       <c r="BU7" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BV7" t="n">
         <v>14.5</v>
       </c>
       <c r="BW7" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BX7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BY7" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BZ7" t="n">
         <v>25</v>
       </c>
       <c r="CA7" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-15 22:23:54</t>
+          <t>2026-06-16 00:31:41</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
         <v>1.55</v>
       </c>
       <c r="G8" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="H8" t="n">
         <v>6</v>
@@ -2396,7 +2396,7 @@
         <v>4.3</v>
       </c>
       <c r="K8" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L8" t="n">
         <v>1.29</v>
@@ -2405,34 +2405,34 @@
         <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O8" t="n">
         <v>1.23</v>
       </c>
       <c r="P8" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="R8" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="S8" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="T8" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="U8" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V8" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W8" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="X8" t="n">
         <v>23</v>
@@ -2453,10 +2453,10 @@
         <v>11</v>
       </c>
       <c r="AD8" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AE8" t="n">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="AF8" t="n">
         <v>12</v>
@@ -2477,7 +2477,7 @@
         <v>17.5</v>
       </c>
       <c r="AL8" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AM8" t="n">
         <v>700</v>
@@ -2495,10 +2495,10 @@
         <v>18</v>
       </c>
       <c r="AR8" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AT8" t="n">
         <v>8.800000000000001</v>
@@ -2510,7 +2510,7 @@
         <v>18.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AX8" t="n">
         <v>8.4</v>
@@ -2522,7 +2522,7 @@
         <v>16</v>
       </c>
       <c r="BA8" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB8" t="n">
         <v>11.5</v>
@@ -2534,67 +2534,67 @@
         <v>18</v>
       </c>
       <c r="BE8" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BF8" t="n">
         <v>6</v>
       </c>
       <c r="BG8" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BH8" t="n">
         <v>4</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BJ8" t="n">
         <v>10.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>12</v>
+        <v>3.25</v>
       </c>
       <c r="BN8" t="n">
         <v>4.3</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="BP8" t="n">
         <v>10</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT8" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-15 22:23:54</t>
+          <t>2026-06-16 00:31:41</t>
         </is>
       </c>
     </row>
@@ -2635,16 +2635,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="G9" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H9" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I9" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="J9" t="n">
         <v>3.75</v>
@@ -2653,22 +2653,22 @@
         <v>3.9</v>
       </c>
       <c r="L9" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M9" t="n">
         <v>1.04</v>
       </c>
       <c r="N9" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O9" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P9" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="R9" t="n">
         <v>1.53</v>
@@ -2677,7 +2677,7 @@
         <v>2.58</v>
       </c>
       <c r="T9" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="U9" t="n">
         <v>2.48</v>
@@ -2698,7 +2698,7 @@
         <v>70</v>
       </c>
       <c r="AA9" t="n">
-        <v>65</v>
+        <v>900</v>
       </c>
       <c r="AB9" t="n">
         <v>15.5</v>
@@ -2716,7 +2716,7 @@
         <v>19.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH9" t="n">
         <v>18</v>
@@ -2728,22 +2728,22 @@
         <v>34</v>
       </c>
       <c r="AK9" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AL9" t="n">
         <v>65</v>
       </c>
       <c r="AM9" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="AN9" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AO9" t="n">
         <v>25</v>
       </c>
       <c r="AP9" t="n">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="AQ9" t="n">
         <v>14.5</v>
@@ -2752,7 +2752,7 @@
         <v>18.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AT9" t="n">
         <v>11.5</v>
@@ -2776,13 +2776,13 @@
         <v>13</v>
       </c>
       <c r="BA9" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BB9" t="n">
         <v>14.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>10.5</v>
+        <v>18</v>
       </c>
       <c r="BD9" t="n">
         <v>14.5</v>
@@ -2791,10 +2791,10 @@
         <v>23</v>
       </c>
       <c r="BF9" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BH9" t="n">
         <v>4.1</v>
@@ -2803,7 +2803,7 @@
         <v>3.65</v>
       </c>
       <c r="BJ9" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK9" t="n">
         <v>5.3</v>
@@ -2812,7 +2812,7 @@
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BN9" t="n">
         <v>5.5</v>
@@ -2824,13 +2824,13 @@
         <v>15.5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT9" t="n">
         <v>7</v>
@@ -2842,13 +2842,13 @@
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BX9" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-15 22:23:54</t>
+          <t>2026-06-16 00:31:41</t>
         </is>
       </c>
     </row>
@@ -2889,25 +2889,25 @@
         </is>
       </c>
       <c r="F10" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="G10" t="n">
         <v>2.38</v>
       </c>
-      <c r="G10" t="n">
-        <v>2.5</v>
-      </c>
       <c r="H10" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="I10" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="J10" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K10" t="n">
         <v>3.9</v>
       </c>
       <c r="L10" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="M10" t="n">
         <v>1.04</v>
@@ -2922,25 +2922,25 @@
         <v>2.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R10" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S10" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="T10" t="n">
         <v>1.63</v>
       </c>
       <c r="U10" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="V10" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="W10" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="X10" t="n">
         <v>40</v>
@@ -2949,28 +2949,28 @@
         <v>500</v>
       </c>
       <c r="Z10" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AA10" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB10" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AC10" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD10" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AE10" t="n">
         <v>500</v>
       </c>
       <c r="AF10" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AG10" t="n">
-        <v>500</v>
+        <v>16</v>
       </c>
       <c r="AH10" t="n">
         <v>23</v>
@@ -2982,37 +2982,37 @@
         <v>500</v>
       </c>
       <c r="AK10" t="n">
-        <v>500</v>
+        <v>23</v>
       </c>
       <c r="AL10" t="n">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="AM10" t="n">
         <v>500</v>
       </c>
       <c r="AN10" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="AO10" t="n">
         <v>500</v>
       </c>
       <c r="AP10" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AQ10" t="n">
-        <v>8.4</v>
+        <v>12.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>8.6</v>
+        <v>15</v>
       </c>
       <c r="AS10" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AT10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU10" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV10" t="n">
         <v>10.5</v>
@@ -3021,10 +3021,10 @@
         <v>14.5</v>
       </c>
       <c r="AX10" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY10" t="n">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ10" t="n">
         <v>12.5</v>
@@ -3033,22 +3033,22 @@
         <v>24</v>
       </c>
       <c r="BB10" t="n">
-        <v>14.5</v>
+        <v>19</v>
       </c>
       <c r="BC10" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD10" t="n">
         <v>23</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF10" t="n">
         <v>11</v>
       </c>
       <c r="BG10" t="n">
-        <v>17.5</v>
+        <v>8.4</v>
       </c>
       <c r="BH10" t="n">
         <v>4</v>
@@ -3066,16 +3066,16 @@
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BN10" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BO10" t="n">
         <v>4.8</v>
       </c>
       <c r="BP10" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BQ10" t="n">
         <v>8.199999999999999</v>
@@ -3084,10 +3084,10 @@
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="BT10" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="BU10" t="n">
         <v>5.3</v>
@@ -3096,13 +3096,13 @@
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>9.4</v>
+        <v>1.11</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-15 22:23:54</t>
+          <t>2026-06-16 00:31:41</t>
         </is>
       </c>
     </row>
@@ -3146,13 +3146,13 @@
         <v>1.47</v>
       </c>
       <c r="G11" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="H11" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I11" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="J11" t="n">
         <v>4.4</v>
@@ -3173,13 +3173,13 @@
         <v>1.08</v>
       </c>
       <c r="P11" t="n">
-        <v>4.5</v>
+        <v>2.56</v>
       </c>
       <c r="Q11" t="n">
         <v>1.08</v>
       </c>
       <c r="R11" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="S11" t="n">
         <v>1.31</v>
@@ -3251,55 +3251,55 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AY11" t="n">
         <v>1.18</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AZ11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BB11" t="n">
         <v>1.18</v>
       </c>
-      <c r="AR11" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AU11" t="n">
+      <c r="BC11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BD11" t="n">
         <v>1.15</v>
       </c>
-      <c r="AV11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BB11" t="n">
+      <c r="BE11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BF11" t="n">
         <v>1.17</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>1.16</v>
       </c>
       <c r="BG11" t="n">
         <v>1.55</v>
@@ -3314,59 +3314,59 @@
         <v>9</v>
       </c>
       <c r="BK11" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN11" t="n">
         <v>5.7</v>
       </c>
       <c r="BO11" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BP11" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BR11" t="n">
         <v>14.5</v>
       </c>
       <c r="BS11" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BT11" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BU11" t="n">
-        <v>5.9</v>
+        <v>9.4</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>36</v>
+      </c>
+      <c r="BY11" t="n">
         <v>8.800000000000001</v>
-      </c>
-      <c r="BX11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY11" t="n">
-        <v>8.4</v>
       </c>
       <c r="BZ11" t="n">
         <v>6.6</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-15 22:23:54</t>
+          <t>2026-06-16 00:31:41</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-15 22:23:54</t>
+          <t>2026-06-16 00:31:41</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="G13" t="n">
         <v>3.3</v>
@@ -3669,7 +3669,7 @@
         <v>5.2</v>
       </c>
       <c r="L13" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="M13" t="n">
         <v>1.01</v>
@@ -3813,7 +3813,7 @@
         <v>5.6</v>
       </c>
       <c r="BH13" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BI13" t="n">
         <v>4.9</v>
@@ -3822,13 +3822,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK13" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BN13" t="n">
         <v>8</v>
@@ -3840,13 +3840,13 @@
         <v>20</v>
       </c>
       <c r="BQ13" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR13" t="n">
         <v>21</v>
       </c>
       <c r="BS13" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BT13" t="n">
         <v>6.6</v>
@@ -3858,23 +3858,23 @@
         <v>13.5</v>
       </c>
       <c r="BW13" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BX13" t="n">
         <v>17.5</v>
       </c>
       <c r="BY13" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BZ13" t="n">
         <v>9.4</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-15 22:23:54</t>
+          <t>2026-06-16 00:31:41</t>
         </is>
       </c>
     </row>
@@ -3926,10 +3926,10 @@
         <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N14" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="O14" t="n">
         <v>1.39</v>
@@ -3944,10 +3944,10 @@
         <v>1.27</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T14" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U14" t="n">
         <v>1.75</v>
@@ -3983,7 +3983,7 @@
         <v>160</v>
       </c>
       <c r="AF14" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AG14" t="n">
         <v>10.5</v>
@@ -4004,10 +4004,10 @@
         <v>50</v>
       </c>
       <c r="AM14" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AN14" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AO14" t="n">
         <v>250</v>
@@ -4019,10 +4019,10 @@
         <v>16</v>
       </c>
       <c r="AR14" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS14" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT14" t="n">
         <v>6</v>
@@ -4034,7 +4034,7 @@
         <v>21</v>
       </c>
       <c r="AW14" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX14" t="n">
         <v>7.2</v>
@@ -4043,28 +4043,28 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ14" t="n">
-        <v>8.4</v>
+        <v>22</v>
       </c>
       <c r="BA14" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB14" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BC14" t="n">
         <v>17</v>
       </c>
       <c r="BD14" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BE14" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG14" t="n">
         <v>9.800000000000001</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>10</v>
       </c>
       <c r="BH14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-15 22:23:54</t>
+          <t>2026-06-16 00:31:41</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-16.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="G2" t="n">
         <v>2.04</v>
@@ -869,40 +869,40 @@
         <v>4.7</v>
       </c>
       <c r="J2" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K2" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="L2" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="M2" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N2" t="n">
         <v>3.6</v>
       </c>
       <c r="O2" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R2" t="n">
         <v>1.33</v>
       </c>
-      <c r="P2" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.32</v>
-      </c>
       <c r="S2" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="T2" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U2" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="V2" t="n">
         <v>1.28</v>
@@ -914,7 +914,7 @@
         <v>27</v>
       </c>
       <c r="Y2" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="Z2" t="n">
         <v>500</v>
@@ -923,22 +923,22 @@
         <v>900</v>
       </c>
       <c r="AB2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD2" t="n">
         <v>500</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>42</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>970</v>
       </c>
       <c r="AE2" t="n">
         <v>500</v>
       </c>
       <c r="AF2" t="n">
-        <v>970</v>
+        <v>40</v>
       </c>
       <c r="AG2" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AH2" t="n">
         <v>950</v>
@@ -968,13 +968,13 @@
         <v>7.6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AR2" t="n">
-        <v>3.65</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.62</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT2" t="n">
         <v>5.1</v>
@@ -983,10 +983,10 @@
         <v>4.9</v>
       </c>
       <c r="AV2" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="AW2" t="n">
-        <v>2.76</v>
+        <v>7.8</v>
       </c>
       <c r="AX2" t="n">
         <v>6.2</v>
@@ -995,34 +995,34 @@
         <v>6.2</v>
       </c>
       <c r="AZ2" t="n">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="BA2" t="n">
-        <v>2.62</v>
+        <v>7.8</v>
       </c>
       <c r="BB2" t="n">
-        <v>3.85</v>
+        <v>10.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.15</v>
+        <v>7.2</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.66</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF2" t="n">
-        <v>3.55</v>
+        <v>5.8</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.1</v>
+        <v>7.8</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
@@ -1034,13 +1034,13 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.43</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN2" t="n">
         <v>4.8</v>
       </c>
       <c r="BO2" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
@@ -1052,25 +1052,25 @@
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.67</v>
+        <v>6.4</v>
       </c>
       <c r="BT2" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BU2" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.45</v>
+        <v>6.6</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.41</v>
+        <v>7.2</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-16 00:31:41</t>
+          <t>2026-06-16 02:39:49</t>
         </is>
       </c>
     </row>
@@ -1111,220 +1111,220 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="G3" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="H3" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="I3" t="n">
         <v>8</v>
       </c>
       <c r="J3" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="K3" t="n">
         <v>4.6</v>
       </c>
       <c r="L3" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="O3" t="n">
         <v>1.3</v>
       </c>
       <c r="P3" t="n">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="R3" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="S3" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T3" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="U3" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="V3" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="W3" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="X3" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="Y3" t="n">
-        <v>950</v>
+        <v>130</v>
       </c>
       <c r="Z3" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AA3" t="n">
-        <v>270</v>
+        <v>700</v>
       </c>
       <c r="AB3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>500</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>700</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>500</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>700</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>100</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>700</v>
+      </c>
+      <c r="AN3" t="n">
         <v>9.4</v>
       </c>
-      <c r="AC3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>75</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>140</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>48</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>130</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>170</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AO3" t="n">
-        <v>190</v>
+        <v>700</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.8</v>
+        <v>6.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.2</v>
+        <v>6.8</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.4</v>
+        <v>9.4</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.6</v>
+        <v>9.4</v>
       </c>
       <c r="AT3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>6.8</v>
       </c>
-      <c r="AU3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>4</v>
-      </c>
       <c r="BA3" t="n">
-        <v>4.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.1</v>
+        <v>6.8</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.9</v>
+        <v>6.8</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.8</v>
+        <v>7.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.6</v>
+        <v>9</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="BJ3" t="n">
         <v>11.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="BP3" t="n">
         <v>10.5</v>
       </c>
       <c r="BQ3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS3" t="n">
         <v>7.6</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>8</v>
       </c>
       <c r="BT3" t="n">
         <v>11</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-16 00:31:41</t>
+          <t>2026-06-16 02:39:49</t>
         </is>
       </c>
     </row>
@@ -1365,97 +1365,97 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="G4" t="n">
-        <v>2.7</v>
+        <v>2.58</v>
       </c>
       <c r="H4" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="I4" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="J4" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L4" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="M4" t="n">
         <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="O4" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="P4" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="R4" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S4" t="n">
-        <v>2.58</v>
+        <v>3</v>
       </c>
       <c r="T4" t="n">
         <v>1.69</v>
       </c>
       <c r="U4" t="n">
-        <v>1.11</v>
+        <v>2.3</v>
       </c>
       <c r="V4" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W4" t="n">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="X4" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z4" t="n">
         <v>22</v>
       </c>
-      <c r="Y4" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>26</v>
-      </c>
       <c r="AA4" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AB4" t="n">
         <v>13.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="AD4" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AE4" t="n">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="AF4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AG4" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="AJ4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AK4" t="n">
         <v>27</v>
@@ -1464,121 +1464,121 @@
         <v>36</v>
       </c>
       <c r="AM4" t="n">
-        <v>200</v>
+        <v>75</v>
       </c>
       <c r="AN4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.35</v>
+        <v>6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.8</v>
+        <v>5.8</v>
       </c>
       <c r="AR4" t="n">
-        <v>3.4</v>
+        <v>6.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.55</v>
+        <v>7.6</v>
       </c>
       <c r="AT4" t="n">
-        <v>4.1</v>
+        <v>7</v>
       </c>
       <c r="AU4" t="n">
         <v>4.9</v>
       </c>
       <c r="AV4" t="n">
-        <v>3.8</v>
+        <v>5.7</v>
       </c>
       <c r="AW4" t="n">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="AX4" t="n">
-        <v>3.35</v>
+        <v>6</v>
       </c>
       <c r="AY4" t="n">
-        <v>4</v>
+        <v>6.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>3.25</v>
+        <v>5.9</v>
       </c>
       <c r="BA4" t="n">
-        <v>3.65</v>
+        <v>7.4</v>
       </c>
       <c r="BB4" t="n">
-        <v>3.5</v>
+        <v>7.2</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.4</v>
+        <v>6.8</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE4" t="n">
-        <v>3.65</v>
+        <v>8.4</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.55</v>
+        <v>6</v>
       </c>
       <c r="BG4" t="n">
-        <v>4</v>
+        <v>6.6</v>
       </c>
       <c r="BH4" t="n">
         <v>3.9</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="BJ4" t="n">
         <v>9.4</v>
       </c>
       <c r="BK4" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN4" t="n">
         <v>5.9</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.8</v>
+        <v>3.75</v>
       </c>
       <c r="BP4" t="n">
         <v>19</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BR4" t="n">
         <v>30</v>
       </c>
       <c r="BS4" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BT4" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.8</v>
+        <v>3.95</v>
       </c>
       <c r="BV4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BW4" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BX4" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BY4" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-16 00:31:41</t>
+          <t>2026-06-16 02:39:49</t>
         </is>
       </c>
     </row>
@@ -1619,82 +1619,82 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="G5" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="H5" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="I5" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="J5" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="K5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N5" t="n">
         <v>5.6</v>
       </c>
-      <c r="L5" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N5" t="n">
-        <v>4.8</v>
-      </c>
       <c r="O5" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P5" t="n">
-        <v>2.28</v>
+        <v>2.56</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="S5" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="T5" t="n">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="U5" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="V5" t="n">
         <v>3</v>
       </c>
       <c r="W5" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X5" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="Y5" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AA5" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AB5" t="n">
         <v>75</v>
       </c>
       <c r="AC5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AD5" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AE5" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AF5" t="n">
         <v>160</v>
@@ -1703,13 +1703,13 @@
         <v>75</v>
       </c>
       <c r="AH5" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AI5" t="n">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="AJ5" t="n">
-        <v>310</v>
+        <v>250</v>
       </c>
       <c r="AK5" t="n">
         <v>260</v>
@@ -1718,121 +1718,121 @@
         <v>230</v>
       </c>
       <c r="AM5" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="AN5" t="n">
-        <v>170</v>
+        <v>120</v>
       </c>
       <c r="AO5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>6.2</v>
       </c>
-      <c r="AP5" t="n">
-        <v>19</v>
-      </c>
-      <c r="AQ5" t="n">
+      <c r="BA5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>9</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ5" t="n">
         <v>8.4</v>
       </c>
-      <c r="AR5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>13</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BC5" t="n">
+      <c r="BR5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS5" t="n">
         <v>8.4</v>
       </c>
-      <c r="BD5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>15</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>12</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BT5" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="BV5" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BW5" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BX5" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BY5" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-16 00:31:41</t>
+          <t>2026-06-16 02:39:49</t>
         </is>
       </c>
     </row>
@@ -1873,230 +1873,230 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.6</v>
+        <v>1.84</v>
       </c>
       <c r="G6" t="n">
-        <v>6</v>
+        <v>1.93</v>
       </c>
       <c r="H6" t="n">
-        <v>2.8</v>
+        <v>4.4</v>
       </c>
       <c r="I6" t="n">
-        <v>44</v>
+        <v>5.3</v>
       </c>
       <c r="J6" t="n">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="K6" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M6" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>1.3</v>
+        <v>3.7</v>
       </c>
       <c r="O6" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="P6" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="R6" t="n">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="S6" t="n">
-        <v>1.33</v>
+        <v>3.6</v>
       </c>
       <c r="T6" t="n">
-        <v>1.11</v>
+        <v>1.87</v>
       </c>
       <c r="U6" t="n">
-        <v>1.11</v>
+        <v>1.96</v>
       </c>
       <c r="V6" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="W6" t="n">
-        <v>1.65</v>
+        <v>2.06</v>
       </c>
       <c r="X6" t="n">
-        <v>950</v>
+        <v>14.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>950</v>
+        <v>17.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="AA6" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB6" t="n">
-        <v>950</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC6" t="n">
-        <v>500</v>
+        <v>9</v>
       </c>
       <c r="AD6" t="n">
-        <v>950</v>
+        <v>21</v>
       </c>
       <c r="AE6" t="n">
         <v>500</v>
       </c>
       <c r="AF6" t="n">
-        <v>500</v>
+        <v>11.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>950</v>
+        <v>10.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>950</v>
+        <v>22</v>
       </c>
       <c r="AI6" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AJ6" t="n">
-        <v>900</v>
+        <v>21</v>
       </c>
       <c r="AK6" t="n">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="AL6" t="n">
-        <v>500</v>
+        <v>42</v>
       </c>
       <c r="AM6" t="n">
         <v>580</v>
       </c>
       <c r="AN6" t="n">
-        <v>500</v>
+        <v>14</v>
       </c>
       <c r="AO6" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.06</v>
+        <v>6.2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.07</v>
+        <v>6</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.07</v>
+        <v>7.4</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.07</v>
+        <v>8.6</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.07</v>
+        <v>4.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.07</v>
+        <v>6.4</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.07</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.07</v>
+        <v>5.1</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.07</v>
+        <v>4.9</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.07</v>
+        <v>6.4</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.07</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.07</v>
+        <v>6.4</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.07</v>
+        <v>6.4</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.07</v>
+        <v>7.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.07</v>
+        <v>8.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.07</v>
+        <v>5.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.55</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH6" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.04</v>
+        <v>2.78</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.04</v>
+        <v>2.56</v>
       </c>
       <c r="BN6" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="BP6" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BR6" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BT6" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BV6" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BX6" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-16 00:31:41</t>
+          <t>2026-06-16 02:39:49</t>
         </is>
       </c>
     </row>
@@ -2127,230 +2127,230 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="G7" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="H7" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="I7" t="n">
         <v>2.04</v>
       </c>
       <c r="J7" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K7" t="n">
         <v>4.1</v>
       </c>
       <c r="L7" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="M7" t="n">
         <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="O7" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P7" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="R7" t="n">
         <v>1.34</v>
       </c>
       <c r="S7" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="T7" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U7" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V7" t="n">
         <v>1.96</v>
       </c>
       <c r="W7" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="X7" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD7" t="n">
         <v>11</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>15</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>24</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>12.5</v>
       </c>
       <c r="AE7" t="n">
         <v>23</v>
       </c>
       <c r="AF7" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AG7" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AI7" t="n">
         <v>40</v>
       </c>
       <c r="AJ7" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AK7" t="n">
         <v>150</v>
       </c>
       <c r="AL7" t="n">
-        <v>160</v>
+        <v>65</v>
       </c>
       <c r="AM7" t="n">
         <v>580</v>
       </c>
       <c r="AN7" t="n">
-        <v>240</v>
+        <v>500</v>
       </c>
       <c r="AO7" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AP7" t="n">
-        <v>10.5</v>
+        <v>6</v>
       </c>
       <c r="AQ7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BA7" t="n">
         <v>8</v>
       </c>
-      <c r="AR7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>20</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>14</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BB7" t="n">
-        <v>4.9</v>
+        <v>9</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.7</v>
+        <v>8.4</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.7</v>
+        <v>8.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.7</v>
+        <v>8.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>11.5</v>
+        <v>6.2</v>
       </c>
       <c r="BH7" t="n">
         <v>3.55</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.1</v>
+        <v>2.74</v>
       </c>
       <c r="BJ7" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>11</v>
+        <v>2.64</v>
       </c>
       <c r="BN7" t="n">
         <v>7.8</v>
       </c>
       <c r="BO7" t="n">
-        <v>5.7</v>
+        <v>4.5</v>
       </c>
       <c r="BP7" t="n">
         <v>36</v>
       </c>
       <c r="BQ7" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BR7" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS7" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT7" t="n">
         <v>4.9</v>
       </c>
       <c r="BU7" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="BV7" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BW7" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BX7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BY7" t="n">
-        <v>8.6</v>
+        <v>2.46</v>
       </c>
       <c r="BZ7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="CA7" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-16 00:31:41</t>
+          <t>2026-06-16 02:39:49</t>
         </is>
       </c>
     </row>
@@ -2381,220 +2381,220 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="G8" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="H8" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I8" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="J8" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="K8" t="n">
         <v>5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="M8" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O8" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P8" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="R8" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="S8" t="n">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="T8" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="U8" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="V8" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W8" t="n">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="X8" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="Y8" t="n">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="Z8" t="n">
-        <v>220</v>
+        <v>500</v>
       </c>
       <c r="AA8" t="n">
         <v>700</v>
       </c>
       <c r="AB8" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AE8" t="n">
         <v>700</v>
       </c>
       <c r="AF8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG8" t="n">
         <v>10.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AI8" t="n">
         <v>700</v>
       </c>
       <c r="AJ8" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AK8" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AL8" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AM8" t="n">
         <v>700</v>
       </c>
       <c r="AN8" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="AO8" t="n">
         <v>700</v>
       </c>
       <c r="AP8" t="n">
-        <v>15</v>
+        <v>7.4</v>
       </c>
       <c r="AQ8" t="n">
-        <v>18</v>
+        <v>7.8</v>
       </c>
       <c r="AR8" t="n">
-        <v>7</v>
+        <v>9.4</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="AT8" t="n">
-        <v>8.800000000000001</v>
+        <v>5.4</v>
       </c>
       <c r="AU8" t="n">
-        <v>8.4</v>
+        <v>5.8</v>
       </c>
       <c r="AV8" t="n">
-        <v>18.5</v>
+        <v>7.8</v>
       </c>
       <c r="AW8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AZ8" t="n">
         <v>7.2</v>
       </c>
-      <c r="AX8" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>16</v>
-      </c>
       <c r="BA8" t="n">
-        <v>7</v>
+        <v>9.6</v>
       </c>
       <c r="BB8" t="n">
-        <v>11.5</v>
+        <v>6.2</v>
       </c>
       <c r="BC8" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BD8" t="n">
-        <v>18</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE8" t="n">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="BF8" t="n">
-        <v>6</v>
+        <v>4.3</v>
       </c>
       <c r="BG8" t="n">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="BH8" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="BJ8" t="n">
         <v>10.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>3.25</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN8" t="n">
         <v>4.3</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="BP8" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BT8" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>3.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>3.15</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-16 00:31:41</t>
+          <t>2026-06-16 02:39:49</t>
         </is>
       </c>
     </row>
@@ -2635,58 +2635,58 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="G9" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="H9" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I9" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="J9" t="n">
         <v>3.75</v>
       </c>
       <c r="K9" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L9" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="M9" t="n">
         <v>1.04</v>
       </c>
       <c r="N9" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="O9" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P9" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="R9" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="S9" t="n">
-        <v>2.58</v>
+        <v>2.72</v>
       </c>
       <c r="T9" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="U9" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="V9" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W9" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="X9" t="n">
         <v>40</v>
@@ -2698,19 +2698,19 @@
         <v>70</v>
       </c>
       <c r="AA9" t="n">
-        <v>900</v>
+        <v>150</v>
       </c>
       <c r="AB9" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AC9" t="n">
         <v>10.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>20</v>
+        <v>14.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="AF9" t="n">
         <v>19.5</v>
@@ -2740,31 +2740,31 @@
         <v>12.5</v>
       </c>
       <c r="AO9" t="n">
-        <v>25</v>
+        <v>600</v>
       </c>
       <c r="AP9" t="n">
-        <v>10.5</v>
+        <v>19</v>
       </c>
       <c r="AQ9" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AR9" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AS9" t="n">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT9" t="n">
         <v>11.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="AV9" t="n">
         <v>12.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="AX9" t="n">
         <v>14.5</v>
@@ -2776,89 +2776,89 @@
         <v>13</v>
       </c>
       <c r="BA9" t="n">
-        <v>7.6</v>
+        <v>32</v>
       </c>
       <c r="BB9" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BC9" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="BD9" t="n">
-        <v>14.5</v>
+        <v>25</v>
       </c>
       <c r="BE9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BF9" t="n">
         <v>10.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="BH9" t="n">
         <v>4.1</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BJ9" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BN9" t="n">
         <v>5.5</v>
       </c>
       <c r="BO9" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BP9" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BT9" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BX9" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-16 00:31:41</t>
+          <t>2026-06-16 02:39:49</t>
         </is>
       </c>
     </row>
@@ -2889,166 +2889,166 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="G10" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="H10" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="I10" t="n">
         <v>3.1</v>
       </c>
-      <c r="I10" t="n">
-        <v>3.3</v>
-      </c>
       <c r="J10" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K10" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L10" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="M10" t="n">
         <v>1.04</v>
       </c>
       <c r="N10" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O10" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="P10" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="R10" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S10" t="n">
-        <v>2.66</v>
+        <v>2.82</v>
       </c>
       <c r="T10" t="n">
         <v>1.63</v>
       </c>
       <c r="U10" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="V10" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="W10" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="X10" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="Y10" t="n">
-        <v>500</v>
+        <v>29</v>
       </c>
       <c r="Z10" t="n">
         <v>500</v>
       </c>
       <c r="AA10" t="n">
-        <v>900</v>
+        <v>120</v>
       </c>
       <c r="AB10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AC10" t="n">
         <v>12</v>
       </c>
       <c r="AD10" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AE10" t="n">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AF10" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AH10" t="n">
-        <v>23</v>
+        <v>14.5</v>
       </c>
       <c r="AI10" t="n">
         <v>500</v>
       </c>
       <c r="AJ10" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AK10" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AL10" t="n">
         <v>32</v>
       </c>
       <c r="AM10" t="n">
-        <v>500</v>
+        <v>320</v>
       </c>
       <c r="AN10" t="n">
-        <v>38</v>
+        <v>14.5</v>
       </c>
       <c r="AO10" t="n">
-        <v>500</v>
+        <v>28</v>
       </c>
       <c r="AP10" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="AQ10" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR10" t="n">
         <v>15</v>
       </c>
       <c r="AS10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT10" t="n">
         <v>10</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>11</v>
       </c>
       <c r="AU10" t="n">
         <v>7.8</v>
       </c>
       <c r="AV10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW10" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="AX10" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AY10" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ10" t="n">
-        <v>12.5</v>
+        <v>8.6</v>
       </c>
       <c r="BA10" t="n">
         <v>24</v>
       </c>
       <c r="BB10" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="BC10" t="n">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="BD10" t="n">
         <v>23</v>
       </c>
       <c r="BE10" t="n">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BF10" t="n">
         <v>11</v>
       </c>
       <c r="BG10" t="n">
-        <v>8.4</v>
+        <v>19</v>
       </c>
       <c r="BH10" t="n">
         <v>4</v>
@@ -3066,10 +3066,10 @@
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.17</v>
+        <v>2.32</v>
       </c>
       <c r="BN10" t="n">
-        <v>8.4</v>
+        <v>5.6</v>
       </c>
       <c r="BO10" t="n">
         <v>4.8</v>
@@ -3078,16 +3078,16 @@
         <v>20</v>
       </c>
       <c r="BQ10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.56</v>
+        <v>2.12</v>
       </c>
       <c r="BT10" t="n">
-        <v>970</v>
+        <v>6.4</v>
       </c>
       <c r="BU10" t="n">
         <v>5.3</v>
@@ -3096,13 +3096,13 @@
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.11</v>
+        <v>2.1</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.17</v>
+        <v>2.16</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-16 00:31:41</t>
+          <t>2026-06-16 02:39:49</t>
         </is>
       </c>
     </row>
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="G11" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="H11" t="n">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="I11" t="n">
-        <v>10.5</v>
+        <v>6.4</v>
       </c>
       <c r="J11" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="K11" t="n">
-        <v>9.800000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="L11" t="n">
         <v>1.15</v>
@@ -3167,145 +3167,145 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>4.5</v>
+        <v>13</v>
       </c>
       <c r="O11" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="P11" t="n">
-        <v>2.56</v>
+        <v>5.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="R11" t="n">
-        <v>2.56</v>
+        <v>2.72</v>
       </c>
       <c r="S11" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="T11" t="n">
         <v>1.31</v>
       </c>
-      <c r="T11" t="n">
-        <v>1.11</v>
-      </c>
       <c r="U11" t="n">
-        <v>2.66</v>
+        <v>3.65</v>
       </c>
       <c r="V11" t="n">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="W11" t="n">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AA11" t="n">
         <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>950</v>
+        <v>100</v>
       </c>
       <c r="AC11" t="n">
         <v>950</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>660</v>
       </c>
       <c r="AF11" t="n">
-        <v>500</v>
+        <v>38</v>
       </c>
       <c r="AG11" t="n">
-        <v>950</v>
+        <v>16.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ11" t="n">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="AK11" t="n">
-        <v>500</v>
+        <v>17</v>
       </c>
       <c r="AL11" t="n">
-        <v>500</v>
+        <v>30</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AN11" t="n">
-        <v>500</v>
+        <v>3.4</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.2</v>
+        <v>32</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.2</v>
+        <v>4.2</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.2</v>
+        <v>4.2</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.17</v>
+        <v>20</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.16</v>
+        <v>12.5</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.2</v>
+        <v>18.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.2</v>
+        <v>4.3</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.16</v>
+        <v>15</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.18</v>
+        <v>11</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.2</v>
+        <v>11.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.2</v>
+        <v>23</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.18</v>
+        <v>15.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.18</v>
+        <v>11</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.15</v>
+        <v>14.5</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.2</v>
+        <v>21</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.17</v>
+        <v>3.1</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.55</v>
+        <v>18</v>
       </c>
       <c r="BH11" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BI11" t="n">
         <v>5.5</v>
@@ -3314,13 +3314,13 @@
         <v>9</v>
       </c>
       <c r="BK11" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN11" t="n">
         <v>5.7</v>
@@ -3332,41 +3332,41 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BR11" t="n">
         <v>14.5</v>
       </c>
       <c r="BS11" t="n">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT11" t="n">
         <v>11.5</v>
       </c>
       <c r="BU11" t="n">
-        <v>9.4</v>
+        <v>7.4</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BX11" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BZ11" t="n">
         <v>6.6</v>
       </c>
       <c r="CA11" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-16 00:31:41</t>
+          <t>2026-06-16 02:39:49</t>
         </is>
       </c>
     </row>
@@ -3397,58 +3397,58 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="G12" t="n">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="I12" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J12" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="K12" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="L12" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="M12" t="n">
         <v>1.02</v>
       </c>
       <c r="N12" t="n">
+        <v>8</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="P12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U12" t="n">
         <v>3.05</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="P12" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2.66</v>
       </c>
       <c r="V12" t="n">
         <v>1.43</v>
       </c>
       <c r="W12" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="X12" t="n">
         <v>950</v>
@@ -3460,16 +3460,16 @@
         <v>500</v>
       </c>
       <c r="AA12" t="n">
-        <v>900</v>
+        <v>290</v>
       </c>
       <c r="AB12" t="n">
         <v>950</v>
       </c>
       <c r="AC12" t="n">
-        <v>500</v>
+        <v>42</v>
       </c>
       <c r="AD12" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AE12" t="n">
         <v>500</v>
@@ -3478,19 +3478,19 @@
         <v>500</v>
       </c>
       <c r="AG12" t="n">
-        <v>970</v>
+        <v>29</v>
       </c>
       <c r="AH12" t="n">
-        <v>500</v>
+        <v>42</v>
       </c>
       <c r="AI12" t="n">
         <v>500</v>
       </c>
       <c r="AJ12" t="n">
-        <v>900</v>
+        <v>140</v>
       </c>
       <c r="AK12" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AL12" t="n">
         <v>500</v>
@@ -3499,128 +3499,128 @@
         <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AO12" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.61</v>
+        <v>4.9</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.58</v>
+        <v>7</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.58</v>
+        <v>7.4</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.56</v>
+        <v>6.6</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.55</v>
+        <v>6.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.5</v>
+        <v>8.4</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.58</v>
+        <v>7.2</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.56</v>
+        <v>6.8</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.48</v>
+        <v>7</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.52</v>
+        <v>7.6</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.57</v>
+        <v>7</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.59</v>
+        <v>7.4</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.56</v>
+        <v>6.4</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.55</v>
+        <v>6.8</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.6</v>
+        <v>6</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.18</v>
+        <v>4.3</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.05</v>
+        <v>5.6</v>
       </c>
       <c r="BH12" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BJ12" t="n">
         <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.04</v>
+        <v>1.96</v>
       </c>
       <c r="BN12" t="n">
         <v>1000</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BP12" t="n">
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BT12" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BU12" t="n">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-16 00:31:41</t>
+          <t>2026-06-16 02:39:49</t>
         </is>
       </c>
     </row>
@@ -3651,55 +3651,55 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="G13" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="H13" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="I13" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="J13" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K13" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="L13" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="M13" t="n">
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="P13" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="R13" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="S13" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="T13" t="n">
         <v>1.35</v>
       </c>
       <c r="U13" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="V13" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="W13" t="n">
         <v>1.43</v>
@@ -3717,13 +3717,13 @@
         <v>36</v>
       </c>
       <c r="AB13" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AC13" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE13" t="n">
         <v>20</v>
@@ -3744,13 +3744,13 @@
         <v>120</v>
       </c>
       <c r="AK13" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL13" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AM13" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AN13" t="n">
         <v>12</v>
@@ -3759,7 +3759,7 @@
         <v>6.6</v>
       </c>
       <c r="AP13" t="n">
-        <v>8.4</v>
+        <v>20</v>
       </c>
       <c r="AQ13" t="n">
         <v>20</v>
@@ -3768,10 +3768,10 @@
         <v>20</v>
       </c>
       <c r="AS13" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AT13" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AU13" t="n">
         <v>12</v>
@@ -3783,7 +3783,7 @@
         <v>16</v>
       </c>
       <c r="AX13" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AY13" t="n">
         <v>14</v>
@@ -3795,10 +3795,10 @@
         <v>18</v>
       </c>
       <c r="BB13" t="n">
+        <v>42</v>
+      </c>
+      <c r="BC13" t="n">
         <v>23</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>18</v>
       </c>
       <c r="BD13" t="n">
         <v>17</v>
@@ -3828,7 +3828,7 @@
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN13" t="n">
         <v>8</v>
@@ -3840,10 +3840,10 @@
         <v>20</v>
       </c>
       <c r="BQ13" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BR13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BS13" t="n">
         <v>6.8</v>
@@ -3858,7 +3858,7 @@
         <v>13.5</v>
       </c>
       <c r="BW13" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BX13" t="n">
         <v>17.5</v>
@@ -3870,11 +3870,11 @@
         <v>9.4</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-16 00:31:41</t>
+          <t>2026-06-16 02:39:49</t>
         </is>
       </c>
     </row>
@@ -3905,43 +3905,43 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="G14" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="H14" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="I14" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J14" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="K14" t="n">
         <v>4.1</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M14" t="n">
         <v>1.09</v>
       </c>
       <c r="N14" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="O14" t="n">
         <v>1.39</v>
       </c>
       <c r="P14" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R14" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="S14" t="n">
         <v>4.1</v>
@@ -3953,10 +3953,10 @@
         <v>1.75</v>
       </c>
       <c r="V14" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W14" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="X14" t="n">
         <v>12.5</v>
@@ -3983,7 +3983,7 @@
         <v>160</v>
       </c>
       <c r="AF14" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG14" t="n">
         <v>10.5</v>
@@ -3995,10 +3995,10 @@
         <v>150</v>
       </c>
       <c r="AJ14" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AK14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL14" t="n">
         <v>50</v>
@@ -4007,7 +4007,7 @@
         <v>220</v>
       </c>
       <c r="AN14" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AO14" t="n">
         <v>250</v>
@@ -4019,10 +4019,10 @@
         <v>16</v>
       </c>
       <c r="AR14" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AS14" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AT14" t="n">
         <v>6</v>
@@ -4034,7 +4034,7 @@
         <v>21</v>
       </c>
       <c r="AW14" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AX14" t="n">
         <v>7.2</v>
@@ -4046,7 +4046,7 @@
         <v>22</v>
       </c>
       <c r="BA14" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BB14" t="n">
         <v>13.5</v>
@@ -4055,16 +4055,16 @@
         <v>17</v>
       </c>
       <c r="BD14" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE14" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BF14" t="n">
+        <v>12</v>
+      </c>
+      <c r="BG14" t="n">
         <v>10.5</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>9.800000000000001</v>
       </c>
       <c r="BH14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-16 00:31:41</t>
+          <t>2026-06-16 02:39:49</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-16.xlsx
@@ -857,58 +857,58 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="G2" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H2" t="n">
         <v>4.1</v>
       </c>
       <c r="I2" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J2" t="n">
         <v>3.6</v>
       </c>
       <c r="K2" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="O2" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="P2" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="R2" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="T2" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="U2" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="V2" t="n">
         <v>1.28</v>
       </c>
       <c r="W2" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="X2" t="n">
         <v>27</v>
@@ -923,7 +923,7 @@
         <v>900</v>
       </c>
       <c r="AB2" t="n">
-        <v>9</v>
+        <v>14.5</v>
       </c>
       <c r="AC2" t="n">
         <v>14</v>
@@ -938,7 +938,7 @@
         <v>40</v>
       </c>
       <c r="AG2" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="AH2" t="n">
         <v>950</v>
@@ -962,7 +962,7 @@
         <v>55</v>
       </c>
       <c r="AO2" t="n">
-        <v>600</v>
+        <v>70</v>
       </c>
       <c r="AP2" t="n">
         <v>7.6</v>
@@ -974,7 +974,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.199999999999999</v>
+        <v>5</v>
       </c>
       <c r="AT2" t="n">
         <v>5.1</v>
@@ -986,7 +986,7 @@
         <v>7.8</v>
       </c>
       <c r="AW2" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AX2" t="n">
         <v>6.2</v>
@@ -998,7 +998,7 @@
         <v>9</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BB2" t="n">
         <v>10.5</v>
@@ -1007,46 +1007,46 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BD2" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BE2" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BG2" t="n">
-        <v>7.8</v>
+        <v>4.1</v>
       </c>
       <c r="BH2" t="n">
         <v>3.4</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.72</v>
+        <v>2.82</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BN2" t="n">
         <v>4.8</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
@@ -1058,13 +1058,13 @@
         <v>8</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-16 02:39:49</t>
+          <t>2026-06-16 04:48:14</t>
         </is>
       </c>
     </row>
@@ -1117,16 +1117,16 @@
         <v>1.63</v>
       </c>
       <c r="H3" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="I3" t="n">
         <v>8</v>
       </c>
       <c r="J3" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L3" t="n">
         <v>1.39</v>
@@ -1135,22 +1135,22 @@
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="O3" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="P3" t="n">
         <v>2.02</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="R3" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S3" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T3" t="n">
         <v>1.93</v>
@@ -1195,7 +1195,7 @@
         <v>10.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AI3" t="n">
         <v>700</v>
@@ -1216,25 +1216,25 @@
         <v>9.4</v>
       </c>
       <c r="AO3" t="n">
-        <v>700</v>
+        <v>180</v>
       </c>
       <c r="AP3" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AQ3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AU3" t="n">
         <v>6.8</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>5.2</v>
       </c>
       <c r="AV3" t="n">
         <v>7.2</v>
@@ -1243,13 +1243,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AX3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY3" t="n">
         <v>5.1</v>
       </c>
-      <c r="AY3" t="n">
-        <v>5</v>
-      </c>
       <c r="AZ3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BA3" t="n">
         <v>8.800000000000001</v>
@@ -1258,7 +1258,7 @@
         <v>6.8</v>
       </c>
       <c r="BC3" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BD3" t="n">
         <v>7.6</v>
@@ -1267,7 +1267,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BG3" t="n">
         <v>9</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-16 02:39:49</t>
+          <t>2026-06-16 04:48:14</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="G4" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="I4" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J4" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K4" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="L4" t="n">
         <v>1.35</v>
@@ -1392,16 +1392,16 @@
         <v>4.4</v>
       </c>
       <c r="O4" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P4" t="n">
         <v>2.16</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="R4" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S4" t="n">
         <v>3</v>
@@ -1410,7 +1410,7 @@
         <v>1.69</v>
       </c>
       <c r="U4" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="V4" t="n">
         <v>1.48</v>
@@ -1419,13 +1419,13 @@
         <v>1.64</v>
       </c>
       <c r="X4" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="Y4" t="n">
         <v>14.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA4" t="n">
         <v>48</v>
@@ -1467,7 +1467,7 @@
         <v>75</v>
       </c>
       <c r="AN4" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AO4" t="n">
         <v>25</v>
@@ -1476,55 +1476,55 @@
         <v>6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="AR4" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.6</v>
+        <v>22</v>
       </c>
       <c r="AT4" t="n">
         <v>7</v>
       </c>
       <c r="AU4" t="n">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>5.7</v>
+        <v>11</v>
       </c>
       <c r="AW4" t="n">
         <v>7</v>
       </c>
       <c r="AX4" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AY4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>21</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>19</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>19</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>32</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BG4" t="n">
         <v>6.4</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>6</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>6.6</v>
       </c>
       <c r="BH4" t="n">
         <v>3.9</v>
@@ -1542,7 +1542,7 @@
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN4" t="n">
         <v>5.9</v>
@@ -1554,10 +1554,10 @@
         <v>19</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BS4" t="n">
         <v>7.6</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-16 02:39:49</t>
+          <t>2026-06-16 04:48:14</t>
         </is>
       </c>
     </row>
@@ -1619,82 +1619,82 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="G5" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="I5" t="n">
         <v>1.48</v>
       </c>
       <c r="J5" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K5" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="L5" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="M5" t="n">
         <v>1.03</v>
       </c>
       <c r="N5" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="O5" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="P5" t="n">
-        <v>2.56</v>
+        <v>2.76</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="R5" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="S5" t="n">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="T5" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="U5" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="V5" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="W5" t="n">
         <v>1.13</v>
       </c>
       <c r="X5" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="Y5" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA5" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AB5" t="n">
         <v>75</v>
       </c>
       <c r="AC5" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AE5" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AF5" t="n">
         <v>160</v>
@@ -1703,13 +1703,13 @@
         <v>75</v>
       </c>
       <c r="AH5" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AI5" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AJ5" t="n">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="AK5" t="n">
         <v>260</v>
@@ -1718,76 +1718,76 @@
         <v>230</v>
       </c>
       <c r="AM5" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AN5" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="AO5" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.4</v>
+        <v>18.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.7</v>
+        <v>7.4</v>
       </c>
       <c r="AS5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV5" t="n">
         <v>5.1</v>
       </c>
-      <c r="AT5" t="n">
+      <c r="AW5" t="n">
         <v>6.6</v>
       </c>
-      <c r="AU5" t="n">
+      <c r="AX5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BH5" t="n">
         <v>5</v>
       </c>
-      <c r="AV5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BI5" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="BJ5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK5" t="n">
         <v>5.2</v>
@@ -1796,19 +1796,19 @@
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN5" t="n">
         <v>11.5</v>
       </c>
       <c r="BO5" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
@@ -1817,19 +1817,19 @@
         <v>8.4</v>
       </c>
       <c r="BT5" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="BV5" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BW5" t="n">
         <v>4.7</v>
       </c>
       <c r="BX5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BY5" t="n">
         <v>6.8</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-16 02:39:49</t>
+          <t>2026-06-16 04:48:14</t>
         </is>
       </c>
     </row>
@@ -1873,97 +1873,97 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="G6" t="n">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="H6" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="I6" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="J6" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="L6" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M6" t="n">
         <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="O6" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R6" t="n">
         <v>1.33</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.34</v>
       </c>
       <c r="S6" t="n">
         <v>3.6</v>
       </c>
       <c r="T6" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="U6" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V6" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W6" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="X6" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y6" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="Z6" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AA6" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB6" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AC6" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AE6" t="n">
         <v>500</v>
       </c>
       <c r="AF6" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG6" t="n">
         <v>10.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI6" t="n">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="AJ6" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AK6" t="n">
         <v>22</v>
@@ -1975,112 +1975,112 @@
         <v>580</v>
       </c>
       <c r="AN6" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AO6" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AP6" t="n">
         <v>6.2</v>
       </c>
       <c r="AQ6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BF6" t="n">
         <v>6</v>
       </c>
-      <c r="AR6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BG6" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="BJ6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="BN6" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="BP6" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BR6" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BS6" t="n">
         <v>7.6</v>
       </c>
       <c r="BT6" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU6" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BV6" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="BW6" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BX6" t="n">
         <v>55</v>
@@ -2089,14 +2089,14 @@
         <v>8.6</v>
       </c>
       <c r="BZ6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="CA6" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-16 02:39:49</t>
+          <t>2026-06-16 04:48:14</t>
         </is>
       </c>
     </row>
@@ -2127,19 +2127,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="G7" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="H7" t="n">
         <v>1.97</v>
       </c>
       <c r="I7" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K7" t="n">
         <v>4.1</v>
@@ -2151,16 +2151,16 @@
         <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O7" t="n">
         <v>1.32</v>
       </c>
       <c r="P7" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="R7" t="n">
         <v>1.34</v>
@@ -2169,16 +2169,16 @@
         <v>3.55</v>
       </c>
       <c r="T7" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="U7" t="n">
         <v>2.02</v>
       </c>
       <c r="V7" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="W7" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="X7" t="n">
         <v>15.5</v>
@@ -2193,7 +2193,7 @@
         <v>25</v>
       </c>
       <c r="AB7" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AC7" t="n">
         <v>8.6</v>
@@ -2235,19 +2235,19 @@
         <v>16</v>
       </c>
       <c r="AP7" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AR7" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AS7" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AT7" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AU7" t="n">
         <v>4.6</v>
@@ -2256,22 +2256,22 @@
         <v>5.2</v>
       </c>
       <c r="AW7" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AX7" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AY7" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AZ7" t="n">
         <v>6.6</v>
       </c>
       <c r="BA7" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BB7" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC7" t="n">
         <v>8.4</v>
@@ -2280,13 +2280,13 @@
         <v>8.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BF7" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BG7" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BH7" t="n">
         <v>3.55</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-16 02:39:49</t>
+          <t>2026-06-16 04:48:14</t>
         </is>
       </c>
     </row>
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="G8" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="H8" t="n">
         <v>6.2</v>
@@ -2405,34 +2405,34 @@
         <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O8" t="n">
         <v>1.22</v>
       </c>
       <c r="P8" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="R8" t="n">
         <v>1.52</v>
       </c>
       <c r="S8" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="T8" t="n">
         <v>1.78</v>
       </c>
       <c r="U8" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V8" t="n">
         <v>1.16</v>
       </c>
       <c r="W8" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="X8" t="n">
         <v>29</v>
@@ -2453,7 +2453,7 @@
         <v>11.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AE8" t="n">
         <v>700</v>
@@ -2486,28 +2486,28 @@
         <v>7</v>
       </c>
       <c r="AO8" t="n">
-        <v>700</v>
+        <v>110</v>
       </c>
       <c r="AP8" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AQ8" t="n">
         <v>7.8</v>
       </c>
       <c r="AR8" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS8" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AT8" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AU8" t="n">
         <v>5.8</v>
       </c>
       <c r="AV8" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AW8" t="n">
         <v>9.800000000000001</v>
@@ -2519,25 +2519,25 @@
         <v>5.8</v>
       </c>
       <c r="AZ8" t="n">
-        <v>7.2</v>
+        <v>9.6</v>
       </c>
       <c r="BA8" t="n">
         <v>9.6</v>
       </c>
       <c r="BB8" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BC8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BD8" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BE8" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF8" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BG8" t="n">
         <v>10</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-16 02:39:49</t>
+          <t>2026-06-16 04:48:14</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G9" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="H9" t="n">
         <v>3.35</v>
       </c>
       <c r="I9" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="J9" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="K9" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L9" t="n">
         <v>1.32</v>
@@ -2659,7 +2659,7 @@
         <v>1.04</v>
       </c>
       <c r="N9" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O9" t="n">
         <v>1.22</v>
@@ -2680,22 +2680,22 @@
         <v>1.58</v>
       </c>
       <c r="U9" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="V9" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W9" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="X9" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="Y9" t="n">
         <v>19.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="AA9" t="n">
         <v>150</v>
@@ -2704,13 +2704,13 @@
         <v>15</v>
       </c>
       <c r="AC9" t="n">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="AD9" t="n">
         <v>14.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AF9" t="n">
         <v>19.5</v>
@@ -2719,7 +2719,7 @@
         <v>11.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>18</v>
+        <v>14.5</v>
       </c>
       <c r="AI9" t="n">
         <v>95</v>
@@ -2731,70 +2731,70 @@
         <v>22</v>
       </c>
       <c r="AL9" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM9" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="AN9" t="n">
         <v>12.5</v>
       </c>
       <c r="AO9" t="n">
-        <v>600</v>
+        <v>25</v>
       </c>
       <c r="AP9" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS9" t="n">
-        <v>8.800000000000001</v>
+        <v>34</v>
       </c>
       <c r="AT9" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AV9" t="n">
         <v>12.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AX9" t="n">
         <v>14.5</v>
       </c>
       <c r="AY9" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ9" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BB9" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="BC9" t="n">
-        <v>12</v>
+        <v>18.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BE9" t="n">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="BF9" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BG9" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="BH9" t="n">
         <v>4.1</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-16 02:39:49</t>
+          <t>2026-06-16 04:48:14</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G10" t="n">
         <v>2.46</v>
@@ -2898,22 +2898,22 @@
         <v>3.05</v>
       </c>
       <c r="I10" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="J10" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K10" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L10" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M10" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O10" t="n">
         <v>1.23</v>
@@ -2925,10 +2925,10 @@
         <v>1.71</v>
       </c>
       <c r="R10" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="S10" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="T10" t="n">
         <v>1.63</v>
@@ -2940,13 +2940,13 @@
         <v>1.47</v>
       </c>
       <c r="W10" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="X10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y10" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="Z10" t="n">
         <v>500</v>
@@ -2955,22 +2955,22 @@
         <v>120</v>
       </c>
       <c r="AB10" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AC10" t="n">
         <v>12</v>
       </c>
       <c r="AD10" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AE10" t="n">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="AF10" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AG10" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH10" t="n">
         <v>14.5</v>
@@ -2979,37 +2979,37 @@
         <v>500</v>
       </c>
       <c r="AJ10" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AK10" t="n">
         <v>26</v>
       </c>
       <c r="AL10" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="AM10" t="n">
         <v>320</v>
       </c>
       <c r="AN10" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AO10" t="n">
         <v>28</v>
       </c>
       <c r="AP10" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>14.5</v>
+        <v>9.4</v>
       </c>
       <c r="AR10" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AT10" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU10" t="n">
         <v>7.8</v>
@@ -3021,16 +3021,16 @@
         <v>17.5</v>
       </c>
       <c r="AX10" t="n">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ10" t="n">
-        <v>8.6</v>
+        <v>12.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB10" t="n">
         <v>23</v>
@@ -3045,7 +3045,7 @@
         <v>11.5</v>
       </c>
       <c r="BF10" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BG10" t="n">
         <v>19</v>
@@ -3054,55 +3054,55 @@
         <v>4</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK10" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>2.32</v>
+        <v>12</v>
       </c>
       <c r="BN10" t="n">
         <v>5.6</v>
       </c>
       <c r="BO10" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BP10" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>2.12</v>
+        <v>10</v>
       </c>
       <c r="BT10" t="n">
         <v>6.4</v>
       </c>
       <c r="BU10" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>2.1</v>
+        <v>9.4</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.16</v>
+        <v>10.5</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-16 02:39:49</t>
+          <t>2026-06-16 04:48:14</t>
         </is>
       </c>
     </row>
@@ -3149,16 +3149,16 @@
         <v>1.55</v>
       </c>
       <c r="H11" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="I11" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J11" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="K11" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L11" t="n">
         <v>1.15</v>
@@ -3173,22 +3173,22 @@
         <v>1.06</v>
       </c>
       <c r="P11" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Q11" t="n">
         <v>1.22</v>
       </c>
       <c r="R11" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="S11" t="n">
         <v>1.54</v>
       </c>
       <c r="T11" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="U11" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="V11" t="n">
         <v>1.19</v>
@@ -3218,13 +3218,13 @@
         <v>100</v>
       </c>
       <c r="AE11" t="n">
-        <v>660</v>
+        <v>730</v>
       </c>
       <c r="AF11" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AG11" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH11" t="n">
         <v>970</v>
@@ -3236,25 +3236,25 @@
         <v>80</v>
       </c>
       <c r="AK11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL11" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AM11" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AN11" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="AO11" t="n">
         <v>42</v>
       </c>
       <c r="AP11" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AQ11" t="n">
-        <v>32</v>
+        <v>4.2</v>
       </c>
       <c r="AR11" t="n">
         <v>4.2</v>
@@ -3263,58 +3263,58 @@
         <v>4.2</v>
       </c>
       <c r="AT11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU11" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AV11" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AX11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY11" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BA11" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="BB11" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BC11" t="n">
         <v>11</v>
       </c>
       <c r="BD11" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BE11" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="BF11" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BG11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BH11" t="n">
         <v>7.4</v>
       </c>
       <c r="BI11" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BJ11" t="n">
         <v>9</v>
       </c>
       <c r="BK11" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
@@ -3332,19 +3332,19 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="BR11" t="n">
         <v>14.5</v>
       </c>
       <c r="BS11" t="n">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="BT11" t="n">
         <v>11.5</v>
       </c>
       <c r="BU11" t="n">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-16 02:39:49</t>
+          <t>2026-06-16 04:48:14</t>
         </is>
       </c>
     </row>
@@ -3406,10 +3406,10 @@
         <v>3.15</v>
       </c>
       <c r="I12" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="J12" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K12" t="n">
         <v>4.4</v>
@@ -3436,19 +3436,19 @@
         <v>2</v>
       </c>
       <c r="S12" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="T12" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="U12" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="V12" t="n">
         <v>1.43</v>
       </c>
       <c r="W12" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="X12" t="n">
         <v>950</v>
@@ -3463,10 +3463,10 @@
         <v>290</v>
       </c>
       <c r="AB12" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AC12" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AD12" t="n">
         <v>970</v>
@@ -3478,16 +3478,16 @@
         <v>500</v>
       </c>
       <c r="AG12" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="AH12" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="AI12" t="n">
         <v>500</v>
       </c>
       <c r="AJ12" t="n">
-        <v>140</v>
+        <v>900</v>
       </c>
       <c r="AK12" t="n">
         <v>65</v>
@@ -3499,25 +3499,25 @@
         <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="AO12" t="n">
-        <v>970</v>
+        <v>600</v>
       </c>
       <c r="AP12" t="n">
-        <v>4.9</v>
+        <v>3.8</v>
       </c>
       <c r="AQ12" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AR12" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AS12" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AT12" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AU12" t="n">
         <v>6.2</v>
@@ -3526,10 +3526,10 @@
         <v>8.4</v>
       </c>
       <c r="AW12" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX12" t="n">
         <v>7.2</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>6.8</v>
       </c>
       <c r="AY12" t="n">
         <v>7</v>
@@ -3538,31 +3538,31 @@
         <v>7.6</v>
       </c>
       <c r="BA12" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BB12" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BC12" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BD12" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BE12" t="n">
-        <v>6</v>
+        <v>3.8</v>
       </c>
       <c r="BF12" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BH12" t="n">
         <v>5.7</v>
       </c>
       <c r="BI12" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BJ12" t="n">
         <v>1000</v>
@@ -3574,7 +3574,7 @@
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.96</v>
+        <v>1.77</v>
       </c>
       <c r="BN12" t="n">
         <v>1000</v>
@@ -3586,16 +3586,16 @@
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BT12" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BU12" t="n">
         <v>5.5</v>
@@ -3604,23 +3604,23 @@
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>7.6</v>
+        <v>3.35</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-16 02:39:49</t>
+          <t>2026-06-16 04:48:14</t>
         </is>
       </c>
     </row>
@@ -3654,10 +3654,10 @@
         <v>3.15</v>
       </c>
       <c r="G13" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H13" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="I13" t="n">
         <v>2.16</v>
@@ -3678,31 +3678,31 @@
         <v>9.800000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="P13" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="Q13" t="n">
         <v>1.31</v>
       </c>
       <c r="R13" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="S13" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="T13" t="n">
         <v>1.35</v>
       </c>
       <c r="U13" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="V13" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="W13" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X13" t="n">
         <v>240</v>
@@ -3723,28 +3723,28 @@
         <v>14.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AF13" t="n">
         <v>42</v>
       </c>
       <c r="AG13" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AH13" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AJ13" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="AK13" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL13" t="n">
         <v>27</v>
@@ -3759,19 +3759,19 @@
         <v>6.6</v>
       </c>
       <c r="AP13" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="AQ13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR13" t="n">
         <v>20</v>
       </c>
       <c r="AS13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU13" t="n">
         <v>12</v>
@@ -3789,13 +3789,13 @@
         <v>14</v>
       </c>
       <c r="AZ13" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BA13" t="n">
         <v>18</v>
       </c>
       <c r="BB13" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="BC13" t="n">
         <v>23</v>
@@ -3804,13 +3804,13 @@
         <v>17</v>
       </c>
       <c r="BE13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BF13" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BG13" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BH13" t="n">
         <v>6.4</v>
@@ -3828,7 +3828,7 @@
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BN13" t="n">
         <v>8</v>
@@ -3840,10 +3840,10 @@
         <v>20</v>
       </c>
       <c r="BQ13" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BS13" t="n">
         <v>6.8</v>
@@ -3858,7 +3858,7 @@
         <v>13.5</v>
       </c>
       <c r="BW13" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BX13" t="n">
         <v>17.5</v>
@@ -3870,11 +3870,11 @@
         <v>9.4</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-16 02:39:49</t>
+          <t>2026-06-16 04:48:14</t>
         </is>
       </c>
     </row>
@@ -3905,22 +3905,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="G14" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="H14" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="I14" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J14" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K14" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L14" t="n">
         <v>1.46</v>
@@ -3929,10 +3929,10 @@
         <v>1.09</v>
       </c>
       <c r="N14" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O14" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P14" t="n">
         <v>1.78</v>
@@ -3944,19 +3944,19 @@
         <v>1.29</v>
       </c>
       <c r="S14" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T14" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="U14" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="V14" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W14" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="X14" t="n">
         <v>12.5</v>
@@ -3965,7 +3965,7 @@
         <v>19.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AA14" t="n">
         <v>290</v>
@@ -3989,13 +3989,13 @@
         <v>10.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>950</v>
+        <v>30</v>
       </c>
       <c r="AI14" t="n">
         <v>150</v>
       </c>
       <c r="AJ14" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AK14" t="n">
         <v>21</v>
@@ -4016,119 +4016,119 @@
         <v>10.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AS14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT14" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AU14" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV14" t="n">
-        <v>21</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW14" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AX14" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY14" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ14" t="n">
-        <v>22</v>
+        <v>8.4</v>
       </c>
       <c r="BA14" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB14" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BC14" t="n">
         <v>17</v>
       </c>
       <c r="BD14" t="n">
-        <v>9.199999999999999</v>
+        <v>30</v>
       </c>
       <c r="BE14" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>10</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM14" t="n">
         <v>10.5</v>
       </c>
-      <c r="BF14" t="n">
-        <v>12</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>1.09</v>
-      </c>
       <c r="BN14" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.09</v>
+        <v>3.4</v>
       </c>
       <c r="BP14" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.09</v>
+        <v>5.6</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.09</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT14" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU14" t="n">
-        <v>1.09</v>
+        <v>5.5</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.09</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.09</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.09</v>
+        <v>7.6</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-16 02:39:49</t>
+          <t>2026-06-16 04:48:14</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-16.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.94</v>
+        <v>2.16</v>
       </c>
       <c r="G2" t="n">
-        <v>2.02</v>
+        <v>2.22</v>
       </c>
       <c r="H2" t="n">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="I2" t="n">
-        <v>4.6</v>
+        <v>3.85</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="L2" t="n">
         <v>1.41</v>
@@ -881,40 +881,40 @@
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="O2" t="n">
         <v>1.31</v>
       </c>
       <c r="P2" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="R2" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S2" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="T2" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="U2" t="n">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="V2" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="W2" t="n">
-        <v>1.98</v>
+        <v>1.81</v>
       </c>
       <c r="X2" t="n">
         <v>27</v>
       </c>
       <c r="Y2" t="n">
-        <v>500</v>
+        <v>26</v>
       </c>
       <c r="Z2" t="n">
         <v>500</v>
@@ -923,28 +923,28 @@
         <v>900</v>
       </c>
       <c r="AB2" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AC2" t="n">
         <v>14</v>
       </c>
       <c r="AD2" t="n">
-        <v>500</v>
+        <v>26</v>
       </c>
       <c r="AE2" t="n">
         <v>500</v>
       </c>
       <c r="AF2" t="n">
-        <v>40</v>
+        <v>970</v>
       </c>
       <c r="AG2" t="n">
         <v>36</v>
       </c>
       <c r="AH2" t="n">
-        <v>950</v>
+        <v>25</v>
       </c>
       <c r="AI2" t="n">
-        <v>500</v>
+        <v>420</v>
       </c>
       <c r="AJ2" t="n">
         <v>900</v>
@@ -962,73 +962,73 @@
         <v>55</v>
       </c>
       <c r="AO2" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="AP2" t="n">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="AQ2" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="AR2" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AS2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.1</v>
+        <v>9</v>
       </c>
       <c r="AU2" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="AV2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW2" t="n">
         <v>7.8</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>8.6</v>
       </c>
       <c r="AX2" t="n">
         <v>6.2</v>
       </c>
       <c r="AY2" t="n">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="AZ2" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BB2" t="n">
         <v>10.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BD2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BE2" t="n">
         <v>8</v>
       </c>
-      <c r="BE2" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BF2" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.1</v>
+        <v>6.6</v>
       </c>
       <c r="BH2" t="n">
         <v>3.4</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
@@ -1037,16 +1037,16 @@
         <v>8</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
@@ -1055,22 +1055,22 @@
         <v>6.4</v>
       </c>
       <c r="BT2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>5.8</v>
+        <v>2.56</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>7.2</v>
+        <v>2.64</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-16 04:48:14</t>
+          <t>2026-06-16 06:57:01</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="G3" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="H3" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="I3" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="K3" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="L3" t="n">
         <v>1.39</v>
@@ -1135,37 +1135,37 @@
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P3" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="R3" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S3" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T3" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="U3" t="n">
         <v>1.88</v>
       </c>
       <c r="V3" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="W3" t="n">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="X3" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="Y3" t="n">
         <v>130</v>
@@ -1177,13 +1177,13 @@
         <v>700</v>
       </c>
       <c r="AB3" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AE3" t="n">
         <v>700</v>
@@ -1201,130 +1201,130 @@
         <v>700</v>
       </c>
       <c r="AJ3" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AK3" t="n">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="AL3" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AM3" t="n">
         <v>700</v>
       </c>
       <c r="AN3" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AO3" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AP3" t="n">
-        <v>6.4</v>
+        <v>14</v>
       </c>
       <c r="AQ3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT3" t="n">
         <v>7.4</v>
       </c>
-      <c r="AR3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>4.7</v>
-      </c>
       <c r="AU3" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="AW3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AX3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>5.1</v>
-      </c>
       <c r="AZ3" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>11</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF3" t="n">
         <v>7</v>
       </c>
-      <c r="BA3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BG3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="BJ3" t="n">
         <v>11.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.5</v>
+        <v>9.4</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>8.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BO3" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BP3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BT3" t="n">
         <v>11</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:48:14</t>
+          <t>2026-06-16 06:57:01</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="G4" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="H4" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="I4" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="J4" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="K4" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="L4" t="n">
         <v>1.35</v>
@@ -1395,7 +1395,7 @@
         <v>1.26</v>
       </c>
       <c r="P4" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q4" t="n">
         <v>1.79</v>
@@ -1404,25 +1404,25 @@
         <v>1.45</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="T4" t="n">
         <v>1.69</v>
       </c>
       <c r="U4" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="V4" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W4" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X4" t="n">
         <v>22</v>
       </c>
       <c r="Y4" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z4" t="n">
         <v>23</v>
@@ -1443,49 +1443,49 @@
         <v>34</v>
       </c>
       <c r="AF4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG4" t="n">
         <v>12.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AI4" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AJ4" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL4" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM4" t="n">
         <v>75</v>
       </c>
       <c r="AN4" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AO4" t="n">
         <v>25</v>
       </c>
       <c r="AP4" t="n">
-        <v>6</v>
+        <v>15.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>7.6</v>
+        <v>13</v>
       </c>
       <c r="AR4" t="n">
-        <v>7</v>
+        <v>18.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AT4" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="AU4" t="n">
         <v>7.4</v>
@@ -1494,64 +1494,64 @@
         <v>11</v>
       </c>
       <c r="AW4" t="n">
-        <v>7</v>
+        <v>14.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>5.9</v>
+        <v>15</v>
       </c>
       <c r="AY4" t="n">
         <v>10</v>
       </c>
       <c r="AZ4" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="BA4" t="n">
+        <v>20</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>28</v>
+      </c>
+      <c r="BC4" t="n">
         <v>21</v>
       </c>
-      <c r="BB4" t="n">
-        <v>19</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BD4" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>32</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.9</v>
+        <v>14.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>6.4</v>
+        <v>20</v>
       </c>
       <c r="BH4" t="n">
         <v>3.9</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="BJ4" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK4" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN4" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.75</v>
+        <v>4.9</v>
       </c>
       <c r="BP4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BQ4" t="n">
         <v>6.8</v>
@@ -1560,25 +1560,25 @@
         <v>29</v>
       </c>
       <c r="BS4" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BT4" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BU4" t="n">
-        <v>3.95</v>
+        <v>5.3</v>
       </c>
       <c r="BV4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BW4" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BX4" t="n">
         <v>32</v>
       </c>
       <c r="BY4" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-16 04:48:14</t>
+          <t>2026-06-16 06:57:01</t>
         </is>
       </c>
     </row>
@@ -1619,55 +1619,55 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="G5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="I5" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="J5" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="K5" t="n">
         <v>5.9</v>
       </c>
       <c r="L5" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="M5" t="n">
         <v>1.03</v>
       </c>
       <c r="N5" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="O5" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P5" t="n">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="R5" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="S5" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="T5" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="U5" t="n">
         <v>2.22</v>
       </c>
       <c r="V5" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="W5" t="n">
         <v>1.13</v>
@@ -1679,13 +1679,13 @@
         <v>14</v>
       </c>
       <c r="Z5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AA5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AB5" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AC5" t="n">
         <v>13.5</v>
@@ -1700,16 +1700,16 @@
         <v>160</v>
       </c>
       <c r="AG5" t="n">
-        <v>75</v>
+        <v>950</v>
       </c>
       <c r="AH5" t="n">
         <v>22</v>
       </c>
       <c r="AI5" t="n">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="AJ5" t="n">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="AK5" t="n">
         <v>260</v>
@@ -1718,121 +1718,121 @@
         <v>230</v>
       </c>
       <c r="AM5" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN5" t="n">
         <v>100</v>
       </c>
-      <c r="AN5" t="n">
-        <v>90</v>
-      </c>
       <c r="AO5" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AP5" t="n">
-        <v>18.5</v>
+        <v>25</v>
       </c>
       <c r="AQ5" t="n">
-        <v>6.2</v>
+        <v>11</v>
       </c>
       <c r="AR5" t="n">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.2</v>
+        <v>11.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>8.800000000000001</v>
+        <v>17.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>5.1</v>
+        <v>9</v>
       </c>
       <c r="AW5" t="n">
-        <v>6.6</v>
+        <v>12</v>
       </c>
       <c r="AX5" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>8.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>7.4</v>
+        <v>17</v>
       </c>
       <c r="BA5" t="n">
-        <v>8.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BC5" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BD5" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>9.800000000000001</v>
+        <v>15</v>
       </c>
       <c r="BF5" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="BH5" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="BJ5" t="n">
         <v>10.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BN5" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BO5" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BT5" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BV5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BW5" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BX5" t="n">
         <v>20</v>
       </c>
       <c r="BY5" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-16 04:48:14</t>
+          <t>2026-06-16 06:57:01</t>
         </is>
       </c>
     </row>
@@ -1873,230 +1873,230 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="G6" t="n">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="H6" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="I6" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="J6" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="K6" t="n">
         <v>3.75</v>
       </c>
       <c r="L6" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="M6" t="n">
         <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="O6" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="P6" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="R6" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="S6" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="T6" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="U6" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="V6" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W6" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="X6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Y6" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="Z6" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AA6" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC6" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AC6" t="n">
-        <v>8.6</v>
-      </c>
       <c r="AD6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AE6" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AF6" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG6" t="n">
         <v>10.5</v>
       </c>
       <c r="AH6" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK6" t="n">
         <v>21</v>
       </c>
-      <c r="AI6" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>22</v>
-      </c>
       <c r="AL6" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AM6" t="n">
-        <v>580</v>
+        <v>200</v>
       </c>
       <c r="AN6" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AO6" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP6" t="n">
-        <v>6.2</v>
+        <v>12.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>6.6</v>
+        <v>13.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS6" t="n">
         <v>9.4</v>
       </c>
       <c r="AT6" t="n">
-        <v>4.7</v>
+        <v>8</v>
       </c>
       <c r="AU6" t="n">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>6.6</v>
+        <v>16</v>
       </c>
       <c r="AW6" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AX6" t="n">
-        <v>5.6</v>
+        <v>10</v>
       </c>
       <c r="AY6" t="n">
-        <v>5.2</v>
+        <v>9</v>
       </c>
       <c r="AZ6" t="n">
-        <v>6.8</v>
+        <v>16</v>
       </c>
       <c r="BA6" t="n">
         <v>9</v>
       </c>
       <c r="BB6" t="n">
-        <v>7</v>
+        <v>18.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>7</v>
+        <v>17.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BE6" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF6" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="BG6" t="n">
         <v>9</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.74</v>
+        <v>3.25</v>
       </c>
       <c r="BJ6" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>2.54</v>
+        <v>12.5</v>
       </c>
       <c r="BN6" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="BP6" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BR6" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="BS6" t="n">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="BT6" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BU6" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BV6" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BW6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BX6" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BY6" t="n">
-        <v>8.6</v>
+        <v>46</v>
       </c>
       <c r="BZ6" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="CA6" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-16 04:48:14</t>
+          <t>2026-06-16 06:57:01</t>
         </is>
       </c>
     </row>
@@ -2127,19 +2127,19 @@
         </is>
       </c>
       <c r="F7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="J7" t="n">
         <v>3.9</v>
-      </c>
-      <c r="G7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="I7" t="n">
-        <v>2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3.85</v>
       </c>
       <c r="K7" t="n">
         <v>4.1</v>
@@ -2151,73 +2151,73 @@
         <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="O7" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P7" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="R7" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="S7" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T7" t="n">
         <v>1.79</v>
       </c>
       <c r="U7" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V7" t="n">
         <v>2.02</v>
       </c>
-      <c r="V7" t="n">
-        <v>2</v>
-      </c>
       <c r="W7" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="X7" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA7" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AB7" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD7" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AF7" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AG7" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AH7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI7" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AJ7" t="n">
-        <v>500</v>
+        <v>270</v>
       </c>
       <c r="AK7" t="n">
         <v>150</v>
@@ -2226,131 +2226,131 @@
         <v>65</v>
       </c>
       <c r="AM7" t="n">
-        <v>580</v>
+        <v>200</v>
       </c>
       <c r="AN7" t="n">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AO7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA7" t="n">
         <v>16</v>
       </c>
-      <c r="AP7" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BB7" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD7" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BF7" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BG7" t="n">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="BH7" t="n">
         <v>3.55</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.74</v>
+        <v>2.86</v>
       </c>
       <c r="BJ7" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>2.64</v>
+        <v>13</v>
       </c>
       <c r="BN7" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BP7" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BQ7" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="BR7" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BT7" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BU7" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="BV7" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BW7" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BX7" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.46</v>
+        <v>9.4</v>
       </c>
       <c r="BZ7" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="CA7" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-16 04:48:14</t>
+          <t>2026-06-16 06:57:01</t>
         </is>
       </c>
     </row>
@@ -2384,70 +2384,70 @@
         <v>1.53</v>
       </c>
       <c r="G8" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="H8" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="I8" t="n">
         <v>7.4</v>
       </c>
       <c r="J8" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="K8" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="L8" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M8" t="n">
         <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="O8" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P8" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="R8" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="S8" t="n">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="T8" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U8" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V8" t="n">
         <v>1.16</v>
       </c>
       <c r="W8" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="X8" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="Y8" t="n">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="Z8" t="n">
-        <v>500</v>
+        <v>220</v>
       </c>
       <c r="AA8" t="n">
         <v>700</v>
       </c>
       <c r="AB8" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC8" t="n">
         <v>11.5</v>
@@ -2459,142 +2459,142 @@
         <v>700</v>
       </c>
       <c r="AF8" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH8" t="n">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="AI8" t="n">
         <v>700</v>
       </c>
       <c r="AJ8" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AK8" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AL8" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AM8" t="n">
         <v>700</v>
       </c>
       <c r="AN8" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AO8" t="n">
-        <v>110</v>
+        <v>160</v>
       </c>
       <c r="AP8" t="n">
-        <v>7.2</v>
+        <v>21</v>
       </c>
       <c r="AQ8" t="n">
-        <v>7.8</v>
+        <v>15</v>
       </c>
       <c r="AR8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AT8" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AS8" t="n">
+      <c r="AU8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD8" t="n">
         <v>10</v>
       </c>
-      <c r="AT8" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BE8" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BF8" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="BG8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BH8" t="n">
         <v>4.2</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="BJ8" t="n">
         <v>10.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>9.199999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="BN8" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.2</v>
+        <v>3.85</v>
       </c>
       <c r="BP8" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BT8" t="n">
         <v>10.5</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-16 04:48:14</t>
+          <t>2026-06-16 06:57:01</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="G9" t="n">
         <v>2.32</v>
       </c>
       <c r="H9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I9" t="n">
         <v>3.35</v>
       </c>
-      <c r="I9" t="n">
-        <v>3.5</v>
-      </c>
       <c r="J9" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K9" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="L9" t="n">
         <v>1.32</v>
@@ -2659,31 +2659,31 @@
         <v>1.04</v>
       </c>
       <c r="N9" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="O9" t="n">
         <v>1.22</v>
       </c>
       <c r="P9" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="R9" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S9" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="T9" t="n">
         <v>1.58</v>
       </c>
       <c r="U9" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="V9" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W9" t="n">
         <v>1.75</v>
@@ -2692,70 +2692,70 @@
         <v>22</v>
       </c>
       <c r="Y9" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="Z9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA9" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="AB9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD9" t="n">
         <v>14.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>85</v>
+        <v>32</v>
       </c>
       <c r="AF9" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH9" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AI9" t="n">
-        <v>95</v>
+        <v>38</v>
       </c>
       <c r="AJ9" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AK9" t="n">
         <v>22</v>
       </c>
       <c r="AL9" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="AM9" t="n">
-        <v>250</v>
+        <v>65</v>
       </c>
       <c r="AN9" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AO9" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AP9" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AQ9" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AR9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS9" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="AT9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AU9" t="n">
         <v>8</v>
@@ -2764,37 +2764,37 @@
         <v>12.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="AX9" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AY9" t="n">
         <v>10</v>
       </c>
       <c r="AZ9" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BA9" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BB9" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BC9" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BD9" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BE9" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BF9" t="n">
         <v>11</v>
       </c>
       <c r="BG9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BH9" t="n">
         <v>4.1</v>
@@ -2806,13 +2806,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BN9" t="n">
         <v>5.5</v>
@@ -2824,13 +2824,13 @@
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BT9" t="n">
         <v>6.8</v>
@@ -2839,26 +2839,26 @@
         <v>6</v>
       </c>
       <c r="BV9" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BW9" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX9" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BY9" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="CA9" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-16 04:48:14</t>
+          <t>2026-06-16 06:57:01</t>
         </is>
       </c>
     </row>
@@ -2892,19 +2892,19 @@
         <v>2.42</v>
       </c>
       <c r="G10" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="H10" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="I10" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J10" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K10" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L10" t="n">
         <v>1.34</v>
@@ -2919,136 +2919,136 @@
         <v>1.23</v>
       </c>
       <c r="P10" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="R10" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S10" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="T10" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="U10" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="V10" t="n">
         <v>1.47</v>
       </c>
       <c r="W10" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="X10" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="Y10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF10" t="n">
         <v>18</v>
       </c>
-      <c r="Z10" t="n">
-        <v>500</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>120</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>17</v>
-      </c>
-      <c r="AC10" t="n">
+      <c r="AG10" t="n">
         <v>12</v>
       </c>
-      <c r="AD10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>44</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AH10" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AI10" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="AJ10" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AK10" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AL10" t="n">
         <v>70</v>
       </c>
       <c r="AM10" t="n">
-        <v>320</v>
+        <v>65</v>
       </c>
       <c r="AN10" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AO10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>27</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>29</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>27</v>
+      </c>
+      <c r="BE10" t="n">
         <v>28</v>
       </c>
-      <c r="AP10" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>28</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>25</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>23</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>12</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>23</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BF10" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BG10" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BH10" t="n">
         <v>4</v>
@@ -3075,16 +3075,16 @@
         <v>5</v>
       </c>
       <c r="BP10" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BQ10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR10" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BS10" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT10" t="n">
         <v>6.4</v>
@@ -3093,16 +3093,16 @@
         <v>5.7</v>
       </c>
       <c r="BV10" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BW10" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX10" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BY10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-16 04:48:14</t>
+          <t>2026-06-16 06:57:01</t>
         </is>
       </c>
     </row>
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="F11" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="G11" t="n">
         <v>1.52</v>
       </c>
-      <c r="G11" t="n">
-        <v>1.55</v>
-      </c>
       <c r="H11" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="I11" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="J11" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="K11" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="L11" t="n">
         <v>1.15</v>
@@ -3167,13 +3167,13 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O11" t="n">
         <v>1.06</v>
       </c>
       <c r="P11" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Q11" t="n">
         <v>1.22</v>
@@ -3188,13 +3188,13 @@
         <v>1.32</v>
       </c>
       <c r="U11" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="V11" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="W11" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="X11" t="n">
         <v>950</v>
@@ -3218,7 +3218,7 @@
         <v>100</v>
       </c>
       <c r="AE11" t="n">
-        <v>730</v>
+        <v>930</v>
       </c>
       <c r="AF11" t="n">
         <v>85</v>
@@ -3245,7 +3245,7 @@
         <v>60</v>
       </c>
       <c r="AN11" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AO11" t="n">
         <v>42</v>
@@ -3266,10 +3266,10 @@
         <v>21</v>
       </c>
       <c r="AU11" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AV11" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AW11" t="n">
         <v>4.2</v>
@@ -3299,28 +3299,28 @@
         <v>25</v>
       </c>
       <c r="BF11" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="BG11" t="n">
         <v>19</v>
       </c>
       <c r="BH11" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BI11" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BJ11" t="n">
         <v>9</v>
       </c>
       <c r="BK11" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BN11" t="n">
         <v>5.7</v>
@@ -3329,44 +3329,44 @@
         <v>4.9</v>
       </c>
       <c r="BP11" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BR11" t="n">
         <v>14.5</v>
       </c>
       <c r="BS11" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BT11" t="n">
         <v>11.5</v>
       </c>
       <c r="BU11" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BZ11" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="CA11" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-16 04:48:14</t>
+          <t>2026-06-16 06:57:01</t>
         </is>
       </c>
     </row>
@@ -3400,13 +3400,13 @@
         <v>2.18</v>
       </c>
       <c r="G12" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H12" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="I12" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="J12" t="n">
         <v>4.1</v>
@@ -3421,40 +3421,40 @@
         <v>1.02</v>
       </c>
       <c r="N12" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="O12" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="P12" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="R12" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="S12" t="n">
         <v>1.92</v>
       </c>
       <c r="T12" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="U12" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="V12" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W12" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="X12" t="n">
         <v>950</v>
       </c>
       <c r="Y12" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="Z12" t="n">
         <v>500</v>
@@ -3463,34 +3463,34 @@
         <v>290</v>
       </c>
       <c r="AB12" t="n">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AC12" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="AD12" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="AE12" t="n">
         <v>500</v>
       </c>
       <c r="AF12" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AG12" t="n">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="AH12" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="AI12" t="n">
         <v>500</v>
       </c>
       <c r="AJ12" t="n">
-        <v>900</v>
+        <v>140</v>
       </c>
       <c r="AK12" t="n">
-        <v>65</v>
+        <v>970</v>
       </c>
       <c r="AL12" t="n">
         <v>500</v>
@@ -3499,128 +3499,128 @@
         <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="AO12" t="n">
         <v>600</v>
       </c>
       <c r="AP12" t="n">
-        <v>3.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ12" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AR12" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS12" t="n">
-        <v>3.6</v>
+        <v>10</v>
       </c>
       <c r="AT12" t="n">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="AU12" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV12" t="n">
         <v>8.4</v>
       </c>
       <c r="AW12" t="n">
-        <v>7.6</v>
+        <v>13</v>
       </c>
       <c r="AX12" t="n">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="AY12" t="n">
         <v>7</v>
       </c>
       <c r="AZ12" t="n">
-        <v>7.6</v>
+        <v>11.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>7.6</v>
+        <v>14.5</v>
       </c>
       <c r="BB12" t="n">
-        <v>7.8</v>
+        <v>14</v>
       </c>
       <c r="BC12" t="n">
-        <v>6.8</v>
+        <v>10.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>7.2</v>
+        <v>11.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>3.8</v>
+        <v>16.5</v>
       </c>
       <c r="BF12" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BH12" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BI12" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BJ12" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK12" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.77</v>
+        <v>1.25</v>
       </c>
       <c r="BN12" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO12" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BP12" t="n">
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>7.4</v>
+        <v>3.95</v>
       </c>
       <c r="BT12" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BU12" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>7.8</v>
+        <v>3.75</v>
       </c>
       <c r="BX12" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BY12" t="n">
-        <v>3.35</v>
+        <v>2.82</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-16 04:48:14</t>
+          <t>2026-06-16 06:57:01</t>
         </is>
       </c>
     </row>
@@ -3657,64 +3657,64 @@
         <v>3.3</v>
       </c>
       <c r="H13" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="I13" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="J13" t="n">
         <v>4.5</v>
       </c>
       <c r="K13" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L13" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="M13" t="n">
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="O13" t="n">
         <v>1.09</v>
       </c>
       <c r="P13" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="R13" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="S13" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="T13" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="U13" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="V13" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="W13" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="X13" t="n">
-        <v>240</v>
+        <v>120</v>
       </c>
       <c r="Y13" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Z13" t="n">
         <v>25</v>
       </c>
       <c r="AA13" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AB13" t="n">
         <v>34</v>
@@ -3744,7 +3744,7 @@
         <v>60</v>
       </c>
       <c r="AK13" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AL13" t="n">
         <v>27</v>
@@ -3756,7 +3756,7 @@
         <v>12</v>
       </c>
       <c r="AO13" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AP13" t="n">
         <v>38</v>
@@ -3771,7 +3771,7 @@
         <v>26</v>
       </c>
       <c r="AT13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU13" t="n">
         <v>12</v>
@@ -3783,52 +3783,52 @@
         <v>16</v>
       </c>
       <c r="AX13" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AY13" t="n">
         <v>14</v>
       </c>
       <c r="AZ13" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BA13" t="n">
         <v>18</v>
       </c>
       <c r="BB13" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="BC13" t="n">
         <v>23</v>
       </c>
       <c r="BD13" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BE13" t="n">
         <v>24</v>
       </c>
       <c r="BF13" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BG13" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BH13" t="n">
         <v>6.4</v>
       </c>
       <c r="BI13" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BJ13" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BK13" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BN13" t="n">
         <v>8</v>
@@ -3840,41 +3840,41 @@
         <v>20</v>
       </c>
       <c r="BQ13" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR13" t="n">
         <v>21</v>
       </c>
       <c r="BS13" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BT13" t="n">
         <v>6.6</v>
       </c>
       <c r="BU13" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BV13" t="n">
         <v>13.5</v>
       </c>
       <c r="BW13" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BX13" t="n">
         <v>17.5</v>
       </c>
       <c r="BY13" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BZ13" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="CA13" t="n">
         <v>4.9</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-16 04:48:14</t>
+          <t>2026-06-16 06:57:01</t>
         </is>
       </c>
     </row>
@@ -3908,10 +3908,10 @@
         <v>1.58</v>
       </c>
       <c r="G14" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="H14" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="I14" t="n">
         <v>7.8</v>
@@ -3920,7 +3920,7 @@
         <v>4</v>
       </c>
       <c r="K14" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L14" t="n">
         <v>1.46</v>
@@ -3929,25 +3929,25 @@
         <v>1.09</v>
       </c>
       <c r="N14" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="O14" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P14" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R14" t="n">
         <v>1.29</v>
       </c>
       <c r="S14" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T14" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="U14" t="n">
         <v>1.76</v>
@@ -3956,13 +3956,13 @@
         <v>1.14</v>
       </c>
       <c r="W14" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="X14" t="n">
         <v>12.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="Z14" t="n">
         <v>65</v>
@@ -3974,7 +3974,7 @@
         <v>7</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD14" t="n">
         <v>950</v>
@@ -3983,19 +3983,19 @@
         <v>160</v>
       </c>
       <c r="AF14" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AG14" t="n">
         <v>10.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>30</v>
+        <v>950</v>
       </c>
       <c r="AI14" t="n">
         <v>150</v>
       </c>
       <c r="AJ14" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AK14" t="n">
         <v>21</v>
@@ -4007,7 +4007,7 @@
         <v>220</v>
       </c>
       <c r="AN14" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AO14" t="n">
         <v>250</v>
@@ -4019,34 +4019,34 @@
         <v>16.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AS14" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT14" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AU14" t="n">
         <v>7.8</v>
       </c>
       <c r="AV14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AW14" t="n">
         <v>10</v>
       </c>
       <c r="AX14" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AY14" t="n">
-        <v>9</v>
+        <v>5.4</v>
       </c>
       <c r="AZ14" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BA14" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB14" t="n">
         <v>13</v>
@@ -4058,13 +4058,13 @@
         <v>30</v>
       </c>
       <c r="BE14" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF14" t="n">
         <v>10</v>
       </c>
       <c r="BG14" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH14" t="n">
         <v>3.3</v>
@@ -4076,13 +4076,13 @@
         <v>12.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN14" t="n">
         <v>4</v>
@@ -4091,7 +4091,7 @@
         <v>3.4</v>
       </c>
       <c r="BP14" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BQ14" t="n">
         <v>5.6</v>
@@ -4100,35 +4100,35 @@
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BT14" t="n">
         <v>11</v>
       </c>
       <c r="BU14" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-16 04:48:14</t>
+          <t>2026-06-16 06:57:01</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-16.xlsx
@@ -857,58 +857,58 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.16</v>
+        <v>1.86</v>
       </c>
       <c r="G2" t="n">
-        <v>2.22</v>
+        <v>1.93</v>
       </c>
       <c r="H2" t="n">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="I2" t="n">
-        <v>3.85</v>
+        <v>4.9</v>
       </c>
       <c r="J2" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="K2" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="L2" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O2" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P2" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="R2" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="S2" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="T2" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U2" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V2" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="W2" t="n">
-        <v>1.81</v>
+        <v>2.06</v>
       </c>
       <c r="X2" t="n">
         <v>27</v>
@@ -923,19 +923,19 @@
         <v>900</v>
       </c>
       <c r="AB2" t="n">
-        <v>15.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>14</v>
+        <v>8.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AE2" t="n">
         <v>500</v>
       </c>
       <c r="AF2" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AG2" t="n">
         <v>36</v>
@@ -944,13 +944,13 @@
         <v>25</v>
       </c>
       <c r="AI2" t="n">
-        <v>420</v>
+        <v>320</v>
       </c>
       <c r="AJ2" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK2" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="AL2" t="n">
         <v>500</v>
@@ -959,76 +959,76 @@
         <v>580</v>
       </c>
       <c r="AN2" t="n">
-        <v>55</v>
+        <v>19.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="AP2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AQ2" t="n">
-        <v>8.6</v>
+        <v>12.5</v>
       </c>
       <c r="AR2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AT2" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AS2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>9</v>
-      </c>
       <c r="AU2" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AV2" t="n">
         <v>9</v>
       </c>
       <c r="AW2" t="n">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="AX2" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AY2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE2" t="n">
         <v>9</v>
       </c>
-      <c r="AZ2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>8</v>
-      </c>
       <c r="BF2" t="n">
-        <v>5.9</v>
+        <v>12</v>
       </c>
       <c r="BG2" t="n">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="BJ2" t="n">
         <v>9.6</v>
       </c>
       <c r="BK2" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
@@ -1037,40 +1037,40 @@
         <v>8</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>6.4</v>
+        <v>9</v>
       </c>
       <c r="BT2" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>2.56</v>
+        <v>10</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.64</v>
+        <v>10.5</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-16 06:57:01</t>
+          <t>2026-06-16 09:06:36</t>
         </is>
       </c>
     </row>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="G3" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="H3" t="n">
         <v>7.4</v>
@@ -1126,49 +1126,49 @@
         <v>4.2</v>
       </c>
       <c r="K3" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L3" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="M3" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="O3" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P3" t="n">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="R3" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="S3" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="T3" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="U3" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="V3" t="n">
         <v>1.14</v>
       </c>
       <c r="W3" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="X3" t="n">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="Z3" t="n">
         <v>500</v>
@@ -1177,25 +1177,25 @@
         <v>700</v>
       </c>
       <c r="AB3" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AC3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD3" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AE3" t="n">
         <v>700</v>
       </c>
       <c r="AF3" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AG3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH3" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AI3" t="n">
         <v>700</v>
@@ -1204,127 +1204,127 @@
         <v>14</v>
       </c>
       <c r="AK3" t="n">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="AL3" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AM3" t="n">
-        <v>700</v>
+        <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AO3" t="n">
-        <v>190</v>
+        <v>240</v>
       </c>
       <c r="AP3" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>19.5</v>
+        <v>10</v>
       </c>
       <c r="AR3" t="n">
         <v>10.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AT3" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU3" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>10.5</v>
       </c>
-      <c r="AW3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>20</v>
-      </c>
       <c r="BA3" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BB3" t="n">
         <v>11.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BD3" t="n">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BF3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BG3" t="n">
         <v>11</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.86</v>
+        <v>2.74</v>
       </c>
       <c r="BJ3" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BN3" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BP3" t="n">
         <v>10</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BT3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BU3" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:57:01</t>
+          <t>2026-06-16 09:06:36</t>
         </is>
       </c>
     </row>
@@ -1365,16 +1365,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="G4" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="H4" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="I4" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="J4" t="n">
         <v>3.75</v>
@@ -1392,13 +1392,13 @@
         <v>4.4</v>
       </c>
       <c r="O4" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P4" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="R4" t="n">
         <v>1.45</v>
@@ -1407,19 +1407,19 @@
         <v>2.96</v>
       </c>
       <c r="T4" t="n">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="U4" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="V4" t="n">
         <v>1.47</v>
       </c>
       <c r="W4" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="X4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Y4" t="n">
         <v>15.5</v>
@@ -1428,10 +1428,10 @@
         <v>23</v>
       </c>
       <c r="AA4" t="n">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="AB4" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC4" t="n">
         <v>9</v>
@@ -1443,34 +1443,34 @@
         <v>34</v>
       </c>
       <c r="AF4" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH4" t="n">
         <v>17</v>
       </c>
       <c r="AI4" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AJ4" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL4" t="n">
         <v>34</v>
       </c>
       <c r="AM4" t="n">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AN4" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AO4" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AP4" t="n">
         <v>15.5</v>
@@ -1491,13 +1491,13 @@
         <v>7.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW4" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AX4" t="n">
         <v>14.5</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>15</v>
       </c>
       <c r="AY4" t="n">
         <v>10</v>
@@ -1506,10 +1506,10 @@
         <v>14</v>
       </c>
       <c r="BA4" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="BB4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BC4" t="n">
         <v>21</v>
@@ -1518,16 +1518,16 @@
         <v>17.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>8.199999999999999</v>
+        <v>34</v>
       </c>
       <c r="BF4" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BI4" t="n">
         <v>3</v>
@@ -1536,49 +1536,49 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK4" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BN4" t="n">
         <v>5.8</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BP4" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BR4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BS4" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BT4" t="n">
         <v>6.6</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BV4" t="n">
         <v>23</v>
       </c>
       <c r="BW4" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BX4" t="n">
         <v>32</v>
       </c>
       <c r="BY4" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-16 06:57:01</t>
+          <t>2026-06-16 09:06:36</t>
         </is>
       </c>
     </row>
@@ -1619,73 +1619,73 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="H5" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="I5" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="J5" t="n">
         <v>5.3</v>
       </c>
       <c r="K5" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="L5" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M5" t="n">
         <v>1.03</v>
       </c>
       <c r="N5" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="O5" t="n">
         <v>1.17</v>
       </c>
       <c r="P5" t="n">
-        <v>2.84</v>
+        <v>2.72</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="R5" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="S5" t="n">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="T5" t="n">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="U5" t="n">
-        <v>2.22</v>
+        <v>2.06</v>
       </c>
       <c r="V5" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="W5" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X5" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="Y5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z5" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AA5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AB5" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AC5" t="n">
         <v>13.5</v>
@@ -1694,22 +1694,22 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AE5" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AF5" t="n">
         <v>160</v>
       </c>
       <c r="AG5" t="n">
-        <v>950</v>
+        <v>42</v>
       </c>
       <c r="AH5" t="n">
-        <v>22</v>
+        <v>100</v>
       </c>
       <c r="AI5" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AJ5" t="n">
-        <v>240</v>
+        <v>280</v>
       </c>
       <c r="AK5" t="n">
         <v>260</v>
@@ -1718,58 +1718,58 @@
         <v>230</v>
       </c>
       <c r="AM5" t="n">
-        <v>130</v>
+        <v>170</v>
       </c>
       <c r="AN5" t="n">
-        <v>100</v>
+        <v>170</v>
       </c>
       <c r="AO5" t="n">
         <v>5</v>
       </c>
       <c r="AP5" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AQ5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AU5" t="n">
         <v>11</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>6.4</v>
       </c>
       <c r="AV5" t="n">
         <v>9</v>
       </c>
       <c r="AW5" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>10.5</v>
+        <v>6</v>
       </c>
       <c r="AY5" t="n">
-        <v>11.5</v>
+        <v>23</v>
       </c>
       <c r="AZ5" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BA5" t="n">
         <v>11.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>12</v>
+        <v>6.2</v>
       </c>
       <c r="BC5" t="n">
-        <v>11</v>
+        <v>7.4</v>
       </c>
       <c r="BD5" t="n">
-        <v>10.5</v>
+        <v>6</v>
       </c>
       <c r="BE5" t="n">
         <v>15</v>
@@ -1778,49 +1778,49 @@
         <v>15</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BH5" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="BJ5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN5" t="n">
         <v>12</v>
       </c>
       <c r="BO5" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BT5" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="BV5" t="n">
         <v>8.6</v>
@@ -1829,10 +1829,10 @@
         <v>4.9</v>
       </c>
       <c r="BX5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BY5" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-16 06:57:01</t>
+          <t>2026-06-16 09:06:36</t>
         </is>
       </c>
     </row>
@@ -1873,19 +1873,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="G6" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="H6" t="n">
         <v>4.7</v>
       </c>
       <c r="I6" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J6" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K6" t="n">
         <v>3.75</v>
@@ -1897,7 +1897,7 @@
         <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O6" t="n">
         <v>1.31</v>
@@ -1915,16 +1915,16 @@
         <v>3.3</v>
       </c>
       <c r="T6" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="U6" t="n">
         <v>2.08</v>
       </c>
       <c r="V6" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W6" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X6" t="n">
         <v>16</v>
@@ -1936,10 +1936,10 @@
         <v>38</v>
       </c>
       <c r="AA6" t="n">
-        <v>900</v>
+        <v>330</v>
       </c>
       <c r="AB6" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC6" t="n">
         <v>8.800000000000001</v>
@@ -1951,19 +1951,19 @@
         <v>65</v>
       </c>
       <c r="AF6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG6" t="n">
         <v>10.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>160</v>
+        <v>70</v>
       </c>
       <c r="AJ6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK6" t="n">
         <v>21</v>
@@ -1972,67 +1972,67 @@
         <v>36</v>
       </c>
       <c r="AM6" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AN6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP6" t="n">
         <v>13</v>
       </c>
-      <c r="AO6" t="n">
-        <v>600</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AQ6" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AR6" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AS6" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AT6" t="n">
         <v>8</v>
       </c>
       <c r="AU6" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV6" t="n">
         <v>16</v>
       </c>
       <c r="AW6" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AX6" t="n">
         <v>10</v>
       </c>
       <c r="AY6" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ6" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB6" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BC6" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BD6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG6" t="n">
         <v>8</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>11</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>9</v>
       </c>
       <c r="BH6" t="n">
         <v>3.6</v>
@@ -2044,13 +2044,13 @@
         <v>9.6</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BN6" t="n">
         <v>4.7</v>
@@ -2062,25 +2062,25 @@
         <v>13.5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BS6" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BT6" t="n">
         <v>7.8</v>
       </c>
       <c r="BU6" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BV6" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BW6" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX6" t="n">
         <v>50</v>
@@ -2092,11 +2092,11 @@
         <v>23</v>
       </c>
       <c r="CA6" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-16 06:57:01</t>
+          <t>2026-06-16 09:06:36</t>
         </is>
       </c>
     </row>
@@ -2130,55 +2130,55 @@
         <v>4.2</v>
       </c>
       <c r="G7" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="H7" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="I7" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="J7" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="K7" t="n">
         <v>4.1</v>
       </c>
       <c r="L7" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M7" t="n">
         <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O7" t="n">
         <v>1.31</v>
       </c>
       <c r="P7" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="R7" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S7" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="T7" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="U7" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V7" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="W7" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="X7" t="n">
         <v>16.5</v>
@@ -2193,10 +2193,10 @@
         <v>22</v>
       </c>
       <c r="AB7" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD7" t="n">
         <v>10.5</v>
@@ -2211,7 +2211,7 @@
         <v>18</v>
       </c>
       <c r="AH7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI7" t="n">
         <v>38</v>
@@ -2220,7 +2220,7 @@
         <v>270</v>
       </c>
       <c r="AK7" t="n">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="AL7" t="n">
         <v>65</v>
@@ -2229,22 +2229,22 @@
         <v>200</v>
       </c>
       <c r="AN7" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AO7" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AP7" t="n">
         <v>13.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR7" t="n">
         <v>10</v>
       </c>
       <c r="AS7" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AT7" t="n">
         <v>13.5</v>
@@ -2274,13 +2274,13 @@
         <v>10.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BD7" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BE7" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BF7" t="n">
         <v>10</v>
@@ -2289,68 +2289,68 @@
         <v>11.5</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="BJ7" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="BN7" t="n">
         <v>8</v>
       </c>
       <c r="BO7" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BP7" t="n">
         <v>38</v>
       </c>
       <c r="BQ7" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="BR7" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS7" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="BT7" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BU7" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="BV7" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BW7" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BX7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BY7" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="CA7" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-16 06:57:01</t>
+          <t>2026-06-16 09:06:36</t>
         </is>
       </c>
     </row>
@@ -2381,46 +2381,46 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="G8" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="H8" t="n">
+        <v>6</v>
+      </c>
+      <c r="I8" t="n">
         <v>6.6</v>
-      </c>
-      <c r="I8" t="n">
-        <v>7.4</v>
       </c>
       <c r="J8" t="n">
         <v>4.8</v>
       </c>
       <c r="K8" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M8" t="n">
         <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="O8" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P8" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="R8" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="S8" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="T8" t="n">
         <v>1.79</v>
@@ -2429,16 +2429,16 @@
         <v>2.1</v>
       </c>
       <c r="V8" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="W8" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="X8" t="n">
+        <v>29</v>
+      </c>
+      <c r="Y8" t="n">
         <v>25</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>40</v>
       </c>
       <c r="Z8" t="n">
         <v>220</v>
@@ -2447,16 +2447,16 @@
         <v>700</v>
       </c>
       <c r="AB8" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AE8" t="n">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="AF8" t="n">
         <v>10.5</v>
@@ -2471,76 +2471,76 @@
         <v>700</v>
       </c>
       <c r="AJ8" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AK8" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="AL8" t="n">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="AM8" t="n">
         <v>700</v>
       </c>
       <c r="AN8" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AO8" t="n">
-        <v>160</v>
+        <v>85</v>
       </c>
       <c r="AP8" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="AQ8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AR8" t="n">
         <v>11</v>
       </c>
       <c r="AS8" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AT8" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AU8" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV8" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AW8" t="n">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="AX8" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY8" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ8" t="n">
-        <v>11.5</v>
+        <v>19</v>
       </c>
       <c r="BA8" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BB8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC8" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE8" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BF8" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BG8" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BH8" t="n">
         <v>4.2</v>
@@ -2549,40 +2549,40 @@
         <v>3.8</v>
       </c>
       <c r="BJ8" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK8" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BN8" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BO8" t="n">
         <v>3.85</v>
       </c>
       <c r="BP8" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT8" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BU8" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-16 06:57:01</t>
+          <t>2026-06-16 09:06:36</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="G9" t="n">
         <v>2.26</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2.32</v>
       </c>
       <c r="H9" t="n">
         <v>3.25</v>
       </c>
       <c r="I9" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="J9" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="K9" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="L9" t="n">
         <v>1.32</v>
@@ -2659,106 +2659,106 @@
         <v>1.04</v>
       </c>
       <c r="N9" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O9" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P9" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="R9" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S9" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="T9" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="U9" t="n">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="V9" t="n">
         <v>1.42</v>
       </c>
       <c r="W9" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="X9" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="Y9" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="Z9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA9" t="n">
         <v>60</v>
       </c>
       <c r="AB9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD9" t="n">
         <v>14</v>
       </c>
-      <c r="AC9" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD9" t="n">
+      <c r="AE9" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH9" t="n">
         <v>14.5</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>15</v>
       </c>
       <c r="AI9" t="n">
         <v>38</v>
       </c>
       <c r="AJ9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK9" t="n">
         <v>22</v>
       </c>
       <c r="AL9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM9" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AN9" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AO9" t="n">
+        <v>24</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AR9" t="n">
         <v>23</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>19</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>16</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>22</v>
       </c>
       <c r="AS9" t="n">
         <v>46</v>
       </c>
       <c r="AT9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU9" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV9" t="n">
         <v>12.5</v>
@@ -2773,7 +2773,7 @@
         <v>10</v>
       </c>
       <c r="AZ9" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA9" t="n">
         <v>32</v>
@@ -2785,16 +2785,16 @@
         <v>19</v>
       </c>
       <c r="BD9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BE9" t="n">
         <v>50</v>
       </c>
       <c r="BF9" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BH9" t="n">
         <v>4.1</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-16 06:57:01</t>
+          <t>2026-06-16 09:06:36</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="G10" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="H10" t="n">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="I10" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J10" t="n">
         <v>3.75</v>
       </c>
       <c r="K10" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L10" t="n">
         <v>1.34</v>
@@ -2928,7 +2928,7 @@
         <v>1.53</v>
       </c>
       <c r="S10" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="T10" t="n">
         <v>1.59</v>
@@ -2937,13 +2937,13 @@
         <v>2.58</v>
       </c>
       <c r="V10" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="X10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Y10" t="n">
         <v>15.5</v>
@@ -2952,7 +2952,7 @@
         <v>23</v>
       </c>
       <c r="AA10" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AB10" t="n">
         <v>14</v>
@@ -2961,13 +2961,13 @@
         <v>9</v>
       </c>
       <c r="AD10" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE10" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF10" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AG10" t="n">
         <v>12</v>
@@ -2979,34 +2979,34 @@
         <v>50</v>
       </c>
       <c r="AJ10" t="n">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="AK10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL10" t="n">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="AM10" t="n">
         <v>65</v>
       </c>
       <c r="AN10" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AO10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP10" t="n">
         <v>18.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AR10" t="n">
         <v>20</v>
       </c>
       <c r="AS10" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AT10" t="n">
         <v>12.5</v>
@@ -3015,13 +3015,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV10" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX10" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AY10" t="n">
         <v>10.5</v>
@@ -3033,28 +3033,28 @@
         <v>30</v>
       </c>
       <c r="BB10" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BC10" t="n">
         <v>20</v>
       </c>
       <c r="BD10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BE10" t="n">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="BF10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BG10" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BH10" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BJ10" t="n">
         <v>8.800000000000001</v>
@@ -3063,46 +3063,46 @@
         <v>6.6</v>
       </c>
       <c r="BL10" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BM10" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BN10" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BO10" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BP10" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BQ10" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BR10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BS10" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BT10" t="n">
         <v>6.4</v>
       </c>
       <c r="BU10" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BV10" t="n">
         <v>21</v>
       </c>
       <c r="BW10" t="n">
-        <v>9.800000000000001</v>
+        <v>16</v>
       </c>
       <c r="BX10" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BY10" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-16 06:57:01</t>
+          <t>2026-06-16 09:06:36</t>
         </is>
       </c>
     </row>
@@ -3143,55 +3143,55 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="G11" t="n">
         <v>1.52</v>
       </c>
       <c r="H11" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I11" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="J11" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="K11" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="L11" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="M11" t="n">
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O11" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="P11" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="R11" t="n">
-        <v>2.74</v>
+        <v>2.44</v>
       </c>
       <c r="S11" t="n">
-        <v>1.54</v>
+        <v>1.67</v>
       </c>
       <c r="T11" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="U11" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="V11" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W11" t="n">
         <v>2.92</v>
@@ -3200,115 +3200,115 @@
         <v>950</v>
       </c>
       <c r="Y11" t="n">
-        <v>950</v>
+        <v>110</v>
       </c>
       <c r="Z11" t="n">
         <v>180</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AB11" t="n">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="AC11" t="n">
-        <v>950</v>
+        <v>19.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="AE11" t="n">
-        <v>930</v>
+        <v>160</v>
       </c>
       <c r="AF11" t="n">
-        <v>85</v>
+        <v>19.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AH11" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AI11" t="n">
         <v>120</v>
       </c>
       <c r="AJ11" t="n">
-        <v>80</v>
+        <v>19.5</v>
       </c>
       <c r="AK11" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AL11" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="AM11" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN11" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="AO11" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AP11" t="n">
-        <v>4.1</v>
+        <v>46</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4.2</v>
+        <v>40</v>
       </c>
       <c r="AR11" t="n">
-        <v>4.2</v>
+        <v>50</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.2</v>
+        <v>48</v>
       </c>
       <c r="AT11" t="n">
         <v>21</v>
       </c>
       <c r="AU11" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AV11" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.2</v>
+        <v>46</v>
       </c>
       <c r="AX11" t="n">
         <v>16</v>
       </c>
       <c r="AY11" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ11" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BB11" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BC11" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BD11" t="n">
         <v>15.5</v>
       </c>
       <c r="BE11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.98</v>
+        <v>3.3</v>
       </c>
       <c r="BG11" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BH11" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="BI11" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="BJ11" t="n">
         <v>9</v>
@@ -3320,53 +3320,53 @@
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BN11" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BO11" t="n">
         <v>4.9</v>
       </c>
       <c r="BP11" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BR11" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BS11" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BT11" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BU11" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BX11" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY11" t="n">
         <v>10</v>
       </c>
       <c r="BZ11" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="CA11" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-16 06:57:01</t>
+          <t>2026-06-16 09:06:36</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
         <v>2.18</v>
       </c>
       <c r="G12" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="H12" t="n">
         <v>3.1</v>
@@ -3409,40 +3409,40 @@
         <v>3.25</v>
       </c>
       <c r="J12" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K12" t="n">
         <v>4.4</v>
       </c>
       <c r="L12" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="M12" t="n">
         <v>1.02</v>
       </c>
       <c r="N12" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="O12" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="P12" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="R12" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="S12" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="T12" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="U12" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="V12" t="n">
         <v>1.44</v>
@@ -3454,7 +3454,7 @@
         <v>950</v>
       </c>
       <c r="Y12" t="n">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="Z12" t="n">
         <v>500</v>
@@ -3463,121 +3463,121 @@
         <v>290</v>
       </c>
       <c r="AB12" t="n">
-        <v>110</v>
+        <v>38</v>
       </c>
       <c r="AC12" t="n">
-        <v>40</v>
+        <v>12.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AE12" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AF12" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="AG12" t="n">
         <v>13</v>
       </c>
       <c r="AH12" t="n">
-        <v>25</v>
+        <v>15.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AJ12" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="AK12" t="n">
-        <v>970</v>
+        <v>32</v>
       </c>
       <c r="AL12" t="n">
-        <v>500</v>
+        <v>95</v>
       </c>
       <c r="AM12" t="n">
         <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>21</v>
+        <v>7.4</v>
       </c>
       <c r="AO12" t="n">
-        <v>600</v>
+        <v>48</v>
       </c>
       <c r="AP12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AQ12" t="n">
-        <v>8.6</v>
+        <v>13</v>
       </c>
       <c r="AR12" t="n">
-        <v>9.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="AS12" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AU12" t="n">
         <v>10</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>6.4</v>
       </c>
       <c r="AV12" t="n">
         <v>8.4</v>
       </c>
       <c r="AW12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AX12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY12" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AZ12" t="n">
         <v>11.5</v>
       </c>
       <c r="BA12" t="n">
+        <v>15</v>
+      </c>
+      <c r="BB12" t="n">
         <v>14.5</v>
       </c>
-      <c r="BB12" t="n">
-        <v>14</v>
-      </c>
       <c r="BC12" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BD12" t="n">
         <v>11.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BF12" t="n">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="BG12" t="n">
-        <v>6.4</v>
+        <v>11</v>
       </c>
       <c r="BH12" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BI12" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="BJ12" t="n">
-        <v>11</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.25</v>
+        <v>1.58</v>
       </c>
       <c r="BN12" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BO12" t="n">
         <v>5.3</v>
@@ -3586,16 +3586,16 @@
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>3.95</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT12" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BU12" t="n">
         <v>5.3</v>
@@ -3604,23 +3604,23 @@
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="BX12" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-16 06:57:01</t>
+          <t>2026-06-16 09:06:36</t>
         </is>
       </c>
     </row>
@@ -3681,19 +3681,19 @@
         <v>1.09</v>
       </c>
       <c r="P13" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="R13" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="S13" t="n">
         <v>1.75</v>
       </c>
       <c r="T13" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="U13" t="n">
         <v>3.55</v>
@@ -3783,7 +3783,7 @@
         <v>16</v>
       </c>
       <c r="AX13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AY13" t="n">
         <v>14</v>
@@ -3813,40 +3813,40 @@
         <v>5.6</v>
       </c>
       <c r="BH13" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BI13" t="n">
         <v>5</v>
       </c>
       <c r="BJ13" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BK13" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="BL13" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BM13" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="BN13" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO13" t="n">
         <v>6</v>
       </c>
       <c r="BP13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BQ13" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BR13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BS13" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BT13" t="n">
         <v>6.6</v>
@@ -3858,23 +3858,23 @@
         <v>13.5</v>
       </c>
       <c r="BW13" t="n">
-        <v>6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX13" t="n">
         <v>17.5</v>
       </c>
       <c r="BY13" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BZ13" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-16 06:57:01</t>
+          <t>2026-06-16 09:06:36</t>
         </is>
       </c>
     </row>
@@ -3905,193 +3905,193 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="G14" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="H14" t="n">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="I14" t="n">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="J14" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K14" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L14" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="M14" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N14" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="O14" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="P14" t="n">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.18</v>
+        <v>1.98</v>
       </c>
       <c r="R14" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="S14" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="T14" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="U14" t="n">
-        <v>1.76</v>
+        <v>1.91</v>
       </c>
       <c r="V14" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="W14" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="X14" t="n">
-        <v>12.5</v>
+        <v>17</v>
       </c>
       <c r="Y14" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA14" t="n">
-        <v>290</v>
+        <v>200</v>
       </c>
       <c r="AB14" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC14" t="n">
         <v>9.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>950</v>
+        <v>25</v>
       </c>
       <c r="AE14" t="n">
-        <v>160</v>
+        <v>110</v>
       </c>
       <c r="AF14" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AG14" t="n">
         <v>10.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>950</v>
+        <v>24</v>
       </c>
       <c r="AI14" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO14" t="n">
         <v>150</v>
       </c>
-      <c r="AJ14" t="n">
-        <v>15</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>220</v>
-      </c>
-      <c r="AN14" t="n">
+      <c r="AP14" t="n">
         <v>12</v>
       </c>
-      <c r="AO14" t="n">
-        <v>250</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AQ14" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AR14" t="n">
-        <v>9.4</v>
+        <v>38</v>
       </c>
       <c r="AS14" t="n">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="AT14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU14" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV14" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX14" t="n">
         <v>8.6</v>
       </c>
-      <c r="AW14" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>7.6</v>
-      </c>
       <c r="AY14" t="n">
-        <v>5.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ14" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE14" t="n">
         <v>8.6</v>
       </c>
-      <c r="BA14" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>13</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>17</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>30</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BF14" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG14" t="n">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="BH14" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.56</v>
+        <v>2.78</v>
       </c>
       <c r="BJ14" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BK14" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BN14" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BO14" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="BP14" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BQ14" t="n">
         <v>5.6</v>
@@ -4100,35 +4100,35 @@
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT14" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU14" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="CA14" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-16 06:57:01</t>
+          <t>2026-06-16 09:06:36</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-16.xlsx
@@ -857,25 +857,25 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="G2" t="n">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="H2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I2" t="n">
         <v>4.5</v>
       </c>
-      <c r="I2" t="n">
-        <v>4.9</v>
-      </c>
       <c r="J2" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K2" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L2" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
@@ -884,151 +884,151 @@
         <v>4</v>
       </c>
       <c r="O2" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="R2" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="S2" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="T2" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U2" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V2" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="W2" t="n">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="X2" t="n">
-        <v>27</v>
+        <v>16.5</v>
       </c>
       <c r="Y2" t="n">
         <v>26</v>
       </c>
       <c r="Z2" t="n">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="AA2" t="n">
         <v>900</v>
       </c>
       <c r="AB2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE2" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="AF2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG2" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="AH2" t="n">
         <v>25</v>
       </c>
       <c r="AI2" t="n">
-        <v>320</v>
+        <v>420</v>
       </c>
       <c r="AJ2" t="n">
         <v>500</v>
       </c>
       <c r="AK2" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="AL2" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AM2" t="n">
         <v>580</v>
       </c>
       <c r="AN2" t="n">
-        <v>19.5</v>
+        <v>55</v>
       </c>
       <c r="AO2" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AP2" t="n">
         <v>13</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AR2" t="n">
         <v>14.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>9.4</v>
+        <v>65</v>
       </c>
       <c r="AT2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV2" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW2" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AX2" t="n">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="AY2" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ2" t="n">
         <v>11</v>
       </c>
       <c r="BA2" t="n">
-        <v>27</v>
+        <v>7.8</v>
       </c>
       <c r="BB2" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="BC2" t="n">
         <v>11</v>
       </c>
       <c r="BD2" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>29</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BG2" t="n">
         <v>8</v>
       </c>
-      <c r="BE2" t="n">
-        <v>9</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>12</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BH2" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="BJ2" t="n">
         <v>9.6</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
@@ -1043,34 +1043,34 @@
         <v>4.1</v>
       </c>
       <c r="BP2" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>9</v>
+        <v>6.8</v>
       </c>
       <c r="BT2" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>10.5</v>
+        <v>2.4</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-16 09:06:36</t>
+          <t>2026-06-16 11:17:21</t>
         </is>
       </c>
     </row>
@@ -1111,220 +1111,220 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="G3" t="n">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="H3" t="n">
-        <v>7.4</v>
+        <v>5.9</v>
       </c>
       <c r="I3" t="n">
-        <v>8.6</v>
+        <v>6.6</v>
       </c>
       <c r="J3" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K3" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="M3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="O3" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="P3" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="R3" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S3" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T3" t="n">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="U3" t="n">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="V3" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="W3" t="n">
-        <v>2.74</v>
+        <v>2.46</v>
       </c>
       <c r="X3" t="n">
         <v>15.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>500</v>
+        <v>19</v>
       </c>
       <c r="Z3" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AA3" t="n">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="AB3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AC3" t="n">
         <v>10</v>
       </c>
       <c r="AD3" t="n">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="AE3" t="n">
-        <v>700</v>
+        <v>260</v>
       </c>
       <c r="AF3" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AG3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH3" t="n">
-        <v>500</v>
+        <v>24</v>
       </c>
       <c r="AI3" t="n">
-        <v>700</v>
+        <v>110</v>
       </c>
       <c r="AJ3" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AK3" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="AL3" t="n">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="AM3" t="n">
         <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AO3" t="n">
-        <v>240</v>
+        <v>600</v>
       </c>
       <c r="AP3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>42</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>17</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>18</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>9</v>
+      </c>
+      <c r="BG3" t="n">
         <v>12.5</v>
       </c>
-      <c r="AQ3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV3" t="n">
+      <c r="BH3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ3" t="n">
         <v>11.5</v>
       </c>
-      <c r="AW3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>12</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>8</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>11</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BK3" t="n">
-        <v>8.6</v>
+        <v>6.2</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BN3" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BO3" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="BP3" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BX3" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-16 09:06:36</t>
+          <t>2026-06-16 11:17:21</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="G4" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="H4" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="I4" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="J4" t="n">
         <v>3.75</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L4" t="n">
         <v>1.35</v>
@@ -1389,7 +1389,7 @@
         <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O4" t="n">
         <v>1.25</v>
@@ -1398,13 +1398,13 @@
         <v>2.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="R4" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S4" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="T4" t="n">
         <v>1.63</v>
@@ -1413,22 +1413,22 @@
         <v>2.4</v>
       </c>
       <c r="V4" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="W4" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="X4" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA4" t="n">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="AB4" t="n">
         <v>13</v>
@@ -1440,10 +1440,10 @@
         <v>14</v>
       </c>
       <c r="AE4" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AF4" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AG4" t="n">
         <v>12</v>
@@ -1455,7 +1455,7 @@
         <v>40</v>
       </c>
       <c r="AJ4" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK4" t="n">
         <v>25</v>
@@ -1479,7 +1479,7 @@
         <v>13</v>
       </c>
       <c r="AR4" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AS4" t="n">
         <v>20</v>
@@ -1494,7 +1494,7 @@
         <v>11.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>17.5</v>
+        <v>28</v>
       </c>
       <c r="AX4" t="n">
         <v>14.5</v>
@@ -1506,19 +1506,19 @@
         <v>14</v>
       </c>
       <c r="BA4" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="BB4" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BC4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD4" t="n">
         <v>17.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="BF4" t="n">
         <v>13.5</v>
@@ -1527,58 +1527,58 @@
         <v>23</v>
       </c>
       <c r="BH4" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BI4" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="BJ4" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BK4" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="BN4" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BP4" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BR4" t="n">
         <v>28</v>
       </c>
       <c r="BS4" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BT4" t="n">
         <v>6.6</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BV4" t="n">
         <v>23</v>
       </c>
       <c r="BW4" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BX4" t="n">
         <v>32</v>
       </c>
       <c r="BY4" t="n">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-16 09:06:36</t>
+          <t>2026-06-16 11:17:21</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="G5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H5" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="I5" t="n">
         <v>1.43</v>
       </c>
       <c r="J5" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="K5" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="L5" t="n">
         <v>1.27</v>
@@ -1643,103 +1643,103 @@
         <v>1.03</v>
       </c>
       <c r="N5" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="O5" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P5" t="n">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="R5" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="S5" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="T5" t="n">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="U5" t="n">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="V5" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="W5" t="n">
         <v>1.12</v>
       </c>
       <c r="X5" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Y5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA5" t="n">
         <v>13</v>
       </c>
-      <c r="Z5" t="n">
-        <v>970</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>12</v>
-      </c>
       <c r="AB5" t="n">
-        <v>55</v>
+        <v>950</v>
       </c>
       <c r="AC5" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AD5" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AE5" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AF5" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AG5" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="AH5" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="AI5" t="n">
         <v>500</v>
       </c>
       <c r="AJ5" t="n">
-        <v>280</v>
+        <v>240</v>
       </c>
       <c r="AK5" t="n">
         <v>260</v>
       </c>
       <c r="AL5" t="n">
-        <v>230</v>
+        <v>260</v>
       </c>
       <c r="AM5" t="n">
-        <v>170</v>
+        <v>120</v>
       </c>
       <c r="AN5" t="n">
-        <v>170</v>
+        <v>110</v>
       </c>
       <c r="AO5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AP5" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5.5</v>
+        <v>11</v>
       </c>
       <c r="AR5" t="n">
         <v>8.4</v>
       </c>
       <c r="AS5" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AT5" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="AU5" t="n">
         <v>11</v>
@@ -1751,79 +1751,79 @@
         <v>11.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY5" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AZ5" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BA5" t="n">
         <v>11.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.2</v>
+        <v>9.6</v>
       </c>
       <c r="BC5" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="BD5" t="n">
-        <v>6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE5" t="n">
-        <v>15</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF5" t="n">
         <v>15</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BH5" t="n">
         <v>4.8</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BJ5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BN5" t="n">
         <v>12</v>
       </c>
       <c r="BO5" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT5" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BV5" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BW5" t="n">
         <v>4.9</v>
@@ -1832,7 +1832,7 @@
         <v>21</v>
       </c>
       <c r="BY5" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-16 09:06:36</t>
+          <t>2026-06-16 11:17:21</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="G6" t="n">
-        <v>1.92</v>
+        <v>1.99</v>
       </c>
       <c r="H6" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="I6" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J6" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K6" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L6" t="n">
         <v>1.39</v>
@@ -1897,16 +1897,16 @@
         <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O6" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P6" t="n">
         <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="R6" t="n">
         <v>1.39</v>
@@ -1915,25 +1915,25 @@
         <v>3.3</v>
       </c>
       <c r="T6" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="U6" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V6" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W6" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="X6" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA6" t="n">
         <v>330</v>
@@ -1942,13 +1942,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="AF6" t="n">
         <v>13</v>
@@ -1957,13 +1957,13 @@
         <v>10.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI6" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AJ6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK6" t="n">
         <v>21</v>
@@ -1972,37 +1972,37 @@
         <v>36</v>
       </c>
       <c r="AM6" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="AN6" t="n">
         <v>13.5</v>
       </c>
       <c r="AO6" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="AP6" t="n">
         <v>13</v>
       </c>
       <c r="AQ6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR6" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="AS6" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AT6" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU6" t="n">
         <v>7.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW6" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="AX6" t="n">
         <v>10</v>
@@ -2014,31 +2014,31 @@
         <v>15.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB6" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="BC6" t="n">
         <v>17</v>
       </c>
       <c r="BD6" t="n">
-        <v>7.4</v>
+        <v>15</v>
       </c>
       <c r="BE6" t="n">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BF6" t="n">
         <v>10.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="BJ6" t="n">
         <v>9.6</v>
@@ -2083,10 +2083,10 @@
         <v>10.5</v>
       </c>
       <c r="BX6" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BY6" t="n">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="BZ6" t="n">
         <v>23</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-16 09:06:36</t>
+          <t>2026-06-16 11:17:21</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K7" t="n">
         <v>4.2</v>
-      </c>
-      <c r="G7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K7" t="n">
-        <v>4.1</v>
       </c>
       <c r="L7" t="n">
         <v>1.39</v>
@@ -2151,37 +2151,37 @@
         <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O7" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="R7" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="S7" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="T7" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="U7" t="n">
         <v>2.04</v>
       </c>
       <c r="V7" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="W7" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="X7" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y7" t="n">
         <v>9.199999999999999</v>
@@ -2190,13 +2190,13 @@
         <v>12</v>
       </c>
       <c r="AA7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD7" t="n">
         <v>10.5</v>
@@ -2205,19 +2205,19 @@
         <v>21</v>
       </c>
       <c r="AF7" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AG7" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI7" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="AJ7" t="n">
-        <v>270</v>
+        <v>170</v>
       </c>
       <c r="AK7" t="n">
         <v>90</v>
@@ -2232,7 +2232,7 @@
         <v>100</v>
       </c>
       <c r="AO7" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AP7" t="n">
         <v>13.5</v>
@@ -2244,28 +2244,28 @@
         <v>10</v>
       </c>
       <c r="AS7" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AU7" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV7" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AW7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX7" t="n">
         <v>11.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA7" t="n">
         <v>16</v>
@@ -2274,83 +2274,83 @@
         <v>10.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BD7" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE7" t="n">
         <v>12.5</v>
       </c>
       <c r="BF7" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="BJ7" t="n">
         <v>10</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BN7" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO7" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BP7" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BQ7" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR7" t="n">
         <v>46</v>
       </c>
       <c r="BS7" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BT7" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BU7" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BV7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BW7" t="n">
         <v>6.4</v>
       </c>
       <c r="BX7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BY7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BZ7" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="CA7" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-16 09:06:36</t>
+          <t>2026-06-16 11:17:21</t>
         </is>
       </c>
     </row>
@@ -2381,25 +2381,25 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="G8" t="n">
         <v>1.57</v>
       </c>
       <c r="H8" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="I8" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="J8" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="K8" t="n">
         <v>5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M8" t="n">
         <v>1.04</v>
@@ -2411,154 +2411,154 @@
         <v>1.22</v>
       </c>
       <c r="P8" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="R8" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S8" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="T8" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="U8" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V8" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="W8" t="n">
         <v>2.74</v>
       </c>
       <c r="X8" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="Y8" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="Z8" t="n">
-        <v>220</v>
+        <v>60</v>
       </c>
       <c r="AA8" t="n">
-        <v>700</v>
+        <v>200</v>
       </c>
       <c r="AB8" t="n">
         <v>10.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD8" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AE8" t="n">
         <v>400</v>
       </c>
       <c r="AF8" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG8" t="n">
         <v>10</v>
       </c>
       <c r="AH8" t="n">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="AI8" t="n">
-        <v>700</v>
+        <v>320</v>
       </c>
       <c r="AJ8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK8" t="n">
         <v>15.5</v>
       </c>
-      <c r="AK8" t="n">
-        <v>29</v>
-      </c>
       <c r="AL8" t="n">
-        <v>95</v>
+        <v>32</v>
       </c>
       <c r="AM8" t="n">
         <v>700</v>
       </c>
       <c r="AN8" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AO8" t="n">
         <v>85</v>
       </c>
       <c r="AP8" t="n">
-        <v>9</v>
+        <v>19.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AR8" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="AS8" t="n">
-        <v>11.5</v>
+        <v>16.5</v>
       </c>
       <c r="AT8" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AU8" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AV8" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AW8" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="AX8" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AY8" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA8" t="n">
-        <v>10.5</v>
+        <v>28</v>
       </c>
       <c r="BB8" t="n">
         <v>13</v>
       </c>
       <c r="BC8" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>9.800000000000001</v>
+        <v>18</v>
       </c>
       <c r="BE8" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="BF8" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BG8" t="n">
-        <v>10.5</v>
+        <v>38</v>
       </c>
       <c r="BH8" t="n">
         <v>4.2</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BJ8" t="n">
         <v>10</v>
       </c>
       <c r="BK8" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="BN8" t="n">
         <v>4.3</v>
@@ -2567,7 +2567,7 @@
         <v>3.85</v>
       </c>
       <c r="BP8" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BQ8" t="n">
         <v>6</v>
@@ -2576,25 +2576,25 @@
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BT8" t="n">
         <v>10</v>
       </c>
       <c r="BU8" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-16 09:06:36</t>
+          <t>2026-06-16 11:17:21</t>
         </is>
       </c>
     </row>
@@ -2635,43 +2635,43 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="G9" t="n">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="H9" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="I9" t="n">
         <v>3.25</v>
       </c>
-      <c r="I9" t="n">
-        <v>3.4</v>
-      </c>
       <c r="J9" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K9" t="n">
         <v>3.95</v>
       </c>
       <c r="L9" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M9" t="n">
         <v>1.04</v>
       </c>
       <c r="N9" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O9" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P9" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="R9" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="S9" t="n">
         <v>2.66</v>
@@ -2680,25 +2680,25 @@
         <v>1.55</v>
       </c>
       <c r="U9" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="V9" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="W9" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="X9" t="n">
         <v>26</v>
       </c>
       <c r="Y9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Z9" t="n">
         <v>25</v>
       </c>
       <c r="AA9" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB9" t="n">
         <v>14.5</v>
@@ -2710,13 +2710,13 @@
         <v>14</v>
       </c>
       <c r="AE9" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF9" t="n">
         <v>17</v>
       </c>
       <c r="AG9" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH9" t="n">
         <v>14.5</v>
@@ -2725,7 +2725,7 @@
         <v>38</v>
       </c>
       <c r="AJ9" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AK9" t="n">
         <v>22</v>
@@ -2734,37 +2734,37 @@
         <v>29</v>
       </c>
       <c r="AM9" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AN9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>23</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>44</v>
+      </c>
+      <c r="AT9" t="n">
         <v>12.5</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>24</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>22</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>23</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>46</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>13</v>
       </c>
       <c r="AU9" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AV9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AX9" t="n">
         <v>15</v>
@@ -2773,7 +2773,7 @@
         <v>10</v>
       </c>
       <c r="AZ9" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BA9" t="n">
         <v>32</v>
@@ -2785,7 +2785,7 @@
         <v>19</v>
       </c>
       <c r="BD9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BE9" t="n">
         <v>50</v>
@@ -2794,71 +2794,71 @@
         <v>11.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BH9" t="n">
         <v>4.1</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BJ9" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="BN9" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BO9" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BP9" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>8</v>
+        <v>13.5</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BT9" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BU9" t="n">
         <v>6</v>
       </c>
       <c r="BV9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BW9" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BX9" t="n">
         <v>29</v>
       </c>
       <c r="BY9" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BZ9" t="n">
         <v>17.5</v>
       </c>
       <c r="CA9" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-16 09:06:36</t>
+          <t>2026-06-16 11:17:21</t>
         </is>
       </c>
     </row>
@@ -2892,7 +2892,7 @@
         <v>2.46</v>
       </c>
       <c r="G10" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="H10" t="n">
         <v>2.92</v>
@@ -2901,37 +2901,37 @@
         <v>3</v>
       </c>
       <c r="J10" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K10" t="n">
         <v>3.85</v>
       </c>
       <c r="L10" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M10" t="n">
         <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O10" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P10" t="n">
         <v>2.36</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="R10" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="S10" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="T10" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="U10" t="n">
         <v>2.58</v>
@@ -2943,25 +2943,25 @@
         <v>1.65</v>
       </c>
       <c r="X10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Y10" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z10" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AA10" t="n">
         <v>44</v>
       </c>
       <c r="AB10" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD10" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE10" t="n">
         <v>29</v>
@@ -2976,7 +2976,7 @@
         <v>15</v>
       </c>
       <c r="AI10" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="AJ10" t="n">
         <v>34</v>
@@ -2988,28 +2988,28 @@
         <v>32</v>
       </c>
       <c r="AM10" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AN10" t="n">
         <v>15</v>
       </c>
       <c r="AO10" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AP10" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AQ10" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AR10" t="n">
         <v>20</v>
       </c>
       <c r="AS10" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AT10" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU10" t="n">
         <v>8.199999999999999</v>
@@ -3018,7 +3018,7 @@
         <v>11.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AX10" t="n">
         <v>16.5</v>
@@ -3036,10 +3036,10 @@
         <v>30</v>
       </c>
       <c r="BC10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BE10" t="n">
         <v>55</v>
@@ -3048,16 +3048,16 @@
         <v>14</v>
       </c>
       <c r="BG10" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BH10" t="n">
         <v>4.1</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BJ10" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BK10" t="n">
         <v>6.6</v>
@@ -3066,25 +3066,25 @@
         <v>80</v>
       </c>
       <c r="BM10" t="n">
-        <v>12.5</v>
+        <v>70</v>
       </c>
       <c r="BN10" t="n">
         <v>5.8</v>
       </c>
       <c r="BO10" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BP10" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BQ10" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BR10" t="n">
         <v>26</v>
       </c>
       <c r="BS10" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BT10" t="n">
         <v>6.4</v>
@@ -3093,16 +3093,16 @@
         <v>5.6</v>
       </c>
       <c r="BV10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BW10" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="BX10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BY10" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-16 09:06:36</t>
+          <t>2026-06-16 11:17:21</t>
         </is>
       </c>
     </row>
@@ -3143,148 +3143,148 @@
         </is>
       </c>
       <c r="F11" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G11" t="n">
         <v>1.5</v>
       </c>
-      <c r="G11" t="n">
-        <v>1.52</v>
-      </c>
       <c r="H11" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I11" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="J11" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="K11" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="L11" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="M11" t="n">
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O11" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="P11" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="R11" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="S11" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="T11" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="U11" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="V11" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W11" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="X11" t="n">
-        <v>950</v>
+        <v>70</v>
       </c>
       <c r="Y11" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="Z11" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="AA11" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AB11" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="AC11" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AD11" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="AE11" t="n">
-        <v>160</v>
+        <v>60</v>
       </c>
       <c r="AF11" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AG11" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI11" t="n">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="AJ11" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AK11" t="n">
         <v>14</v>
       </c>
       <c r="AL11" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AM11" t="n">
         <v>55</v>
       </c>
       <c r="AN11" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="AO11" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AP11" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AQ11" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AR11" t="n">
+        <v>65</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>44</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>24</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>25</v>
+      </c>
+      <c r="AW11" t="n">
         <v>50</v>
       </c>
-      <c r="AS11" t="n">
-        <v>48</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>21</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>23</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>46</v>
-      </c>
       <c r="AX11" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AY11" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ11" t="n">
         <v>14.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="BB11" t="n">
         <v>17</v>
@@ -3293,34 +3293,34 @@
         <v>12.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="BE11" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="BF11" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="BG11" t="n">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="BH11" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BI11" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BJ11" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK11" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="BN11" t="n">
         <v>5.5</v>
@@ -3329,44 +3329,44 @@
         <v>4.9</v>
       </c>
       <c r="BP11" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BR11" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BS11" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BT11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BU11" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BV11" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BW11" t="n">
         <v>10.5</v>
       </c>
       <c r="BX11" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BY11" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ11" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="CA11" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-16 09:06:36</t>
+          <t>2026-06-16 11:17:21</t>
         </is>
       </c>
     </row>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G12" t="n">
         <v>2.26</v>
@@ -3406,7 +3406,7 @@
         <v>3.1</v>
       </c>
       <c r="I12" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J12" t="n">
         <v>4.2</v>
@@ -3415,40 +3415,40 @@
         <v>4.4</v>
       </c>
       <c r="L12" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="M12" t="n">
         <v>1.02</v>
       </c>
       <c r="N12" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="O12" t="n">
         <v>1.09</v>
       </c>
       <c r="P12" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="R12" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="S12" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="T12" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="U12" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="V12" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W12" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="X12" t="n">
         <v>950</v>
@@ -3457,13 +3457,13 @@
         <v>70</v>
       </c>
       <c r="Z12" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AA12" t="n">
-        <v>290</v>
+        <v>210</v>
       </c>
       <c r="AB12" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AC12" t="n">
         <v>12.5</v>
@@ -3475,7 +3475,7 @@
         <v>160</v>
       </c>
       <c r="AF12" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AG12" t="n">
         <v>13</v>
@@ -3487,13 +3487,13 @@
         <v>120</v>
       </c>
       <c r="AJ12" t="n">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="AK12" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="AL12" t="n">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="AM12" t="n">
         <v>580</v>
@@ -3502,16 +3502,16 @@
         <v>7.4</v>
       </c>
       <c r="AO12" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="AP12" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AQ12" t="n">
         <v>13</v>
       </c>
       <c r="AR12" t="n">
-        <v>14.5</v>
+        <v>23</v>
       </c>
       <c r="AS12" t="n">
         <v>23</v>
@@ -3520,16 +3520,16 @@
         <v>12.5</v>
       </c>
       <c r="AU12" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AV12" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AW12" t="n">
         <v>15</v>
       </c>
       <c r="AX12" t="n">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="AY12" t="n">
         <v>7.2</v>
@@ -3541,61 +3541,61 @@
         <v>15</v>
       </c>
       <c r="BB12" t="n">
-        <v>14.5</v>
+        <v>25</v>
       </c>
       <c r="BC12" t="n">
-        <v>11</v>
+        <v>16.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>11.5</v>
+        <v>18.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BF12" t="n">
         <v>6.4</v>
       </c>
       <c r="BG12" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="BH12" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BI12" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BJ12" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.58</v>
+        <v>42</v>
       </c>
       <c r="BN12" t="n">
-        <v>8.4</v>
+        <v>6.2</v>
       </c>
       <c r="BO12" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BP12" t="n">
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BT12" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BU12" t="n">
         <v>5.3</v>
@@ -3604,23 +3604,23 @@
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.76</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CA12" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-16 09:06:36</t>
+          <t>2026-06-16 11:17:21</t>
         </is>
       </c>
     </row>
@@ -3651,22 +3651,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="G13" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H13" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="I13" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="J13" t="n">
         <v>4.5</v>
       </c>
       <c r="K13" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="L13" t="n">
         <v>1.19</v>
@@ -3675,49 +3675,49 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O13" t="n">
         <v>1.09</v>
       </c>
       <c r="P13" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="R13" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="S13" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="T13" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="U13" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="V13" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="W13" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X13" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="Y13" t="n">
         <v>28</v>
       </c>
       <c r="Z13" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AA13" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AB13" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AC13" t="n">
         <v>14.5</v>
@@ -3726,7 +3726,7 @@
         <v>13.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AF13" t="n">
         <v>42</v>
@@ -3735,7 +3735,7 @@
         <v>17</v>
       </c>
       <c r="AH13" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AI13" t="n">
         <v>21</v>
@@ -3747,34 +3747,34 @@
         <v>32</v>
       </c>
       <c r="AL13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AM13" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AN13" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AO13" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AP13" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AQ13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AR13" t="n">
         <v>21</v>
       </c>
-      <c r="AR13" t="n">
-        <v>20</v>
-      </c>
       <c r="AS13" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AT13" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="AU13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AV13" t="n">
         <v>11.5</v>
@@ -3783,7 +3783,7 @@
         <v>16</v>
       </c>
       <c r="AX13" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AY13" t="n">
         <v>14</v>
@@ -3792,89 +3792,89 @@
         <v>12</v>
       </c>
       <c r="BA13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BB13" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BC13" t="n">
         <v>23</v>
       </c>
       <c r="BD13" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BE13" t="n">
         <v>24</v>
       </c>
       <c r="BF13" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BG13" t="n">
         <v>5.6</v>
       </c>
       <c r="BH13" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BI13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>44</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>40</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO13" t="n">
         <v>5</v>
       </c>
-      <c r="BJ13" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BK13" t="n">
+      <c r="BP13" t="n">
+        <v>20</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>8</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>21</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT13" t="n">
         <v>6.4</v>
       </c>
-      <c r="BL13" t="n">
-        <v>46</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>6</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>21</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>22</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BU13" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BV13" t="n">
         <v>13.5</v>
       </c>
       <c r="BW13" t="n">
-        <v>9.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="BX13" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BY13" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BZ13" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CA13" t="n">
-        <v>7.2</v>
+        <v>5.3</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-16 09:06:36</t>
+          <t>2026-06-16 11:17:21</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
         <v>1.66</v>
       </c>
       <c r="G14" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="H14" t="n">
         <v>6</v>
@@ -3935,55 +3935,55 @@
         <v>1.34</v>
       </c>
       <c r="P14" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="R14" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="S14" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="T14" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="U14" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="V14" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W14" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="X14" t="n">
-        <v>17</v>
+        <v>13.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="Z14" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA14" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AB14" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD14" t="n">
         <v>25</v>
       </c>
       <c r="AE14" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AF14" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AG14" t="n">
         <v>10.5</v>
@@ -3995,85 +3995,85 @@
         <v>110</v>
       </c>
       <c r="AJ14" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AK14" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AL14" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AM14" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AN14" t="n">
         <v>11</v>
       </c>
       <c r="AO14" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AP14" t="n">
         <v>12</v>
       </c>
       <c r="AQ14" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AS14" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AT14" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX14" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AV14" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>8.6</v>
-      </c>
       <c r="AY14" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ14" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>8.199999999999999</v>
+        <v>36</v>
       </c>
       <c r="BB14" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BC14" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>7.4</v>
+        <v>32</v>
       </c>
       <c r="BE14" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BF14" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BG14" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BH14" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="BJ14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BK14" t="n">
         <v>5.5</v>
@@ -4082,22 +4082,22 @@
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN14" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BO14" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="BP14" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BR14" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS14" t="n">
         <v>7.8</v>
@@ -4106,29 +4106,29 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BU14" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BZ14" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="CA14" t="n">
         <v>7.2</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-16 09:06:36</t>
+          <t>2026-06-16 11:17:21</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-16.xlsx
@@ -857,220 +857,220 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.95</v>
+        <v>5.1</v>
       </c>
       <c r="G2" t="n">
-        <v>2.04</v>
+        <v>5.6</v>
       </c>
       <c r="H2" t="n">
-        <v>4.1</v>
+        <v>5.8</v>
       </c>
       <c r="I2" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="J2" t="n">
-        <v>3.65</v>
+        <v>1.51</v>
       </c>
       <c r="K2" t="n">
-        <v>3.85</v>
+        <v>1.56</v>
       </c>
       <c r="L2" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1.07</v>
+        <v>2.4</v>
       </c>
       <c r="N2" t="n">
-        <v>4</v>
+        <v>1.09</v>
       </c>
       <c r="O2" t="n">
-        <v>1.31</v>
+        <v>10</v>
       </c>
       <c r="P2" t="n">
-        <v>1.99</v>
+        <v>1.01</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.96</v>
+        <v>50</v>
       </c>
       <c r="R2" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="S2" t="n">
-        <v>3.45</v>
+        <v>340</v>
       </c>
       <c r="T2" t="n">
-        <v>1.76</v>
+        <v>21</v>
       </c>
       <c r="U2" t="n">
-        <v>2.18</v>
+        <v>1.04</v>
       </c>
       <c r="V2" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="W2" t="n">
-        <v>1.96</v>
+        <v>1.24</v>
       </c>
       <c r="X2" t="n">
-        <v>16.5</v>
+        <v>1.72</v>
       </c>
       <c r="Y2" t="n">
-        <v>26</v>
+        <v>7.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AA2" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>10</v>
+        <v>6.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.4</v>
+        <v>30</v>
       </c>
       <c r="AD2" t="n">
-        <v>29</v>
+        <v>420</v>
       </c>
       <c r="AE2" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="AG2" t="n">
-        <v>10</v>
+        <v>350</v>
       </c>
       <c r="AH2" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>420</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>13</v>
+        <v>1.61</v>
       </c>
       <c r="AQ2" t="n">
-        <v>14</v>
+        <v>6.2</v>
       </c>
       <c r="AR2" t="n">
+        <v>42</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>23</v>
+      </c>
+      <c r="AV2" t="n">
         <v>14.5</v>
       </c>
-      <c r="AS2" t="n">
-        <v>65</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AW2" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AX2" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="AY2" t="n">
-        <v>8.6</v>
+        <v>16</v>
       </c>
       <c r="AZ2" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.8</v>
+        <v>15</v>
       </c>
       <c r="BB2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="BC2" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="BD2" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="BE2" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="BF2" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BG2" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BQ2" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BT2" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW2" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-16 11:17:21</t>
+          <t>2026-06-16 13:41:22</t>
         </is>
       </c>
     </row>
@@ -1111,220 +1111,220 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="G3" t="n">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="H3" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="I3" t="n">
+        <v>8</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>150</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>46</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC3" t="n">
         <v>6.6</v>
       </c>
-      <c r="J3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="W3" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="X3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>19</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>160</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>260</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>18</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>600</v>
-      </c>
-      <c r="AP3" t="n">
+      <c r="BD3" t="n">
         <v>13.5</v>
       </c>
-      <c r="AQ3" t="n">
-        <v>17</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>42</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>17</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>34</v>
-      </c>
       <c r="BE3" t="n">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="BF3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BG3" t="n">
-        <v>12.5</v>
+        <v>80</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BK3" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM3" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS3" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BT3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BV3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-16 11:17:21</t>
+          <t>2026-06-16 13:41:22</t>
         </is>
       </c>
     </row>
@@ -1365,220 +1365,220 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.34</v>
+        <v>2.8</v>
       </c>
       <c r="G4" t="n">
-        <v>2.42</v>
+        <v>2.86</v>
       </c>
       <c r="H4" t="n">
         <v>3.05</v>
       </c>
       <c r="I4" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J4" t="n">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="K4" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="L4" t="n">
-        <v>1.35</v>
+        <v>2.6</v>
       </c>
       <c r="M4" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="N4" t="n">
-        <v>4.6</v>
+        <v>2.36</v>
       </c>
       <c r="O4" t="n">
-        <v>1.25</v>
+        <v>1.69</v>
       </c>
       <c r="P4" t="n">
-        <v>2.2</v>
+        <v>1.45</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.76</v>
+        <v>3.05</v>
       </c>
       <c r="R4" t="n">
-        <v>1.46</v>
+        <v>1.14</v>
       </c>
       <c r="S4" t="n">
-        <v>2.92</v>
+        <v>7.4</v>
       </c>
       <c r="T4" t="n">
-        <v>1.63</v>
+        <v>2.36</v>
       </c>
       <c r="U4" t="n">
-        <v>2.4</v>
+        <v>1.62</v>
       </c>
       <c r="V4" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="W4" t="n">
-        <v>1.7</v>
+        <v>1.49</v>
       </c>
       <c r="X4" t="n">
-        <v>18.5</v>
+        <v>7.8</v>
       </c>
       <c r="Y4" t="n">
-        <v>16.5</v>
+        <v>7.8</v>
       </c>
       <c r="Z4" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AA4" t="n">
         <v>55</v>
       </c>
       <c r="AB4" t="n">
-        <v>13</v>
+        <v>7.4</v>
       </c>
       <c r="AC4" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="AD4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>130</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>390</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>70</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>95</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>42</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>44</v>
+      </c>
+      <c r="AX4" t="n">
         <v>14</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AY4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>26</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>85</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>42</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>40</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>80</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>220</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>55</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>55</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>46</v>
+      </c>
+      <c r="BK4" t="n">
         <v>36</v>
       </c>
-      <c r="AF4" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM4" t="n">
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>95</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>75</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BV4" t="n">
         <v>110</v>
       </c>
-      <c r="AN4" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>29</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>20</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>28</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>20</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>25</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>23</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>9</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>17</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>28</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>9</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>23</v>
-      </c>
       <c r="BW4" t="n">
-        <v>8.4</v>
+        <v>75</v>
       </c>
       <c r="BX4" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>9.4</v>
+        <v>4.2</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-16 11:17:21</t>
+          <t>2026-06-16 13:41:22</t>
         </is>
       </c>
     </row>
@@ -1619,220 +1619,220 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H5" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="I5" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="J5" t="n">
-        <v>5.4</v>
+        <v>4.3</v>
       </c>
       <c r="K5" t="n">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="L5" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.84</v>
+        <v>9.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.51</v>
+        <v>1.1</v>
       </c>
       <c r="R5" t="n">
-        <v>1.72</v>
+        <v>2.86</v>
       </c>
       <c r="S5" t="n">
-        <v>2.3</v>
+        <v>1.44</v>
       </c>
       <c r="T5" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="W5" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X5" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>9.4</v>
+        <v>5.6</v>
       </c>
       <c r="AE5" t="n">
-        <v>14.5</v>
+        <v>6.6</v>
       </c>
       <c r="AF5" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="AH5" t="n">
-        <v>25</v>
+        <v>10.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>500</v>
+        <v>12</v>
       </c>
       <c r="AJ5" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>260</v>
+        <v>100</v>
       </c>
       <c r="AL5" t="n">
-        <v>260</v>
+        <v>55</v>
       </c>
       <c r="AM5" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AN5" t="n">
         <v>110</v>
       </c>
       <c r="AO5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>34</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>12</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>11</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>930</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>50</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>11</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>11</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>18</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>15</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>11</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>11</v>
+      </c>
+      <c r="BX5" t="n">
         <v>5.1</v>
       </c>
-      <c r="AP5" t="n">
-        <v>25</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>9</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>15</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>12</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>21</v>
-      </c>
       <c r="BY5" t="n">
-        <v>7.6</v>
+        <v>4.6</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-16 11:17:21</t>
+          <t>2026-06-16 13:41:22</t>
         </is>
       </c>
     </row>
@@ -1873,230 +1873,230 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.9</v>
+        <v>1.42</v>
       </c>
       <c r="G6" t="n">
-        <v>1.99</v>
+        <v>1.45</v>
       </c>
       <c r="H6" t="n">
-        <v>4.5</v>
+        <v>9.4</v>
       </c>
       <c r="I6" t="n">
-        <v>5</v>
+        <v>10.5</v>
       </c>
       <c r="J6" t="n">
-        <v>3.45</v>
+        <v>4.8</v>
       </c>
       <c r="K6" t="n">
-        <v>3.7</v>
+        <v>5.2</v>
       </c>
       <c r="L6" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>4</v>
+        <v>8.4</v>
       </c>
       <c r="O6" t="n">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>2.54</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.92</v>
+        <v>1.61</v>
       </c>
       <c r="R6" t="n">
-        <v>1.39</v>
+        <v>1.52</v>
       </c>
       <c r="S6" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="T6" t="n">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="U6" t="n">
-        <v>2.12</v>
+        <v>2.56</v>
       </c>
       <c r="V6" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="W6" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="X6" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>330</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD6" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AE6" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>13</v>
+        <v>7.8</v>
       </c>
       <c r="AG6" t="n">
-        <v>10.5</v>
+        <v>7.2</v>
       </c>
       <c r="AH6" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AI6" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="AK6" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AL6" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM6" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AO6" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>13</v>
+        <v>7.6</v>
       </c>
       <c r="AQ6" t="n">
-        <v>14</v>
+        <v>7.6</v>
       </c>
       <c r="AR6" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AS6" t="n">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="AT6" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AU6" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>44</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>13</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>700</v>
+      </c>
+      <c r="BM6" t="n">
         <v>15</v>
       </c>
-      <c r="AW6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>17</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>15</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>11</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
+      <c r="BN6" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>46</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>32</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU6" t="n">
         <v>13</v>
       </c>
-      <c r="BN6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>4</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>7</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>27</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BV6" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BX6" t="n">
+        <v>150</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>80</v>
+      </c>
+      <c r="BZ6" t="n">
         <v>60</v>
       </c>
-      <c r="BY6" t="n">
-        <v>12</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>23</v>
-      </c>
       <c r="CA6" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-16 11:17:21</t>
+          <t>2026-06-16 13:41:22</t>
         </is>
       </c>
     </row>
@@ -2127,175 +2127,175 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="G7" t="n">
-        <v>4.8</v>
+        <v>2.36</v>
       </c>
       <c r="H7" t="n">
-        <v>1.85</v>
+        <v>3.5</v>
       </c>
       <c r="I7" t="n">
-        <v>1.86</v>
+        <v>3.7</v>
       </c>
       <c r="J7" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="K7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>8</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="U7" t="n">
         <v>4.2</v>
       </c>
-      <c r="L7" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N7" t="n">
-        <v>4</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.04</v>
-      </c>
       <c r="V7" t="n">
-        <v>2.16</v>
+        <v>1.38</v>
       </c>
       <c r="W7" t="n">
-        <v>1.27</v>
+        <v>1.71</v>
       </c>
       <c r="X7" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AH7" t="n">
         <v>12</v>
       </c>
-      <c r="AA7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>17</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>36</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>21</v>
-      </c>
       <c r="AI7" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="AJ7" t="n">
-        <v>170</v>
+        <v>38</v>
       </c>
       <c r="AK7" t="n">
-        <v>90</v>
+        <v>32</v>
       </c>
       <c r="AL7" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="AM7" t="n">
-        <v>200</v>
+        <v>110</v>
       </c>
       <c r="AN7" t="n">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="AO7" t="n">
-        <v>12.5</v>
+        <v>29</v>
       </c>
       <c r="AP7" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>8.199999999999999</v>
+        <v>15.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>10</v>
+        <v>15.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>14</v>
+        <v>7.8</v>
       </c>
       <c r="AU7" t="n">
-        <v>7.8</v>
+        <v>5</v>
       </c>
       <c r="AV7" t="n">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="AW7" t="n">
         <v>17</v>
       </c>
       <c r="AX7" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY7" t="n">
-        <v>15.5</v>
+        <v>8</v>
       </c>
       <c r="AZ7" t="n">
-        <v>17.5</v>
+        <v>10.5</v>
       </c>
       <c r="BA7" t="n">
+        <v>24</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>34</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>27</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>70</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>38</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>23</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI7" t="n">
         <v>16</v>
       </c>
-      <c r="BB7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>2.84</v>
-      </c>
       <c r="BJ7" t="n">
-        <v>10</v>
+        <v>6.8</v>
       </c>
       <c r="BK7" t="n">
         <v>5.6</v>
@@ -2304,53 +2304,53 @@
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>11.5</v>
+        <v>44</v>
       </c>
       <c r="BN7" t="n">
-        <v>8.199999999999999</v>
+        <v>1.4</v>
       </c>
       <c r="BO7" t="n">
-        <v>6</v>
+        <v>1.33</v>
       </c>
       <c r="BP7" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="BQ7" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BR7" t="n">
-        <v>46</v>
+        <v>170</v>
       </c>
       <c r="BS7" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="BT7" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>3.55</v>
+        <v>16</v>
       </c>
       <c r="BV7" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>6.4</v>
+        <v>16</v>
       </c>
       <c r="BX7" t="n">
-        <v>27</v>
+        <v>140</v>
       </c>
       <c r="BY7" t="n">
-        <v>8.6</v>
+        <v>42</v>
       </c>
       <c r="BZ7" t="n">
-        <v>22</v>
+        <v>830</v>
       </c>
       <c r="CA7" t="n">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-16 11:17:21</t>
+          <t>2026-06-16 13:41:22</t>
         </is>
       </c>
     </row>
@@ -2381,82 +2381,82 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="G8" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="H8" t="n">
         <v>6.4</v>
       </c>
       <c r="I8" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="J8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N8" t="n">
         <v>4.6</v>
       </c>
-      <c r="K8" t="n">
-        <v>5</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N8" t="n">
-        <v>5.1</v>
-      </c>
       <c r="O8" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="P8" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="R8" t="n">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="S8" t="n">
-        <v>2.72</v>
+        <v>3.05</v>
       </c>
       <c r="T8" t="n">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="U8" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="V8" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W8" t="n">
-        <v>2.74</v>
+        <v>2.6</v>
       </c>
       <c r="X8" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="Z8" t="n">
         <v>60</v>
       </c>
       <c r="AA8" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AB8" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC8" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD8" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="AE8" t="n">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="AF8" t="n">
         <v>10</v>
@@ -2468,133 +2468,133 @@
         <v>21</v>
       </c>
       <c r="AI8" t="n">
-        <v>320</v>
+        <v>95</v>
       </c>
       <c r="AJ8" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AK8" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AL8" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AM8" t="n">
-        <v>700</v>
+        <v>120</v>
       </c>
       <c r="AN8" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="AO8" t="n">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="AP8" t="n">
-        <v>19.5</v>
+        <v>16</v>
       </c>
       <c r="AQ8" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AR8" t="n">
         <v>44</v>
       </c>
       <c r="AS8" t="n">
-        <v>16.5</v>
+        <v>130</v>
       </c>
       <c r="AT8" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU8" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AV8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW8" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="AX8" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AY8" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ8" t="n">
         <v>18</v>
       </c>
       <c r="BA8" t="n">
+        <v>70</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD8" t="n">
         <v>28</v>
       </c>
-      <c r="BB8" t="n">
-        <v>13</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>18</v>
-      </c>
       <c r="BE8" t="n">
-        <v>28</v>
+        <v>85</v>
       </c>
       <c r="BF8" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BG8" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="BH8" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>960</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>110</v>
+      </c>
+      <c r="BN8" t="n">
         <v>4.2</v>
       </c>
-      <c r="BI8" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>10</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BO8" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="BP8" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BQ8" t="n">
-        <v>6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR8" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS8" t="n">
+        <v>24</v>
+      </c>
+      <c r="BT8" t="n">
         <v>9.6</v>
       </c>
-      <c r="BT8" t="n">
-        <v>10</v>
-      </c>
       <c r="BU8" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="BV8" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BW8" t="n">
-        <v>12.5</v>
+        <v>44</v>
       </c>
       <c r="BX8" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BY8" t="n">
-        <v>12.5</v>
+        <v>55</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-16 11:17:21</t>
+          <t>2026-06-16 13:41:22</t>
         </is>
       </c>
     </row>
@@ -2635,79 +2635,79 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="G9" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="H9" t="n">
         <v>3.15</v>
       </c>
       <c r="I9" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J9" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="K9" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="L9" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M9" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="O9" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P9" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="R9" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="S9" t="n">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="T9" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="U9" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="V9" t="n">
         <v>1.45</v>
       </c>
       <c r="W9" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="X9" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="Y9" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Z9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA9" t="n">
         <v>55</v>
       </c>
       <c r="AB9" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE9" t="n">
         <v>32</v>
@@ -2716,49 +2716,49 @@
         <v>17</v>
       </c>
       <c r="AG9" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AI9" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ9" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AK9" t="n">
         <v>22</v>
       </c>
       <c r="AL9" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AM9" t="n">
         <v>60</v>
       </c>
       <c r="AN9" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AO9" t="n">
         <v>23</v>
       </c>
       <c r="AP9" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS9" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AT9" t="n">
         <v>12.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AV9" t="n">
         <v>12</v>
@@ -2767,7 +2767,7 @@
         <v>28</v>
       </c>
       <c r="AX9" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AY9" t="n">
         <v>10</v>
@@ -2779,10 +2779,10 @@
         <v>32</v>
       </c>
       <c r="BB9" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BC9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD9" t="n">
         <v>26</v>
@@ -2791,16 +2791,16 @@
         <v>50</v>
       </c>
       <c r="BF9" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BG9" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BH9" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BJ9" t="n">
         <v>8.6</v>
@@ -2809,7 +2809,7 @@
         <v>7.6</v>
       </c>
       <c r="BL9" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BM9" t="n">
         <v>65</v>
@@ -2821,44 +2821,44 @@
         <v>5</v>
       </c>
       <c r="BP9" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BQ9" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BR9" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BS9" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BT9" t="n">
         <v>6.6</v>
       </c>
       <c r="BU9" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BV9" t="n">
         <v>22</v>
       </c>
       <c r="BW9" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="BX9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BY9" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BZ9" t="n">
         <v>17.5</v>
       </c>
       <c r="CA9" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-16 11:17:21</t>
+          <t>2026-06-16 13:41:22</t>
         </is>
       </c>
     </row>
@@ -2889,139 +2889,139 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="G10" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="H10" t="n">
-        <v>2.92</v>
+        <v>2.82</v>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="J10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K10" t="n">
         <v>3.8</v>
       </c>
-      <c r="K10" t="n">
-        <v>3.85</v>
-      </c>
       <c r="L10" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="M10" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N10" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="O10" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="P10" t="n">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="R10" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="S10" t="n">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="T10" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="U10" t="n">
-        <v>2.58</v>
+        <v>2.48</v>
       </c>
       <c r="V10" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="W10" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="X10" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z10" t="n">
         <v>21</v>
       </c>
       <c r="AA10" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AB10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH10" t="n">
         <v>14.5</v>
       </c>
-      <c r="AC10" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>29</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>15</v>
-      </c>
       <c r="AI10" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL10" t="n">
         <v>34</v>
       </c>
-      <c r="AJ10" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>32</v>
-      </c>
       <c r="AM10" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AN10" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AO10" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AP10" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR10" t="n">
         <v>19</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>20</v>
       </c>
       <c r="AS10" t="n">
         <v>40</v>
       </c>
       <c r="AT10" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AU10" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AV10" t="n">
         <v>11.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX10" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AY10" t="n">
         <v>10.5</v>
@@ -3030,31 +3030,31 @@
         <v>13.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BB10" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BC10" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BD10" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BE10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BF10" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BH10" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BJ10" t="n">
         <v>8.6</v>
@@ -3063,13 +3063,13 @@
         <v>6.6</v>
       </c>
       <c r="BL10" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="BM10" t="n">
         <v>70</v>
       </c>
       <c r="BN10" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BO10" t="n">
         <v>5.2</v>
@@ -3078,31 +3078,31 @@
         <v>17.5</v>
       </c>
       <c r="BQ10" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BS10" t="n">
-        <v>10</v>
+        <v>14.5</v>
       </c>
       <c r="BT10" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BU10" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BV10" t="n">
         <v>20</v>
       </c>
       <c r="BW10" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BX10" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BY10" t="n">
-        <v>10</v>
+        <v>15.5</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-16 11:17:21</t>
+          <t>2026-06-16 13:41:22</t>
         </is>
       </c>
     </row>
@@ -3143,100 +3143,100 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="G11" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="H11" t="n">
         <v>6.4</v>
       </c>
       <c r="I11" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J11" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="K11" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="L11" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="M11" t="n">
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="O11" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="P11" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="R11" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="S11" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="T11" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="U11" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="V11" t="n">
         <v>1.17</v>
       </c>
       <c r="W11" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="X11" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="Y11" t="n">
+        <v>75</v>
+      </c>
+      <c r="Z11" t="n">
         <v>120</v>
       </c>
-      <c r="Z11" t="n">
-        <v>90</v>
-      </c>
       <c r="AA11" t="n">
+        <v>210</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>19</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE11" t="n">
         <v>160</v>
       </c>
-      <c r="AB11" t="n">
-        <v>27</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>18</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>42</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>60</v>
-      </c>
       <c r="AF11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG11" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH11" t="n">
         <v>17</v>
       </c>
       <c r="AI11" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AJ11" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AK11" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AL11" t="n">
         <v>19</v>
@@ -3245,76 +3245,76 @@
         <v>55</v>
       </c>
       <c r="AN11" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="AO11" t="n">
+        <v>29</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AQ11" t="n">
         <v>50</v>
       </c>
-      <c r="AP11" t="n">
-        <v>50</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>48</v>
-      </c>
       <c r="AR11" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AS11" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AT11" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AU11" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AV11" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AW11" t="n">
         <v>50</v>
       </c>
       <c r="AX11" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AY11" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ11" t="n">
         <v>14.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BB11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BC11" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BD11" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BE11" t="n">
         <v>32</v>
       </c>
       <c r="BF11" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="BG11" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BH11" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BI11" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BJ11" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BK11" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
@@ -3323,22 +3323,22 @@
         <v>42</v>
       </c>
       <c r="BN11" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BO11" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="BP11" t="n">
         <v>8.6</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="BR11" t="n">
-        <v>14.5</v>
+        <v>65</v>
       </c>
       <c r="BS11" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT11" t="n">
         <v>12</v>
@@ -3347,26 +3347,26 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BV11" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BX11" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ11" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-16 11:17:21</t>
+          <t>2026-06-16 13:41:22</t>
         </is>
       </c>
     </row>
@@ -3397,16 +3397,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="G12" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="H12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I12" t="n">
         <v>3.1</v>
-      </c>
-      <c r="I12" t="n">
-        <v>3.2</v>
       </c>
       <c r="J12" t="n">
         <v>4.2</v>
@@ -3421,7 +3421,7 @@
         <v>1.02</v>
       </c>
       <c r="N12" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="O12" t="n">
         <v>1.09</v>
@@ -3439,82 +3439,82 @@
         <v>1.88</v>
       </c>
       <c r="T12" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="U12" t="n">
         <v>3.5</v>
       </c>
       <c r="V12" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W12" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="X12" t="n">
-        <v>950</v>
+        <v>120</v>
       </c>
       <c r="Y12" t="n">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="Z12" t="n">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="AA12" t="n">
         <v>210</v>
       </c>
       <c r="AB12" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="AC12" t="n">
         <v>12.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE12" t="n">
-        <v>160</v>
+        <v>48</v>
       </c>
       <c r="AF12" t="n">
         <v>40</v>
       </c>
       <c r="AG12" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AI12" t="n">
-        <v>120</v>
+        <v>46</v>
       </c>
       <c r="AJ12" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="AK12" t="n">
         <v>20</v>
       </c>
       <c r="AL12" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AM12" t="n">
-        <v>580</v>
+        <v>200</v>
       </c>
       <c r="AN12" t="n">
         <v>7.4</v>
       </c>
       <c r="AO12" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="AP12" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AQ12" t="n">
         <v>13</v>
       </c>
       <c r="AR12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AS12" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="AT12" t="n">
         <v>12.5</v>
@@ -3523,13 +3523,13 @@
         <v>10.5</v>
       </c>
       <c r="AV12" t="n">
-        <v>8.6</v>
+        <v>13</v>
       </c>
       <c r="AW12" t="n">
         <v>15</v>
       </c>
       <c r="AX12" t="n">
-        <v>14.5</v>
+        <v>20</v>
       </c>
       <c r="AY12" t="n">
         <v>7.2</v>
@@ -3538,25 +3538,25 @@
         <v>11.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="BB12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC12" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BE12" t="n">
         <v>18</v>
       </c>
       <c r="BF12" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BH12" t="n">
         <v>6</v>
@@ -3604,7 +3604,7 @@
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>3.9</v>
+        <v>8.6</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-16 11:17:21</t>
+          <t>2026-06-16 13:41:22</t>
         </is>
       </c>
     </row>
@@ -3657,7 +3657,7 @@
         <v>3.25</v>
       </c>
       <c r="H13" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="I13" t="n">
         <v>2.16</v>
@@ -3675,25 +3675,25 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="O13" t="n">
         <v>1.09</v>
       </c>
       <c r="P13" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Q13" t="n">
         <v>1.29</v>
       </c>
       <c r="R13" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="S13" t="n">
         <v>1.71</v>
       </c>
       <c r="T13" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="U13" t="n">
         <v>3.7</v>
@@ -3702,13 +3702,13 @@
         <v>1.86</v>
       </c>
       <c r="W13" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X13" t="n">
         <v>90</v>
       </c>
       <c r="Y13" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="Z13" t="n">
         <v>27</v>
@@ -3717,10 +3717,10 @@
         <v>34</v>
       </c>
       <c r="AB13" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AC13" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AD13" t="n">
         <v>13.5</v>
@@ -3744,7 +3744,7 @@
         <v>60</v>
       </c>
       <c r="AK13" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AL13" t="n">
         <v>26</v>
@@ -3762,7 +3762,7 @@
         <v>40</v>
       </c>
       <c r="AQ13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR13" t="n">
         <v>21</v>
@@ -3771,7 +3771,7 @@
         <v>29</v>
       </c>
       <c r="AT13" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AU13" t="n">
         <v>13</v>
@@ -3780,10 +3780,10 @@
         <v>11.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AX13" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AY13" t="n">
         <v>14</v>
@@ -3804,13 +3804,13 @@
         <v>21</v>
       </c>
       <c r="BE13" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BF13" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BH13" t="n">
         <v>6.4</v>
@@ -3834,7 +3834,7 @@
         <v>8</v>
       </c>
       <c r="BO13" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BP13" t="n">
         <v>20</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-16 11:17:21</t>
+          <t>2026-06-16 13:41:22</t>
         </is>
       </c>
     </row>
@@ -3905,22 +3905,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="G14" t="n">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="H14" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="I14" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="J14" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K14" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L14" t="n">
         <v>1.42</v>
@@ -3929,100 +3929,100 @@
         <v>1.08</v>
       </c>
       <c r="N14" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O14" t="n">
         <v>1.34</v>
       </c>
       <c r="P14" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="Q14" t="n">
         <v>2.02</v>
       </c>
       <c r="R14" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="S14" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="T14" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="U14" t="n">
         <v>1.87</v>
       </c>
       <c r="V14" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W14" t="n">
-        <v>2.44</v>
+        <v>2.58</v>
       </c>
       <c r="X14" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Z14" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AA14" t="n">
         <v>210</v>
       </c>
       <c r="AB14" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="AC14" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AD14" t="n">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="AE14" t="n">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="AF14" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AG14" t="n">
         <v>10.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI14" t="n">
-        <v>110</v>
+        <v>170</v>
       </c>
       <c r="AJ14" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AK14" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL14" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="AM14" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AN14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO14" t="n">
         <v>160</v>
       </c>
       <c r="AP14" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AR14" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AS14" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AT14" t="n">
         <v>7.2</v>
@@ -4034,101 +4034,101 @@
         <v>21</v>
       </c>
       <c r="AW14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX14" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AY14" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ14" t="n">
         <v>19.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="BB14" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BC14" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BE14" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF14" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG14" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH14" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="BJ14" t="n">
         <v>12</v>
       </c>
       <c r="BK14" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY14" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="BN14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>12</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>32</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BT14" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BU14" t="n">
-        <v>5</v>
-      </c>
-      <c r="BV14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW14" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BX14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY14" t="n">
-        <v>9</v>
-      </c>
       <c r="BZ14" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="CA14" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-16 11:17:21</t>
+          <t>2026-06-16 13:41:22</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB7"/>
+  <dimension ref="A1:CB5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,36 +843,36 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Varnamo</t>
+          <t>Vikingur Reykjavik</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Helsingborgs</t>
+          <t>KR Reykjavik</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>100</v>
+        <v>1.02</v>
       </c>
       <c r="G2" t="n">
-        <v>790</v>
+        <v>1.03</v>
       </c>
       <c r="H2" t="n">
-        <v>1.12</v>
+        <v>75</v>
       </c>
       <c r="I2" t="n">
-        <v>1.15</v>
+        <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="K2" t="n">
-        <v>10.5</v>
+        <v>42</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -881,43 +881,43 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S2" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U2" t="n">
         <v>1.01</v>
       </c>
-      <c r="Q2" t="n">
-        <v>100</v>
-      </c>
-      <c r="R2" t="n">
+      <c r="V2" t="n">
         <v>1.01</v>
       </c>
-      <c r="S2" t="n">
-        <v>350</v>
-      </c>
-      <c r="T2" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="V2" t="n">
-        <v>17.5</v>
-      </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.13</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>850</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
         <v>1000</v>
@@ -926,7 +926,7 @@
         <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>850</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
         <v>1000</v>
@@ -935,88 +935,88 @@
         <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>1.83</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AI2" t="n">
         <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AM2" t="n">
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AO2" t="n">
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>250</v>
+        <v>9</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.12</v>
+        <v>9</v>
       </c>
       <c r="AR2" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AT2" t="n">
-        <v>250</v>
+        <v>9</v>
       </c>
       <c r="AU2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AV2" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AW2" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AX2" t="n">
-        <v>250</v>
+        <v>1.69</v>
       </c>
       <c r="AY2" t="n">
-        <v>7.8</v>
+        <v>5.6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>7.8</v>
+        <v>38</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="BB2" t="n">
-        <v>250</v>
+        <v>5</v>
       </c>
       <c r="BC2" t="n">
-        <v>7.8</v>
+        <v>18.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BF2" t="n">
-        <v>7.8</v>
+        <v>22</v>
       </c>
       <c r="BG2" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
@@ -1080,14 +1080,14 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-16 15:50:53</t>
+          <t>2026-06-16 18:00:14</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,180 +1097,180 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>IA Akranes</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>United IK Nordic</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="H3" t="n">
+        <v>30</v>
+      </c>
+      <c r="I3" t="n">
+        <v>40</v>
+      </c>
+      <c r="J3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="R3" t="n">
         <v>1.01</v>
       </c>
-      <c r="G3" t="n">
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V3" t="n">
         <v>1.02</v>
       </c>
-      <c r="H3" t="n">
-        <v>230</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J3" t="n">
-        <v>50</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="S3" t="n">
+      <c r="W3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>770</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>780</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>990</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>34</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>210</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>90</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>210</v>
+      </c>
+      <c r="BB3" t="n">
         <v>26</v>
       </c>
-      <c r="T3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W3" t="n">
-        <v>50</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>85</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>970</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>970</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>250</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>250</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>250</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>250</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>250</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>250</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>250</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>250</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>55</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>120</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>9</v>
-      </c>
       <c r="BC3" t="n">
-        <v>38</v>
+        <v>95</v>
       </c>
       <c r="BD3" t="n">
-        <v>15.5</v>
+        <v>210</v>
       </c>
       <c r="BE3" t="n">
-        <v>48</v>
+        <v>4.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="BG3" t="n">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="BH3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-16 15:50:53</t>
+          <t>2026-06-16 18:00:14</t>
         </is>
       </c>
     </row>
@@ -1356,246 +1356,246 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Vikingur Reykjavik</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>KR Reykjavik</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.47</v>
+        <v>4.8</v>
       </c>
       <c r="G4" t="n">
-        <v>1.48</v>
+        <v>5.1</v>
       </c>
       <c r="H4" t="n">
-        <v>6.2</v>
+        <v>4.8</v>
       </c>
       <c r="I4" t="n">
-        <v>6.6</v>
+        <v>5.4</v>
       </c>
       <c r="J4" t="n">
-        <v>6</v>
+        <v>1.65</v>
       </c>
       <c r="K4" t="n">
-        <v>6.2</v>
+        <v>1.67</v>
       </c>
       <c r="L4" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>1.18</v>
       </c>
       <c r="W4" t="n">
-        <v>3.05</v>
+        <v>1.23</v>
       </c>
       <c r="X4" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>3.15</v>
+        <v>5.7</v>
       </c>
       <c r="AO4" t="n">
-        <v>24</v>
+        <v>5.5</v>
       </c>
       <c r="AP4" t="n">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="AQ4" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="AR4" t="n">
-        <v>80</v>
+        <v>11</v>
       </c>
       <c r="AS4" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="AT4" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="AU4" t="n">
-        <v>17.5</v>
+        <v>11</v>
       </c>
       <c r="AV4" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="AW4" t="n">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="AX4" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="AY4" t="n">
         <v>11</v>
       </c>
       <c r="AZ4" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="BA4" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="BB4" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="BC4" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BD4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="BE4" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="BF4" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="BG4" t="n">
-        <v>22</v>
+        <v>3.95</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BN4" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="BP4" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BT4" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BU4" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BV4" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BW4" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BZ4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="CA4" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-16 15:50:53</t>
+          <t>2026-06-16 18:00:14</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,752 +1605,244 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>IA Akranes</t>
+          <t>Fortaleza EC</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>America MG</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.2</v>
+        <v>1.58</v>
       </c>
       <c r="G5" t="n">
-        <v>2.26</v>
+        <v>1.6</v>
       </c>
       <c r="H5" t="n">
-        <v>3.1</v>
+        <v>7.6</v>
       </c>
       <c r="I5" t="n">
-        <v>3.25</v>
+        <v>8</v>
       </c>
       <c r="J5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K5" t="n">
         <v>4.2</v>
       </c>
-      <c r="K5" t="n">
-        <v>4.4</v>
-      </c>
       <c r="L5" t="n">
-        <v>1.21</v>
+        <v>1.45</v>
       </c>
       <c r="M5" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="N5" t="n">
-        <v>8.800000000000001</v>
+        <v>3.5</v>
       </c>
       <c r="O5" t="n">
-        <v>1.11</v>
+        <v>1.38</v>
       </c>
       <c r="P5" t="n">
-        <v>3.5</v>
+        <v>1.83</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.38</v>
+        <v>2.18</v>
       </c>
       <c r="R5" t="n">
-        <v>2.02</v>
+        <v>1.31</v>
       </c>
       <c r="S5" t="n">
-        <v>1.93</v>
+        <v>4</v>
       </c>
       <c r="T5" t="n">
-        <v>1.39</v>
+        <v>2.18</v>
       </c>
       <c r="U5" t="n">
-        <v>3.3</v>
+        <v>1.79</v>
       </c>
       <c r="V5" t="n">
-        <v>1.44</v>
+        <v>1.14</v>
       </c>
       <c r="W5" t="n">
-        <v>1.79</v>
+        <v>2.66</v>
       </c>
       <c r="X5" t="n">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="Y5" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="Z5" t="n">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="AA5" t="n">
-        <v>60</v>
+        <v>290</v>
       </c>
       <c r="AB5" t="n">
-        <v>23</v>
+        <v>6.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>12</v>
+        <v>9.6</v>
       </c>
       <c r="AD5" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>150</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>240</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>48</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>26</v>
+      </c>
+      <c r="AW5" t="n">
         <v>15</v>
       </c>
-      <c r="AE5" t="n">
-        <v>29</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>22</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>48</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AO5" t="n">
+      <c r="AX5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>25</v>
+      </c>
+      <c r="BA5" t="n">
         <v>13.5</v>
       </c>
-      <c r="AP5" t="n">
-        <v>34</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>25</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>28</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>50</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>20</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AV5" t="n">
+      <c r="BB5" t="n">
         <v>13.5</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>25</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>19</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>24</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>26</v>
       </c>
       <c r="BC5" t="n">
         <v>17</v>
       </c>
       <c r="BD5" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG5" t="n">
         <v>19</v>
       </c>
-      <c r="BE5" t="n">
-        <v>34</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BG5" t="n">
+      <c r="BH5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>12</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>11</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>32</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>11</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>80</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>11</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>85</v>
+      </c>
+      <c r="BY5" t="n">
         <v>11.5</v>
       </c>
-      <c r="BH5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>42</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>27</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>25</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>34</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BZ5" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.71</v>
+        <v>8.4</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-16 15:50:53</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Icelandic Urvalsdeild</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>16:15:00</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Stjarnan</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Breidablik</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>3</v>
-      </c>
-      <c r="G6" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="H6" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="K6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="P6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="U6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="X6" t="n">
-        <v>60</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>30</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>27</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>38</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>40</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>15</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>22</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>44</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>15</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>120</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>26</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>32</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>55</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>25</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>22</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>30</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>22</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>13</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>32</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>18</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>42</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>24</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>22</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>27</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>7</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>42</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>40</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>8</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>20</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>14</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>17</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>2026-06-16 15:50:53</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Brazilian Serie B</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>20:00:00</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Fortaleza EC</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>America MG</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="H7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="W7" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="X7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>22</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>210</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>18</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>150</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>19</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>48</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>22</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>18</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>34</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>17</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>17</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>6</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>11</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>28</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>21</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="CB7" t="inlineStr">
-        <is>
-          <t>2026-06-16 15:50:53</t>
+          <t>2026-06-16 18:00:14</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB2"/>
+  <dimension ref="A1:CB1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -827,260 +827,6 @@
       <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>SnapshotTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Brazilian Serie B</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>20:00:00</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Fortaleza EC</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>America MG</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="H2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="I2" t="n">
-        <v>55</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N2" t="n">
-        <v>3</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S2" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>19</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>990</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>990</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>990</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>18</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>420</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>970</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>960</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>590</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>910</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>690</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>950</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>960</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>2026-06-16 20:09:59</t>
         </is>
       </c>
     </row>
